--- a/DhalisMenu_cat.xlsx
+++ b/DhalisMenu_cat.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\All DATA Important\Projects\New folder\restaurant_billing_app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69EE69A2-9C1F-40B5-9C2F-319FB75620FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17F92D24-3C83-45C1-ADE9-F01346695040}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="145">
   <si>
     <t>Item</t>
   </si>
@@ -455,6 +455,9 @@
   </si>
   <si>
     <t>Thumsup30</t>
+  </si>
+  <si>
+    <t>One Liter Bottel Cold Drink</t>
   </si>
 </sst>
 </file>
@@ -827,7 +830,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F70"/>
+  <dimension ref="A1:F71"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="8.81640625" bestFit="1" customWidth="1"/>
@@ -2202,16 +2205,16 @@
         <v>103</v>
       </c>
       <c r="B69" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
       <c r="C69">
         <v>0</v>
       </c>
       <c r="D69">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="E69" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="F69" t="s">
         <v>7</v>
@@ -2222,18 +2225,38 @@
         <v>103</v>
       </c>
       <c r="B70" t="s">
+        <v>131</v>
+      </c>
+      <c r="C70">
+        <v>0</v>
+      </c>
+      <c r="D70">
+        <v>60</v>
+      </c>
+      <c r="E70" t="s">
+        <v>132</v>
+      </c>
+      <c r="F70" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A71" t="s">
+        <v>103</v>
+      </c>
+      <c r="B71" t="s">
         <v>133</v>
       </c>
-      <c r="C70">
-        <v>0</v>
-      </c>
-      <c r="D70">
+      <c r="C71">
+        <v>0</v>
+      </c>
+      <c r="D71">
         <v>85</v>
       </c>
-      <c r="E70" t="s">
+      <c r="E71" t="s">
         <v>134</v>
       </c>
-      <c r="F70" t="s">
+      <c r="F71" t="s">
         <v>7</v>
       </c>
     </row>

--- a/DhalisMenu_cat.xlsx
+++ b/DhalisMenu_cat.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\All DATA Important\Projects\New folder\restaurant_billing_app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17F92D24-3C83-45C1-ADE9-F01346695040}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB6BA246-B837-4C2B-986F-642DCD71700A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1591,7 +1591,7 @@
         <v>0</v>
       </c>
       <c r="D38">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E38" t="s">
         <v>76</v>

--- a/DhalisMenu_cat.xlsx
+++ b/DhalisMenu_cat.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\All DATA Important\Projects\New folder\restaurant_billing_app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB6BA246-B837-4C2B-986F-642DCD71700A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E486D152-17FA-4159-9103-F4AFB3FF0670}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1291,7 +1291,7 @@
         <v>0</v>
       </c>
       <c r="D23">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="E23" t="s">
         <v>49</v>

--- a/DhalisMenu_cat.xlsx
+++ b/DhalisMenu_cat.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\All DATA Important\Projects\New folder\restaurant_billing_app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E486D152-17FA-4159-9103-F4AFB3FF0670}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{627C8BE4-0852-4C65-AB84-6ECFF40CCE05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="150">
   <si>
     <t>Item</t>
   </si>
@@ -458,6 +458,21 @@
   </si>
   <si>
     <t>One Liter Bottel Cold Drink</t>
+  </si>
+  <si>
+    <t>Frooti Big Bottel Cold Drink</t>
+  </si>
+  <si>
+    <t>Frooti Big Bottel Cold Drink.jpg</t>
+  </si>
+  <si>
+    <t>Water Bottle 30</t>
+  </si>
+  <si>
+    <t>Water Bottle 20</t>
+  </si>
+  <si>
+    <t>Water Bottle.jpg</t>
   </si>
 </sst>
 </file>
@@ -830,7 +845,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F71"/>
+  <dimension ref="A1:F74"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="8.81640625" bestFit="1" customWidth="1"/>
@@ -1211,7 +1226,7 @@
         <v>0</v>
       </c>
       <c r="D19">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E19" t="s">
         <v>41</v>
@@ -1231,7 +1246,7 @@
         <v>0</v>
       </c>
       <c r="D20">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E20" t="s">
         <v>43</v>
@@ -1251,7 +1266,7 @@
         <v>0</v>
       </c>
       <c r="D21">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E21" t="s">
         <v>45</v>
@@ -2257,6 +2272,66 @@
         <v>134</v>
       </c>
       <c r="F71" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A72" t="s">
+        <v>103</v>
+      </c>
+      <c r="B72" t="s">
+        <v>145</v>
+      </c>
+      <c r="C72">
+        <v>0</v>
+      </c>
+      <c r="D72">
+        <v>100</v>
+      </c>
+      <c r="E72" t="s">
+        <v>146</v>
+      </c>
+      <c r="F72" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A73" t="s">
+        <v>103</v>
+      </c>
+      <c r="B73" t="s">
+        <v>147</v>
+      </c>
+      <c r="C73">
+        <v>0</v>
+      </c>
+      <c r="D73">
+        <v>30</v>
+      </c>
+      <c r="E73" t="s">
+        <v>149</v>
+      </c>
+      <c r="F73" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A74" t="s">
+        <v>103</v>
+      </c>
+      <c r="B74" t="s">
+        <v>148</v>
+      </c>
+      <c r="C74">
+        <v>0</v>
+      </c>
+      <c r="D74">
+        <v>30</v>
+      </c>
+      <c r="E74" t="s">
+        <v>149</v>
+      </c>
+      <c r="F74" t="s">
         <v>7</v>
       </c>
     </row>

--- a/DhalisMenu_cat.xlsx
+++ b/DhalisMenu_cat.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\All DATA Important\Projects\New folder\restaurant_billing_app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{627C8BE4-0852-4C65-AB84-6ECFF40CCE05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB126082-A450-4462-8133-5414C5952FC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -463,16 +463,16 @@
     <t>Frooti Big Bottel Cold Drink</t>
   </si>
   <si>
-    <t>Frooti Big Bottel Cold Drink.jpg</t>
-  </si>
-  <si>
     <t>Water Bottle 30</t>
   </si>
   <si>
     <t>Water Bottle 20</t>
   </si>
   <si>
-    <t>Water Bottle.jpg</t>
+    <t>Water Bottle.jpeg</t>
+  </si>
+  <si>
+    <t>Frooti Big Bottel Cold Drink.jpeg</t>
   </si>
 </sst>
 </file>
@@ -2289,7 +2289,7 @@
         <v>100</v>
       </c>
       <c r="E72" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="F72" t="s">
         <v>7</v>
@@ -2300,7 +2300,7 @@
         <v>103</v>
       </c>
       <c r="B73" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C73">
         <v>0</v>
@@ -2309,7 +2309,7 @@
         <v>30</v>
       </c>
       <c r="E73" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F73" t="s">
         <v>7</v>
@@ -2320,7 +2320,7 @@
         <v>103</v>
       </c>
       <c r="B74" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C74">
         <v>0</v>
@@ -2329,7 +2329,7 @@
         <v>30</v>
       </c>
       <c r="E74" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F74" t="s">
         <v>7</v>

--- a/DhalisMenu_cat.xlsx
+++ b/DhalisMenu_cat.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\All DATA Important\Projects\New folder\restaurant_billing_app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB126082-A450-4462-8133-5414C5952FC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23583BD6-D4A5-4D97-93B5-31BB153FD294}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -322,9 +322,6 @@
     <t>Thums up 35.jpg</t>
   </si>
   <si>
-    <t>Campa Energy 30Rs</t>
-  </si>
-  <si>
     <t>Campa Energy 30Rs.jpg</t>
   </si>
   <si>
@@ -473,6 +470,9 @@
   </si>
   <si>
     <t>Frooti Big Bottel Cold Drink.jpeg</t>
+  </si>
+  <si>
+    <t>Campa Energy 35Rs</t>
   </si>
 </sst>
 </file>
@@ -1226,7 +1226,7 @@
         <v>0</v>
       </c>
       <c r="D19">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E19" t="s">
         <v>41</v>
@@ -1246,7 +1246,7 @@
         <v>0</v>
       </c>
       <c r="D20">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E20" t="s">
         <v>43</v>
@@ -1266,7 +1266,7 @@
         <v>0</v>
       </c>
       <c r="D21">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E21" t="s">
         <v>45</v>
@@ -1277,7 +1277,7 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B22" t="s">
         <v>46</v>
@@ -1297,7 +1297,7 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B23" t="s">
         <v>48</v>
@@ -1317,7 +1317,7 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B24" t="s">
         <v>50</v>
@@ -1337,7 +1337,7 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B25" t="s">
         <v>52</v>
@@ -1357,7 +1357,7 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B26" t="s">
         <v>54</v>
@@ -1377,7 +1377,7 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B27" t="s">
         <v>56</v>
@@ -1397,7 +1397,7 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B28" t="s">
         <v>57</v>
@@ -1417,7 +1417,7 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B29" t="s">
         <v>58</v>
@@ -1437,7 +1437,7 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B30" t="s">
         <v>59</v>
@@ -1457,7 +1457,7 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B31" t="s">
         <v>61</v>
@@ -1477,7 +1477,7 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B32" t="s">
         <v>63</v>
@@ -1497,7 +1497,7 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B33" t="s">
         <v>65</v>
@@ -1517,7 +1517,7 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B34" t="s">
         <v>67</v>
@@ -1537,7 +1537,7 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B35" t="s">
         <v>69</v>
@@ -1557,7 +1557,7 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B36" t="s">
         <v>71</v>
@@ -1577,7 +1577,7 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B37" t="s">
         <v>73</v>
@@ -1597,7 +1597,7 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B38" t="s">
         <v>75</v>
@@ -1617,7 +1617,7 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B39" t="s">
         <v>77</v>
@@ -1637,10 +1637,10 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B40" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C40">
         <v>0</v>
@@ -1657,10 +1657,10 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B41" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C41">
         <v>0</v>
@@ -1669,7 +1669,7 @@
         <v>45</v>
       </c>
       <c r="E41" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F41" t="s">
         <v>7</v>
@@ -1677,7 +1677,7 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B42" t="s">
         <v>80</v>
@@ -1697,7 +1697,7 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B43" t="s">
         <v>82</v>
@@ -1717,10 +1717,10 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B44" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C44">
         <v>0</v>
@@ -1729,7 +1729,7 @@
         <v>53</v>
       </c>
       <c r="E44" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F44" t="s">
         <v>7</v>
@@ -1737,10 +1737,10 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B45" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C45">
         <v>0</v>
@@ -1749,7 +1749,7 @@
         <v>62</v>
       </c>
       <c r="E45" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F45" t="s">
         <v>7</v>
@@ -1757,10 +1757,10 @@
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B46" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C46">
         <v>0</v>
@@ -1769,7 +1769,7 @@
         <v>52</v>
       </c>
       <c r="E46" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F46" t="s">
         <v>7</v>
@@ -1777,10 +1777,10 @@
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B47" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C47">
         <v>0</v>
@@ -1789,7 +1789,7 @@
         <v>52</v>
       </c>
       <c r="E47" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="F47" t="s">
         <v>7</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B48" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C48">
         <v>0</v>
@@ -1809,7 +1809,7 @@
         <v>57</v>
       </c>
       <c r="E48" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="F48" t="s">
         <v>7</v>
@@ -1817,10 +1817,10 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B49" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C49">
         <v>0</v>
@@ -1829,7 +1829,7 @@
         <v>25</v>
       </c>
       <c r="E49" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F49" t="s">
         <v>7</v>
@@ -1837,10 +1837,10 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B50" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C50">
         <v>0</v>
@@ -1849,7 +1849,7 @@
         <v>10</v>
       </c>
       <c r="E50" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F50" t="s">
         <v>7</v>
@@ -1857,10 +1857,10 @@
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B51" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C51">
         <v>0</v>
@@ -1869,7 +1869,7 @@
         <v>10</v>
       </c>
       <c r="E51" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F51" t="s">
         <v>7</v>
@@ -1877,10 +1877,10 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B52" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C52">
         <v>0</v>
@@ -1889,7 +1889,7 @@
         <v>5</v>
       </c>
       <c r="E52" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F52" t="s">
         <v>7</v>
@@ -1897,10 +1897,10 @@
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B53" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C53">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>25</v>
       </c>
       <c r="E53" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F53" t="s">
         <v>7</v>
@@ -1917,10 +1917,10 @@
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B54" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C54">
         <v>0</v>
@@ -1929,7 +1929,7 @@
         <v>10</v>
       </c>
       <c r="E54" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F54" t="s">
         <v>7</v>
@@ -1937,10 +1937,10 @@
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B55" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C55">
         <v>0</v>
@@ -1949,7 +1949,7 @@
         <v>1</v>
       </c>
       <c r="E55" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F55" t="s">
         <v>7</v>
@@ -1957,7 +1957,7 @@
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B56" t="s">
         <v>84</v>
@@ -1977,7 +1977,7 @@
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B57" t="s">
         <v>86</v>
@@ -1997,7 +1997,7 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B58" t="s">
         <v>88</v>
@@ -2017,7 +2017,7 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B59" t="s">
         <v>90</v>
@@ -2037,7 +2037,7 @@
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B60" t="s">
         <v>92</v>
@@ -2057,10 +2057,10 @@
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B61" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C61">
         <v>0</v>
@@ -2069,7 +2069,7 @@
         <v>20</v>
       </c>
       <c r="E61" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F61" t="s">
         <v>7</v>
@@ -2077,10 +2077,10 @@
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B62" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C62">
         <v>0</v>
@@ -2089,7 +2089,7 @@
         <v>20</v>
       </c>
       <c r="E62" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F62" t="s">
         <v>7</v>
@@ -2097,10 +2097,10 @@
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B63" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C63">
         <v>0</v>
@@ -2109,7 +2109,7 @@
         <v>20</v>
       </c>
       <c r="E63" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F63" t="s">
         <v>7</v>
@@ -2117,10 +2117,10 @@
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B64" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C64">
         <v>0</v>
@@ -2129,7 +2129,7 @@
         <v>20</v>
       </c>
       <c r="E64" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F64" t="s">
         <v>7</v>
@@ -2137,7 +2137,7 @@
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B65" t="s">
         <v>95</v>
@@ -2157,10 +2157,10 @@
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B66" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C66">
         <v>0</v>
@@ -2177,7 +2177,7 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B67" t="s">
         <v>97</v>
@@ -2197,19 +2197,19 @@
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B68" t="s">
+        <v>149</v>
+      </c>
+      <c r="C68">
+        <v>0</v>
+      </c>
+      <c r="D68">
+        <v>35</v>
+      </c>
+      <c r="E68" t="s">
         <v>99</v>
-      </c>
-      <c r="C68">
-        <v>0</v>
-      </c>
-      <c r="D68">
-        <v>30</v>
-      </c>
-      <c r="E68" t="s">
-        <v>100</v>
       </c>
       <c r="F68" t="s">
         <v>7</v>
@@ -2217,10 +2217,10 @@
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B69" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C69">
         <v>0</v>
@@ -2229,7 +2229,7 @@
         <v>50</v>
       </c>
       <c r="E69" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F69" t="s">
         <v>7</v>
@@ -2237,10 +2237,10 @@
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B70" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C70">
         <v>0</v>
@@ -2249,7 +2249,7 @@
         <v>60</v>
       </c>
       <c r="E70" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F70" t="s">
         <v>7</v>
@@ -2257,10 +2257,10 @@
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B71" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C71">
         <v>0</v>
@@ -2269,7 +2269,7 @@
         <v>85</v>
       </c>
       <c r="E71" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F71" t="s">
         <v>7</v>
@@ -2277,10 +2277,10 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B72" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C72">
         <v>0</v>
@@ -2289,7 +2289,7 @@
         <v>100</v>
       </c>
       <c r="E72" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F72" t="s">
         <v>7</v>
@@ -2297,10 +2297,10 @@
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B73" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C73">
         <v>0</v>
@@ -2309,7 +2309,7 @@
         <v>30</v>
       </c>
       <c r="E73" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F73" t="s">
         <v>7</v>
@@ -2317,10 +2317,10 @@
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B74" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C74">
         <v>0</v>
@@ -2329,7 +2329,7 @@
         <v>30</v>
       </c>
       <c r="E74" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F74" t="s">
         <v>7</v>

--- a/DhalisMenu_cat.xlsx
+++ b/DhalisMenu_cat.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\All DATA Important\Projects\New folder\restaurant_billing_app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23583BD6-D4A5-4D97-93B5-31BB153FD294}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2FF8A1D-7995-431F-9AF4-E0BD8A7785BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$61</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$68</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="157">
   <si>
     <t>Item</t>
   </si>
@@ -473,6 +473,27 @@
   </si>
   <si>
     <t>Campa Energy 35Rs</t>
+  </si>
+  <si>
+    <t>Chill Patato</t>
+  </si>
+  <si>
+    <t>Honey Chill Patato</t>
+  </si>
+  <si>
+    <t>Singapuri Chowmin</t>
+  </si>
+  <si>
+    <t>Chowmin</t>
+  </si>
+  <si>
+    <t>Momos Vegs</t>
+  </si>
+  <si>
+    <t>Momos Paneer</t>
+  </si>
+  <si>
+    <t>Spring Roll</t>
   </si>
 </sst>
 </file>
@@ -845,7 +866,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F74"/>
+  <dimension ref="A1:F81"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="8.81640625" bestFit="1" customWidth="1"/>
@@ -940,16 +961,13 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>150</v>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="D5">
-        <v>90</v>
-      </c>
-      <c r="E5" t="s">
-        <v>13</v>
+        <v>80</v>
       </c>
       <c r="F5" t="s">
         <v>7</v>
@@ -960,16 +978,13 @@
         <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>14</v>
+        <v>151</v>
       </c>
       <c r="C6">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="D6">
-        <v>90</v>
-      </c>
-      <c r="E6" t="s">
-        <v>15</v>
+        <v>100</v>
       </c>
       <c r="F6" t="s">
         <v>7</v>
@@ -980,16 +995,13 @@
         <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>16</v>
+        <v>153</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="D7">
-        <v>90</v>
-      </c>
-      <c r="E7" t="s">
-        <v>17</v>
+        <v>80</v>
       </c>
       <c r="F7" t="s">
         <v>7</v>
@@ -1000,16 +1012,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>18</v>
+        <v>152</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="D8">
-        <v>90</v>
-      </c>
-      <c r="E8" t="s">
-        <v>19</v>
+        <v>100</v>
       </c>
       <c r="F8" t="s">
         <v>7</v>
@@ -1020,16 +1029,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>20</v>
+        <v>154</v>
       </c>
       <c r="C9">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="D9">
-        <v>90</v>
-      </c>
-      <c r="E9" t="s">
-        <v>21</v>
+        <v>50</v>
       </c>
       <c r="F9" t="s">
         <v>7</v>
@@ -1040,16 +1046,13 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>22</v>
+        <v>155</v>
       </c>
       <c r="C10">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="D10">
-        <v>350</v>
-      </c>
-      <c r="E10" t="s">
-        <v>23</v>
+        <v>90</v>
       </c>
       <c r="F10" t="s">
         <v>7</v>
@@ -1060,16 +1063,13 @@
         <v>7</v>
       </c>
       <c r="B11" t="s">
-        <v>24</v>
+        <v>156</v>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="D11">
-        <v>150</v>
-      </c>
-      <c r="E11" t="s">
-        <v>25</v>
+        <v>70</v>
       </c>
       <c r="F11" t="s">
         <v>7</v>
@@ -1080,16 +1080,16 @@
         <v>7</v>
       </c>
       <c r="B12" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="C12">
         <v>0</v>
       </c>
       <c r="D12">
-        <v>150</v>
+        <v>90</v>
       </c>
       <c r="E12" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="F12" t="s">
         <v>7</v>
@@ -1100,16 +1100,16 @@
         <v>7</v>
       </c>
       <c r="B13" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="C13">
         <v>0</v>
       </c>
       <c r="D13">
-        <v>175</v>
+        <v>90</v>
       </c>
       <c r="E13" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="F13" t="s">
         <v>7</v>
@@ -1120,16 +1120,16 @@
         <v>7</v>
       </c>
       <c r="B14" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="C14">
         <v>0</v>
       </c>
       <c r="D14">
-        <v>200</v>
+        <v>90</v>
       </c>
       <c r="E14" t="s">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="F14" t="s">
         <v>7</v>
@@ -1140,16 +1140,16 @@
         <v>7</v>
       </c>
       <c r="B15" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="C15">
         <v>0</v>
       </c>
       <c r="D15">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="E15" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="F15" t="s">
         <v>7</v>
@@ -1160,16 +1160,16 @@
         <v>7</v>
       </c>
       <c r="B16" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="C16">
         <v>0</v>
       </c>
       <c r="D16">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="E16" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="F16" t="s">
         <v>7</v>
@@ -1180,16 +1180,16 @@
         <v>7</v>
       </c>
       <c r="B17" t="s">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="C17">
         <v>0</v>
       </c>
       <c r="D17">
-        <v>80</v>
+        <v>350</v>
       </c>
       <c r="E17" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="F17" t="s">
         <v>7</v>
@@ -1200,16 +1200,16 @@
         <v>7</v>
       </c>
       <c r="B18" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="C18">
         <v>0</v>
       </c>
       <c r="D18">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="E18" t="s">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="F18" t="s">
         <v>7</v>
@@ -1220,16 +1220,16 @@
         <v>7</v>
       </c>
       <c r="B19" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="C19">
         <v>0</v>
       </c>
       <c r="D19">
-        <v>20</v>
+        <v>150</v>
       </c>
       <c r="E19" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="F19" t="s">
         <v>7</v>
@@ -1240,16 +1240,16 @@
         <v>7</v>
       </c>
       <c r="B20" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="C20">
         <v>0</v>
       </c>
       <c r="D20">
-        <v>25</v>
+        <v>175</v>
       </c>
       <c r="E20" t="s">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="F20" t="s">
         <v>7</v>
@@ -1260,16 +1260,16 @@
         <v>7</v>
       </c>
       <c r="B21" t="s">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="C21">
         <v>0</v>
       </c>
       <c r="D21">
-        <v>30</v>
+        <v>200</v>
       </c>
       <c r="E21" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="F21" t="s">
         <v>7</v>
@@ -1277,19 +1277,19 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>103</v>
+        <v>7</v>
       </c>
       <c r="B22" t="s">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="C22">
         <v>0</v>
       </c>
       <c r="D22">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="E22" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="F22" t="s">
         <v>7</v>
@@ -1297,19 +1297,19 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>103</v>
+        <v>7</v>
       </c>
       <c r="B23" t="s">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="C23">
         <v>0</v>
       </c>
       <c r="D23">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="E23" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="F23" t="s">
         <v>7</v>
@@ -1317,19 +1317,19 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>103</v>
+        <v>7</v>
       </c>
       <c r="B24" t="s">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="C24">
         <v>0</v>
       </c>
       <c r="D24">
-        <v>650</v>
+        <v>80</v>
       </c>
       <c r="E24" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="F24" t="s">
         <v>7</v>
@@ -1337,19 +1337,19 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>103</v>
+        <v>7</v>
       </c>
       <c r="B25" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="C25">
         <v>0</v>
       </c>
       <c r="D25">
-        <v>550</v>
+        <v>100</v>
       </c>
       <c r="E25" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="F25" t="s">
         <v>7</v>
@@ -1357,19 +1357,19 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>103</v>
+        <v>7</v>
       </c>
       <c r="B26" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="C26">
         <v>0</v>
       </c>
       <c r="D26">
-        <v>600</v>
+        <v>20</v>
       </c>
       <c r="E26" t="s">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="F26" t="s">
         <v>7</v>
@@ -1377,19 +1377,19 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>103</v>
+        <v>7</v>
       </c>
       <c r="B27" t="s">
-        <v>56</v>
+        <v>42</v>
       </c>
       <c r="C27">
         <v>0</v>
       </c>
       <c r="D27">
-        <v>400</v>
+        <v>25</v>
       </c>
       <c r="E27" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="F27" t="s">
         <v>7</v>
@@ -1397,19 +1397,19 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>103</v>
+        <v>7</v>
       </c>
       <c r="B28" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="C28">
         <v>0</v>
       </c>
       <c r="D28">
-        <v>550</v>
+        <v>30</v>
       </c>
       <c r="E28" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="F28" t="s">
         <v>7</v>
@@ -1420,16 +1420,16 @@
         <v>103</v>
       </c>
       <c r="B29" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="C29">
         <v>0</v>
       </c>
       <c r="D29">
-        <v>500</v>
+        <v>25</v>
       </c>
       <c r="E29" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="F29" t="s">
         <v>7</v>
@@ -1437,19 +1437,19 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B30" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="C30">
         <v>0</v>
       </c>
       <c r="D30">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="E30" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="F30" t="s">
         <v>7</v>
@@ -1457,19 +1457,19 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B31" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="C31">
         <v>0</v>
       </c>
       <c r="D31">
-        <v>10</v>
+        <v>650</v>
       </c>
       <c r="E31" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="F31" t="s">
         <v>7</v>
@@ -1477,19 +1477,19 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B32" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="C32">
         <v>0</v>
       </c>
       <c r="D32">
-        <v>20</v>
+        <v>550</v>
       </c>
       <c r="E32" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="F32" t="s">
         <v>7</v>
@@ -1497,19 +1497,19 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B33" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="C33">
         <v>0</v>
       </c>
       <c r="D33">
-        <v>5</v>
+        <v>600</v>
       </c>
       <c r="E33" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="F33" t="s">
         <v>7</v>
@@ -1517,19 +1517,19 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B34" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="C34">
         <v>0</v>
       </c>
       <c r="D34">
-        <v>10</v>
+        <v>400</v>
       </c>
       <c r="E34" t="s">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="F34" t="s">
         <v>7</v>
@@ -1537,19 +1537,19 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B35" t="s">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="C35">
         <v>0</v>
       </c>
       <c r="D35">
-        <v>15</v>
+        <v>550</v>
       </c>
       <c r="E35" t="s">
-        <v>70</v>
+        <v>51</v>
       </c>
       <c r="F35" t="s">
         <v>7</v>
@@ -1557,19 +1557,19 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B36" t="s">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="C36">
         <v>0</v>
       </c>
       <c r="D36">
-        <v>10</v>
+        <v>500</v>
       </c>
       <c r="E36" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="F36" t="s">
         <v>7</v>
@@ -1580,16 +1580,16 @@
         <v>104</v>
       </c>
       <c r="B37" t="s">
-        <v>73</v>
+        <v>59</v>
       </c>
       <c r="C37">
         <v>0</v>
       </c>
       <c r="D37">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E37" t="s">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="F37" t="s">
         <v>7</v>
@@ -1600,16 +1600,16 @@
         <v>104</v>
       </c>
       <c r="B38" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="C38">
         <v>0</v>
       </c>
       <c r="D38">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="E38" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
       <c r="F38" t="s">
         <v>7</v>
@@ -1620,16 +1620,16 @@
         <v>104</v>
       </c>
       <c r="B39" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="C39">
         <v>0</v>
       </c>
       <c r="D39">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E39" t="s">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="F39" t="s">
         <v>7</v>
@@ -1640,16 +1640,16 @@
         <v>104</v>
       </c>
       <c r="B40" t="s">
-        <v>120</v>
+        <v>65</v>
       </c>
       <c r="C40">
         <v>0</v>
       </c>
       <c r="D40">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E40" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="F40" t="s">
         <v>7</v>
@@ -1660,16 +1660,16 @@
         <v>104</v>
       </c>
       <c r="B41" t="s">
-        <v>119</v>
+        <v>67</v>
       </c>
       <c r="C41">
         <v>0</v>
       </c>
       <c r="D41">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="E41" t="s">
-        <v>121</v>
+        <v>68</v>
       </c>
       <c r="F41" t="s">
         <v>7</v>
@@ -1680,16 +1680,16 @@
         <v>104</v>
       </c>
       <c r="B42" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="C42">
         <v>0</v>
       </c>
       <c r="D42">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="E42" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="F42" t="s">
         <v>7</v>
@@ -1700,7 +1700,7 @@
         <v>104</v>
       </c>
       <c r="B43" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="C43">
         <v>0</v>
@@ -1709,7 +1709,7 @@
         <v>10</v>
       </c>
       <c r="E43" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="F43" t="s">
         <v>7</v>
@@ -1720,16 +1720,16 @@
         <v>104</v>
       </c>
       <c r="B44" t="s">
-        <v>110</v>
+        <v>73</v>
       </c>
       <c r="C44">
         <v>0</v>
       </c>
       <c r="D44">
-        <v>53</v>
+        <v>10</v>
       </c>
       <c r="E44" t="s">
-        <v>109</v>
+        <v>74</v>
       </c>
       <c r="F44" t="s">
         <v>7</v>
@@ -1740,16 +1740,16 @@
         <v>104</v>
       </c>
       <c r="B45" t="s">
-        <v>111</v>
+        <v>75</v>
       </c>
       <c r="C45">
         <v>0</v>
       </c>
       <c r="D45">
-        <v>62</v>
+        <v>27</v>
       </c>
       <c r="E45" t="s">
-        <v>112</v>
+        <v>76</v>
       </c>
       <c r="F45" t="s">
         <v>7</v>
@@ -1760,16 +1760,16 @@
         <v>104</v>
       </c>
       <c r="B46" t="s">
-        <v>113</v>
+        <v>77</v>
       </c>
       <c r="C46">
         <v>0</v>
       </c>
       <c r="D46">
-        <v>52</v>
+        <v>5</v>
       </c>
       <c r="E46" t="s">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="F46" t="s">
         <v>7</v>
@@ -1780,16 +1780,16 @@
         <v>104</v>
       </c>
       <c r="B47" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="C47">
         <v>0</v>
       </c>
       <c r="D47">
-        <v>52</v>
+        <v>20</v>
       </c>
       <c r="E47" t="s">
-        <v>116</v>
+        <v>79</v>
       </c>
       <c r="F47" t="s">
         <v>7</v>
@@ -1800,16 +1800,16 @@
         <v>104</v>
       </c>
       <c r="B48" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C48">
         <v>0</v>
       </c>
       <c r="D48">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="E48" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F48" t="s">
         <v>7</v>
@@ -1820,7 +1820,7 @@
         <v>104</v>
       </c>
       <c r="B49" t="s">
-        <v>136</v>
+        <v>80</v>
       </c>
       <c r="C49">
         <v>0</v>
@@ -1829,7 +1829,7 @@
         <v>25</v>
       </c>
       <c r="E49" t="s">
-        <v>137</v>
+        <v>81</v>
       </c>
       <c r="F49" t="s">
         <v>7</v>
@@ -1840,7 +1840,7 @@
         <v>104</v>
       </c>
       <c r="B50" t="s">
-        <v>134</v>
+        <v>82</v>
       </c>
       <c r="C50">
         <v>0</v>
@@ -1849,7 +1849,7 @@
         <v>10</v>
       </c>
       <c r="E50" t="s">
-        <v>138</v>
+        <v>83</v>
       </c>
       <c r="F50" t="s">
         <v>7</v>
@@ -1860,16 +1860,16 @@
         <v>104</v>
       </c>
       <c r="B51" t="s">
-        <v>139</v>
+        <v>110</v>
       </c>
       <c r="C51">
         <v>0</v>
       </c>
       <c r="D51">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="E51" t="s">
-        <v>141</v>
+        <v>109</v>
       </c>
       <c r="F51" t="s">
         <v>7</v>
@@ -1880,16 +1880,16 @@
         <v>104</v>
       </c>
       <c r="B52" t="s">
-        <v>135</v>
+        <v>111</v>
       </c>
       <c r="C52">
         <v>0</v>
       </c>
       <c r="D52">
-        <v>5</v>
+        <v>62</v>
       </c>
       <c r="E52" t="s">
-        <v>140</v>
+        <v>112</v>
       </c>
       <c r="F52" t="s">
         <v>7</v>
@@ -1900,16 +1900,16 @@
         <v>104</v>
       </c>
       <c r="B53" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="C53">
         <v>0</v>
       </c>
       <c r="D53">
-        <v>25</v>
+        <v>52</v>
       </c>
       <c r="E53" t="s">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="F53" t="s">
         <v>7</v>
@@ -1920,16 +1920,16 @@
         <v>104</v>
       </c>
       <c r="B54" t="s">
-        <v>128</v>
+        <v>115</v>
       </c>
       <c r="C54">
         <v>0</v>
       </c>
       <c r="D54">
-        <v>10</v>
+        <v>52</v>
       </c>
       <c r="E54" t="s">
-        <v>129</v>
+        <v>116</v>
       </c>
       <c r="F54" t="s">
         <v>7</v>
@@ -1940,16 +1940,16 @@
         <v>104</v>
       </c>
       <c r="B55" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="C55">
         <v>0</v>
       </c>
       <c r="D55">
-        <v>1</v>
+        <v>57</v>
       </c>
       <c r="E55" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="F55" t="s">
         <v>7</v>
@@ -1957,19 +1957,19 @@
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B56" t="s">
-        <v>84</v>
+        <v>136</v>
       </c>
       <c r="C56">
         <v>0</v>
       </c>
       <c r="D56">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="E56" t="s">
-        <v>85</v>
+        <v>137</v>
       </c>
       <c r="F56" t="s">
         <v>7</v>
@@ -1977,10 +1977,10 @@
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B57" t="s">
-        <v>86</v>
+        <v>134</v>
       </c>
       <c r="C57">
         <v>0</v>
@@ -1989,7 +1989,7 @@
         <v>10</v>
       </c>
       <c r="E57" t="s">
-        <v>87</v>
+        <v>138</v>
       </c>
       <c r="F57" t="s">
         <v>7</v>
@@ -1997,10 +1997,10 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B58" t="s">
-        <v>88</v>
+        <v>139</v>
       </c>
       <c r="C58">
         <v>0</v>
@@ -2009,7 +2009,7 @@
         <v>10</v>
       </c>
       <c r="E58" t="s">
-        <v>89</v>
+        <v>141</v>
       </c>
       <c r="F58" t="s">
         <v>7</v>
@@ -2017,19 +2017,19 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B59" t="s">
-        <v>90</v>
+        <v>135</v>
       </c>
       <c r="C59">
         <v>0</v>
       </c>
       <c r="D59">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E59" t="s">
-        <v>91</v>
+        <v>140</v>
       </c>
       <c r="F59" t="s">
         <v>7</v>
@@ -2037,19 +2037,19 @@
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B60" t="s">
-        <v>92</v>
+        <v>124</v>
       </c>
       <c r="C60">
         <v>0</v>
       </c>
       <c r="D60">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="E60" t="s">
-        <v>93</v>
+        <v>125</v>
       </c>
       <c r="F60" t="s">
         <v>7</v>
@@ -2057,19 +2057,19 @@
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B61" t="s">
-        <v>100</v>
+        <v>128</v>
       </c>
       <c r="C61">
         <v>0</v>
       </c>
       <c r="D61">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E61" t="s">
-        <v>101</v>
+        <v>129</v>
       </c>
       <c r="F61" t="s">
         <v>7</v>
@@ -2077,19 +2077,19 @@
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B62" t="s">
-        <v>105</v>
+        <v>117</v>
       </c>
       <c r="C62">
         <v>0</v>
       </c>
       <c r="D62">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="E62" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="F62" t="s">
         <v>7</v>
@@ -2100,16 +2100,16 @@
         <v>102</v>
       </c>
       <c r="B63" t="s">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="C63">
         <v>0</v>
       </c>
       <c r="D63">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E63" t="s">
-        <v>108</v>
+        <v>85</v>
       </c>
       <c r="F63" t="s">
         <v>7</v>
@@ -2120,16 +2120,16 @@
         <v>102</v>
       </c>
       <c r="B64" t="s">
-        <v>126</v>
+        <v>86</v>
       </c>
       <c r="C64">
         <v>0</v>
       </c>
       <c r="D64">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E64" t="s">
-        <v>127</v>
+        <v>87</v>
       </c>
       <c r="F64" t="s">
         <v>7</v>
@@ -2140,16 +2140,16 @@
         <v>102</v>
       </c>
       <c r="B65" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="C65">
         <v>0</v>
       </c>
       <c r="D65">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="E65" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="F65" t="s">
         <v>7</v>
@@ -2160,16 +2160,16 @@
         <v>102</v>
       </c>
       <c r="B66" t="s">
-        <v>142</v>
+        <v>90</v>
       </c>
       <c r="C66">
         <v>0</v>
       </c>
       <c r="D66">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E66" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="F66" t="s">
         <v>7</v>
@@ -2180,16 +2180,16 @@
         <v>102</v>
       </c>
       <c r="B67" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="C67">
         <v>0</v>
       </c>
       <c r="D67">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="E67" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="F67" t="s">
         <v>7</v>
@@ -2200,16 +2200,16 @@
         <v>102</v>
       </c>
       <c r="B68" t="s">
-        <v>149</v>
+        <v>100</v>
       </c>
       <c r="C68">
         <v>0</v>
       </c>
       <c r="D68">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="E68" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="F68" t="s">
         <v>7</v>
@@ -2220,16 +2220,16 @@
         <v>102</v>
       </c>
       <c r="B69" t="s">
-        <v>143</v>
+        <v>105</v>
       </c>
       <c r="C69">
         <v>0</v>
       </c>
       <c r="D69">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="E69" t="s">
-        <v>133</v>
+        <v>107</v>
       </c>
       <c r="F69" t="s">
         <v>7</v>
@@ -2240,16 +2240,16 @@
         <v>102</v>
       </c>
       <c r="B70" t="s">
-        <v>130</v>
+        <v>106</v>
       </c>
       <c r="C70">
         <v>0</v>
       </c>
       <c r="D70">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="E70" t="s">
-        <v>131</v>
+        <v>108</v>
       </c>
       <c r="F70" t="s">
         <v>7</v>
@@ -2260,16 +2260,16 @@
         <v>102</v>
       </c>
       <c r="B71" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="C71">
         <v>0</v>
       </c>
       <c r="D71">
-        <v>85</v>
+        <v>20</v>
       </c>
       <c r="E71" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="F71" t="s">
         <v>7</v>
@@ -2280,16 +2280,16 @@
         <v>102</v>
       </c>
       <c r="B72" t="s">
-        <v>144</v>
+        <v>95</v>
       </c>
       <c r="C72">
         <v>0</v>
       </c>
       <c r="D72">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="E72" t="s">
-        <v>148</v>
+        <v>96</v>
       </c>
       <c r="F72" t="s">
         <v>7</v>
@@ -2300,7 +2300,7 @@
         <v>102</v>
       </c>
       <c r="B73" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C73">
         <v>0</v>
@@ -2309,7 +2309,7 @@
         <v>30</v>
       </c>
       <c r="E73" t="s">
-        <v>147</v>
+        <v>94</v>
       </c>
       <c r="F73" t="s">
         <v>7</v>
@@ -2320,18 +2320,158 @@
         <v>102</v>
       </c>
       <c r="B74" t="s">
+        <v>97</v>
+      </c>
+      <c r="C74">
+        <v>0</v>
+      </c>
+      <c r="D74">
+        <v>35</v>
+      </c>
+      <c r="E74" t="s">
+        <v>98</v>
+      </c>
+      <c r="F74" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A75" t="s">
+        <v>102</v>
+      </c>
+      <c r="B75" t="s">
+        <v>149</v>
+      </c>
+      <c r="C75">
+        <v>0</v>
+      </c>
+      <c r="D75">
+        <v>35</v>
+      </c>
+      <c r="E75" t="s">
+        <v>99</v>
+      </c>
+      <c r="F75" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A76" t="s">
+        <v>102</v>
+      </c>
+      <c r="B76" t="s">
+        <v>143</v>
+      </c>
+      <c r="C76">
+        <v>0</v>
+      </c>
+      <c r="D76">
+        <v>50</v>
+      </c>
+      <c r="E76" t="s">
+        <v>133</v>
+      </c>
+      <c r="F76" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A77" t="s">
+        <v>102</v>
+      </c>
+      <c r="B77" t="s">
+        <v>130</v>
+      </c>
+      <c r="C77">
+        <v>0</v>
+      </c>
+      <c r="D77">
+        <v>60</v>
+      </c>
+      <c r="E77" t="s">
+        <v>131</v>
+      </c>
+      <c r="F77" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A78" t="s">
+        <v>102</v>
+      </c>
+      <c r="B78" t="s">
+        <v>132</v>
+      </c>
+      <c r="C78">
+        <v>0</v>
+      </c>
+      <c r="D78">
+        <v>85</v>
+      </c>
+      <c r="E78" t="s">
+        <v>133</v>
+      </c>
+      <c r="F78" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A79" t="s">
+        <v>102</v>
+      </c>
+      <c r="B79" t="s">
+        <v>144</v>
+      </c>
+      <c r="C79">
+        <v>0</v>
+      </c>
+      <c r="D79">
+        <v>100</v>
+      </c>
+      <c r="E79" t="s">
+        <v>148</v>
+      </c>
+      <c r="F79" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A80" t="s">
+        <v>102</v>
+      </c>
+      <c r="B80" t="s">
+        <v>145</v>
+      </c>
+      <c r="C80">
+        <v>0</v>
+      </c>
+      <c r="D80">
+        <v>30</v>
+      </c>
+      <c r="E80" t="s">
+        <v>147</v>
+      </c>
+      <c r="F80" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A81" t="s">
+        <v>102</v>
+      </c>
+      <c r="B81" t="s">
         <v>146</v>
       </c>
-      <c r="C74">
-        <v>0</v>
-      </c>
-      <c r="D74">
+      <c r="C81">
+        <v>0</v>
+      </c>
+      <c r="D81">
         <v>30</v>
       </c>
-      <c r="E74" t="s">
+      <c r="E81" t="s">
         <v>147</v>
       </c>
-      <c r="F74" t="s">
+      <c r="F81" t="s">
         <v>7</v>
       </c>
     </row>

--- a/DhalisMenu_cat.xlsx
+++ b/DhalisMenu_cat.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\All DATA Important\Projects\New folder\restaurant_billing_app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2FF8A1D-7995-431F-9AF4-E0BD8A7785BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D587A8B-9FD7-4C03-88A0-E090C3D84BDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="163">
   <si>
     <t>Item</t>
   </si>
@@ -475,25 +475,43 @@
     <t>Campa Energy 35Rs</t>
   </si>
   <si>
-    <t>Chill Patato</t>
-  </si>
-  <si>
-    <t>Honey Chill Patato</t>
-  </si>
-  <si>
-    <t>Singapuri Chowmin</t>
-  </si>
-  <si>
-    <t>Chowmin</t>
-  </si>
-  <si>
-    <t>Momos Vegs</t>
-  </si>
-  <si>
-    <t>Momos Paneer</t>
-  </si>
-  <si>
     <t>Spring Roll</t>
+  </si>
+  <si>
+    <t>Chill Potato</t>
+  </si>
+  <si>
+    <t>Honey Chill Potato</t>
+  </si>
+  <si>
+    <t>Momo's Vegs</t>
+  </si>
+  <si>
+    <t>Momo's Paneer</t>
+  </si>
+  <si>
+    <t>Singapore Chowmein</t>
+  </si>
+  <si>
+    <t>Chowmein</t>
+  </si>
+  <si>
+    <t>Chill Potato.jpg</t>
+  </si>
+  <si>
+    <t>Honey Chill Potato.jpg</t>
+  </si>
+  <si>
+    <t>Momo's Vegs.jpg</t>
+  </si>
+  <si>
+    <t>Spring Roll.jpg</t>
+  </si>
+  <si>
+    <t>Chowmin.jpg</t>
+  </si>
+  <si>
+    <t>Singapuri Chowmin.jpg</t>
   </si>
 </sst>
 </file>
@@ -961,7 +979,7 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C5">
         <v>40</v>
@@ -969,6 +987,9 @@
       <c r="D5">
         <v>80</v>
       </c>
+      <c r="E5" t="s">
+        <v>157</v>
+      </c>
       <c r="F5" t="s">
         <v>7</v>
       </c>
@@ -978,7 +999,7 @@
         <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C6">
         <v>50</v>
@@ -986,6 +1007,9 @@
       <c r="D6">
         <v>100</v>
       </c>
+      <c r="E6" t="s">
+        <v>158</v>
+      </c>
       <c r="F6" t="s">
         <v>7</v>
       </c>
@@ -995,7 +1019,7 @@
         <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C7">
         <v>40</v>
@@ -1003,6 +1027,9 @@
       <c r="D7">
         <v>80</v>
       </c>
+      <c r="E7" t="s">
+        <v>161</v>
+      </c>
       <c r="F7" t="s">
         <v>7</v>
       </c>
@@ -1012,7 +1039,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="C8">
         <v>60</v>
@@ -1020,6 +1047,9 @@
       <c r="D8">
         <v>100</v>
       </c>
+      <c r="E8" t="s">
+        <v>162</v>
+      </c>
       <c r="F8" t="s">
         <v>7</v>
       </c>
@@ -1029,7 +1059,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C9">
         <v>30</v>
@@ -1037,6 +1067,9 @@
       <c r="D9">
         <v>50</v>
       </c>
+      <c r="E9" t="s">
+        <v>159</v>
+      </c>
       <c r="F9" t="s">
         <v>7</v>
       </c>
@@ -1046,7 +1079,7 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C10">
         <v>50</v>
@@ -1054,6 +1087,9 @@
       <c r="D10">
         <v>90</v>
       </c>
+      <c r="E10" t="s">
+        <v>159</v>
+      </c>
       <c r="F10" t="s">
         <v>7</v>
       </c>
@@ -1063,7 +1099,7 @@
         <v>7</v>
       </c>
       <c r="B11" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="C11">
         <v>40</v>
@@ -1071,6 +1107,9 @@
       <c r="D11">
         <v>70</v>
       </c>
+      <c r="E11" t="s">
+        <v>160</v>
+      </c>
       <c r="F11" t="s">
         <v>7</v>
       </c>
@@ -1386,7 +1425,7 @@
         <v>0</v>
       </c>
       <c r="D27">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E27" t="s">
         <v>43</v>
@@ -2286,7 +2325,7 @@
         <v>0</v>
       </c>
       <c r="D72">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E72" t="s">
         <v>96</v>
@@ -2386,7 +2425,7 @@
         <v>0</v>
       </c>
       <c r="D77">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="E77" t="s">
         <v>131</v>
@@ -2466,7 +2505,7 @@
         <v>0</v>
       </c>
       <c r="D81">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E81" t="s">
         <v>147</v>

--- a/DhalisMenu_cat.xlsx
+++ b/DhalisMenu_cat.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\All DATA Important\Projects\New folder\restaurant_billing_app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D587A8B-9FD7-4C03-88A0-E090C3D84BDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3408794E-6A44-4310-A586-9F75F1E9DD71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -310,9 +310,6 @@
     <t>Thusmup Can.jpg</t>
   </si>
   <si>
-    <t>Dite Coke 25 rs</t>
-  </si>
-  <si>
     <t>Dite Coke 25 rs.jpg</t>
   </si>
   <si>
@@ -451,9 +448,6 @@
     <t>Act II Pop corn Butter.jpg</t>
   </si>
   <si>
-    <t>Thumsup30</t>
-  </si>
-  <si>
     <t>One Liter Bottel Cold Drink</t>
   </si>
   <si>
@@ -472,9 +466,6 @@
     <t>Frooti Big Bottel Cold Drink.jpeg</t>
   </si>
   <si>
-    <t>Campa Energy 35Rs</t>
-  </si>
-  <si>
     <t>Spring Roll</t>
   </si>
   <si>
@@ -487,9 +478,6 @@
     <t>Momo's Vegs</t>
   </si>
   <si>
-    <t>Momo's Paneer</t>
-  </si>
-  <si>
     <t>Singapore Chowmein</t>
   </si>
   <si>
@@ -512,6 +500,18 @@
   </si>
   <si>
     <t>Singapuri Chowmin.jpg</t>
+  </si>
+  <si>
+    <t>Momo's Fry's</t>
+  </si>
+  <si>
+    <t>Dite Coke  Can 30 rs</t>
+  </si>
+  <si>
+    <t>Thumsup Can 30 rs</t>
+  </si>
+  <si>
+    <t>Campa Energy Can 35Rs</t>
   </si>
 </sst>
 </file>
@@ -979,7 +979,7 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="C5">
         <v>40</v>
@@ -988,7 +988,7 @@
         <v>80</v>
       </c>
       <c r="E5" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="F5" t="s">
         <v>7</v>
@@ -999,7 +999,7 @@
         <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="C6">
         <v>50</v>
@@ -1008,7 +1008,7 @@
         <v>100</v>
       </c>
       <c r="E6" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="F6" t="s">
         <v>7</v>
@@ -1019,7 +1019,7 @@
         <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="C7">
         <v>40</v>
@@ -1028,7 +1028,7 @@
         <v>80</v>
       </c>
       <c r="E7" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="F7" t="s">
         <v>7</v>
@@ -1039,7 +1039,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C8">
         <v>60</v>
@@ -1048,7 +1048,7 @@
         <v>100</v>
       </c>
       <c r="E8" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="F8" t="s">
         <v>7</v>
@@ -1059,16 +1059,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="C9">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="D9">
-        <v>50</v>
+        <v>80</v>
       </c>
       <c r="E9" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="F9" t="s">
         <v>7</v>
@@ -1079,16 +1079,16 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="C10">
         <v>50</v>
       </c>
       <c r="D10">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="E10" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="F10" t="s">
         <v>7</v>
@@ -1099,16 +1099,16 @@
         <v>7</v>
       </c>
       <c r="B11" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="C11">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="D11">
-        <v>70</v>
+        <v>120</v>
       </c>
       <c r="E11" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="F11" t="s">
         <v>7</v>
@@ -1456,7 +1456,7 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B29" t="s">
         <v>46</v>
@@ -1476,7 +1476,7 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B30" t="s">
         <v>48</v>
@@ -1496,7 +1496,7 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B31" t="s">
         <v>50</v>
@@ -1516,7 +1516,7 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B32" t="s">
         <v>52</v>
@@ -1536,7 +1536,7 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B33" t="s">
         <v>54</v>
@@ -1556,7 +1556,7 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B34" t="s">
         <v>56</v>
@@ -1576,7 +1576,7 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B35" t="s">
         <v>57</v>
@@ -1596,7 +1596,7 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B36" t="s">
         <v>58</v>
@@ -1616,7 +1616,7 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B37" t="s">
         <v>59</v>
@@ -1636,7 +1636,7 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B38" t="s">
         <v>61</v>
@@ -1656,7 +1656,7 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B39" t="s">
         <v>63</v>
@@ -1676,7 +1676,7 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B40" t="s">
         <v>65</v>
@@ -1696,7 +1696,7 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B41" t="s">
         <v>67</v>
@@ -1716,7 +1716,7 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B42" t="s">
         <v>69</v>
@@ -1736,7 +1736,7 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B43" t="s">
         <v>71</v>
@@ -1756,7 +1756,7 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B44" t="s">
         <v>73</v>
@@ -1776,7 +1776,7 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B45" t="s">
         <v>75</v>
@@ -1796,7 +1796,7 @@
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B46" t="s">
         <v>77</v>
@@ -1816,10 +1816,10 @@
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B47" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C47">
         <v>0</v>
@@ -1836,10 +1836,10 @@
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B48" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C48">
         <v>0</v>
@@ -1848,7 +1848,7 @@
         <v>45</v>
       </c>
       <c r="E48" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F48" t="s">
         <v>7</v>
@@ -1856,7 +1856,7 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B49" t="s">
         <v>80</v>
@@ -1876,7 +1876,7 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B50" t="s">
         <v>82</v>
@@ -1896,10 +1896,10 @@
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B51" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C51">
         <v>0</v>
@@ -1908,7 +1908,7 @@
         <v>53</v>
       </c>
       <c r="E51" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F51" t="s">
         <v>7</v>
@@ -1916,10 +1916,10 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B52" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C52">
         <v>0</v>
@@ -1928,7 +1928,7 @@
         <v>62</v>
       </c>
       <c r="E52" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F52" t="s">
         <v>7</v>
@@ -1936,10 +1936,10 @@
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B53" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C53">
         <v>0</v>
@@ -1948,7 +1948,7 @@
         <v>52</v>
       </c>
       <c r="E53" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F53" t="s">
         <v>7</v>
@@ -1956,10 +1956,10 @@
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B54" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C54">
         <v>0</v>
@@ -1968,7 +1968,7 @@
         <v>52</v>
       </c>
       <c r="E54" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="F54" t="s">
         <v>7</v>
@@ -1976,10 +1976,10 @@
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B55" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C55">
         <v>0</v>
@@ -1988,7 +1988,7 @@
         <v>57</v>
       </c>
       <c r="E55" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F55" t="s">
         <v>7</v>
@@ -1996,10 +1996,10 @@
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B56" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C56">
         <v>0</v>
@@ -2008,7 +2008,7 @@
         <v>25</v>
       </c>
       <c r="E56" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F56" t="s">
         <v>7</v>
@@ -2016,10 +2016,10 @@
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B57" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C57">
         <v>0</v>
@@ -2028,7 +2028,7 @@
         <v>10</v>
       </c>
       <c r="E57" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F57" t="s">
         <v>7</v>
@@ -2036,10 +2036,10 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B58" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C58">
         <v>0</v>
@@ -2048,7 +2048,7 @@
         <v>10</v>
       </c>
       <c r="E58" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F58" t="s">
         <v>7</v>
@@ -2056,10 +2056,10 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B59" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C59">
         <v>0</v>
@@ -2068,7 +2068,7 @@
         <v>5</v>
       </c>
       <c r="E59" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F59" t="s">
         <v>7</v>
@@ -2076,10 +2076,10 @@
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B60" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C60">
         <v>0</v>
@@ -2088,7 +2088,7 @@
         <v>25</v>
       </c>
       <c r="E60" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="F60" t="s">
         <v>7</v>
@@ -2096,10 +2096,10 @@
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B61" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C61">
         <v>0</v>
@@ -2108,7 +2108,7 @@
         <v>10</v>
       </c>
       <c r="E61" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F61" t="s">
         <v>7</v>
@@ -2116,10 +2116,10 @@
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B62" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C62">
         <v>0</v>
@@ -2128,7 +2128,7 @@
         <v>1</v>
       </c>
       <c r="E62" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F62" t="s">
         <v>7</v>
@@ -2136,7 +2136,7 @@
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B63" t="s">
         <v>84</v>
@@ -2156,7 +2156,7 @@
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B64" t="s">
         <v>86</v>
@@ -2176,7 +2176,7 @@
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B65" t="s">
         <v>88</v>
@@ -2196,7 +2196,7 @@
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B66" t="s">
         <v>90</v>
@@ -2216,7 +2216,7 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B67" t="s">
         <v>92</v>
@@ -2236,10 +2236,10 @@
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B68" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C68">
         <v>0</v>
@@ -2248,7 +2248,7 @@
         <v>20</v>
       </c>
       <c r="E68" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F68" t="s">
         <v>7</v>
@@ -2256,10 +2256,10 @@
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B69" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C69">
         <v>0</v>
@@ -2268,7 +2268,7 @@
         <v>20</v>
       </c>
       <c r="E69" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F69" t="s">
         <v>7</v>
@@ -2276,10 +2276,10 @@
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B70" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C70">
         <v>0</v>
@@ -2288,7 +2288,7 @@
         <v>20</v>
       </c>
       <c r="E70" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F70" t="s">
         <v>7</v>
@@ -2296,10 +2296,10 @@
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B71" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C71">
         <v>0</v>
@@ -2308,7 +2308,7 @@
         <v>20</v>
       </c>
       <c r="E71" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="F71" t="s">
         <v>7</v>
@@ -2316,10 +2316,10 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B72" t="s">
-        <v>95</v>
+        <v>160</v>
       </c>
       <c r="C72">
         <v>0</v>
@@ -2328,7 +2328,7 @@
         <v>30</v>
       </c>
       <c r="E72" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F72" t="s">
         <v>7</v>
@@ -2336,10 +2336,10 @@
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B73" t="s">
-        <v>142</v>
+        <v>161</v>
       </c>
       <c r="C73">
         <v>0</v>
@@ -2356,10 +2356,10 @@
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B74" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C74">
         <v>0</v>
@@ -2368,7 +2368,7 @@
         <v>35</v>
       </c>
       <c r="E74" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F74" t="s">
         <v>7</v>
@@ -2376,10 +2376,10 @@
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B75" t="s">
-        <v>149</v>
+        <v>162</v>
       </c>
       <c r="C75">
         <v>0</v>
@@ -2388,7 +2388,7 @@
         <v>35</v>
       </c>
       <c r="E75" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F75" t="s">
         <v>7</v>
@@ -2396,10 +2396,10 @@
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B76" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C76">
         <v>0</v>
@@ -2408,7 +2408,7 @@
         <v>50</v>
       </c>
       <c r="E76" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F76" t="s">
         <v>7</v>
@@ -2416,10 +2416,10 @@
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B77" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C77">
         <v>0</v>
@@ -2428,7 +2428,7 @@
         <v>65</v>
       </c>
       <c r="E77" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F77" t="s">
         <v>7</v>
@@ -2436,10 +2436,10 @@
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B78" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C78">
         <v>0</v>
@@ -2448,7 +2448,7 @@
         <v>85</v>
       </c>
       <c r="E78" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="F78" t="s">
         <v>7</v>
@@ -2456,10 +2456,10 @@
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B79" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C79">
         <v>0</v>
@@ -2468,7 +2468,7 @@
         <v>100</v>
       </c>
       <c r="E79" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="F79" t="s">
         <v>7</v>
@@ -2476,10 +2476,10 @@
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B80" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C80">
         <v>0</v>
@@ -2488,7 +2488,7 @@
         <v>30</v>
       </c>
       <c r="E80" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="F80" t="s">
         <v>7</v>
@@ -2496,10 +2496,10 @@
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B81" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C81">
         <v>0</v>
@@ -2508,7 +2508,7 @@
         <v>20</v>
       </c>
       <c r="E81" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="F81" t="s">
         <v>7</v>

--- a/DhalisMenu_cat.xlsx
+++ b/DhalisMenu_cat.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\All DATA Important\Projects\New folder\restaurant_billing_app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3408794E-6A44-4310-A586-9F75F1E9DD71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B1CEC95-CC79-400E-8907-0CA66547B3DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="164">
   <si>
     <t>Item</t>
   </si>
@@ -502,9 +502,6 @@
     <t>Singapuri Chowmin.jpg</t>
   </si>
   <si>
-    <t>Momo's Fry's</t>
-  </si>
-  <si>
     <t>Dite Coke  Can 30 rs</t>
   </si>
   <si>
@@ -512,6 +509,12 @@
   </si>
   <si>
     <t>Campa Energy Can 35Rs</t>
+  </si>
+  <si>
+    <t>Momo's Veg  Fry's</t>
+  </si>
+  <si>
+    <t>Momo's Veg  Fry's.jpg</t>
   </si>
 </sst>
 </file>
@@ -1079,7 +1082,7 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="C10">
         <v>50</v>
@@ -1088,7 +1091,7 @@
         <v>100</v>
       </c>
       <c r="E10" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="F10" t="s">
         <v>7</v>
@@ -2319,7 +2322,7 @@
         <v>101</v>
       </c>
       <c r="B72" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C72">
         <v>0</v>
@@ -2339,7 +2342,7 @@
         <v>101</v>
       </c>
       <c r="B73" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C73">
         <v>0</v>
@@ -2379,7 +2382,7 @@
         <v>101</v>
       </c>
       <c r="B75" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C75">
         <v>0</v>

--- a/DhalisMenu_cat.xlsx
+++ b/DhalisMenu_cat.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\All DATA Important\Projects\New folder\restaurant_billing_app\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B1CEC95-CC79-400E-8907-0CA66547B3DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FD52F7A-0018-4FE5-9AF9-2816798BF9AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1105,10 +1105,10 @@
         <v>147</v>
       </c>
       <c r="C11">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="D11">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="E11" t="s">
         <v>156</v>

--- a/DhalisMenu_cat.xlsx
+++ b/DhalisMenu_cat.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\All DATA Important\Projects\New folder\restaurant_billing_app\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Documents\Custom Office Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FD52F7A-0018-4FE5-9AF9-2816798BF9AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66974879-192E-43EC-872D-38D728E46FDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$68</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$69</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="166">
   <si>
     <t>Item</t>
   </si>
@@ -515,6 +515,12 @@
   </si>
   <si>
     <t>Momo's Veg  Fry's.jpg</t>
+  </si>
+  <si>
+    <t>Chowmein &amp; Momos &amp; Chilly Patato</t>
+  </si>
+  <si>
+    <t>Chowmine And Cilly.jpg</t>
   </si>
 </sst>
 </file>
@@ -887,7 +893,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F81"/>
+  <dimension ref="A1:F82"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="8.81640625" bestFit="1" customWidth="1"/>
@@ -1022,16 +1028,16 @@
         <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>152</v>
+        <v>164</v>
       </c>
       <c r="C7">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="D7">
-        <v>80</v>
+        <v>30</v>
       </c>
       <c r="E7" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="F7" t="s">
         <v>7</v>
@@ -1042,16 +1048,16 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C8">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="D8">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="E8" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F8" t="s">
         <v>7</v>
@@ -1062,16 +1068,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C9">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="D9">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="E9" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="F9" t="s">
         <v>7</v>
@@ -1082,16 +1088,16 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>162</v>
+        <v>150</v>
       </c>
       <c r="C10">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="D10">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="E10" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="F10" t="s">
         <v>7</v>
@@ -1102,16 +1108,16 @@
         <v>7</v>
       </c>
       <c r="B11" t="s">
-        <v>147</v>
+        <v>162</v>
       </c>
       <c r="C11">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="D11">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="E11" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="F11" t="s">
         <v>7</v>
@@ -1122,16 +1128,16 @@
         <v>7</v>
       </c>
       <c r="B12" t="s">
-        <v>12</v>
+        <v>147</v>
       </c>
       <c r="C12">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="D12">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="E12" t="s">
-        <v>13</v>
+        <v>156</v>
       </c>
       <c r="F12" t="s">
         <v>7</v>
@@ -1142,7 +1148,7 @@
         <v>7</v>
       </c>
       <c r="B13" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C13">
         <v>0</v>
@@ -1151,7 +1157,7 @@
         <v>90</v>
       </c>
       <c r="E13" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F13" t="s">
         <v>7</v>
@@ -1162,7 +1168,7 @@
         <v>7</v>
       </c>
       <c r="B14" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C14">
         <v>0</v>
@@ -1171,7 +1177,7 @@
         <v>90</v>
       </c>
       <c r="E14" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F14" t="s">
         <v>7</v>
@@ -1182,7 +1188,7 @@
         <v>7</v>
       </c>
       <c r="B15" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C15">
         <v>0</v>
@@ -1191,7 +1197,7 @@
         <v>90</v>
       </c>
       <c r="E15" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F15" t="s">
         <v>7</v>
@@ -1202,7 +1208,7 @@
         <v>7</v>
       </c>
       <c r="B16" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C16">
         <v>0</v>
@@ -1211,7 +1217,7 @@
         <v>90</v>
       </c>
       <c r="E16" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F16" t="s">
         <v>7</v>
@@ -1222,16 +1228,16 @@
         <v>7</v>
       </c>
       <c r="B17" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C17">
         <v>0</v>
       </c>
       <c r="D17">
-        <v>350</v>
+        <v>90</v>
       </c>
       <c r="E17" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F17" t="s">
         <v>7</v>
@@ -1242,16 +1248,16 @@
         <v>7</v>
       </c>
       <c r="B18" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C18">
         <v>0</v>
       </c>
       <c r="D18">
-        <v>150</v>
+        <v>350</v>
       </c>
       <c r="E18" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F18" t="s">
         <v>7</v>
@@ -1262,7 +1268,7 @@
         <v>7</v>
       </c>
       <c r="B19" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C19">
         <v>0</v>
@@ -1271,7 +1277,7 @@
         <v>150</v>
       </c>
       <c r="E19" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F19" t="s">
         <v>7</v>
@@ -1282,16 +1288,16 @@
         <v>7</v>
       </c>
       <c r="B20" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C20">
         <v>0</v>
       </c>
       <c r="D20">
-        <v>175</v>
+        <v>150</v>
       </c>
       <c r="E20" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F20" t="s">
         <v>7</v>
@@ -1302,16 +1308,16 @@
         <v>7</v>
       </c>
       <c r="B21" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C21">
         <v>0</v>
       </c>
       <c r="D21">
-        <v>200</v>
+        <v>175</v>
       </c>
       <c r="E21" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F21" t="s">
         <v>7</v>
@@ -1322,16 +1328,16 @@
         <v>7</v>
       </c>
       <c r="B22" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C22">
         <v>0</v>
       </c>
       <c r="D22">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="E22" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F22" t="s">
         <v>7</v>
@@ -1342,7 +1348,7 @@
         <v>7</v>
       </c>
       <c r="B23" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C23">
         <v>0</v>
@@ -1351,7 +1357,7 @@
         <v>100</v>
       </c>
       <c r="E23" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F23" t="s">
         <v>7</v>
@@ -1362,16 +1368,16 @@
         <v>7</v>
       </c>
       <c r="B24" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C24">
         <v>0</v>
       </c>
       <c r="D24">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="E24" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F24" t="s">
         <v>7</v>
@@ -1382,16 +1388,16 @@
         <v>7</v>
       </c>
       <c r="B25" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C25">
         <v>0</v>
       </c>
       <c r="D25">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="E25" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F25" t="s">
         <v>7</v>
@@ -1402,16 +1408,16 @@
         <v>7</v>
       </c>
       <c r="B26" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C26">
         <v>0</v>
       </c>
       <c r="D26">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="E26" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F26" t="s">
         <v>7</v>
@@ -1422,16 +1428,16 @@
         <v>7</v>
       </c>
       <c r="B27" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C27">
         <v>0</v>
       </c>
       <c r="D27">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="E27" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F27" t="s">
         <v>7</v>
@@ -1442,16 +1448,16 @@
         <v>7</v>
       </c>
       <c r="B28" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C28">
         <v>0</v>
       </c>
       <c r="D28">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E28" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F28" t="s">
         <v>7</v>
@@ -1459,19 +1465,19 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>102</v>
+        <v>7</v>
       </c>
       <c r="B29" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C29">
         <v>0</v>
       </c>
       <c r="D29">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E29" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F29" t="s">
         <v>7</v>
@@ -1482,16 +1488,16 @@
         <v>102</v>
       </c>
       <c r="B30" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C30">
         <v>0</v>
       </c>
       <c r="D30">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="E30" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F30" t="s">
         <v>7</v>
@@ -1502,16 +1508,16 @@
         <v>102</v>
       </c>
       <c r="B31" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C31">
         <v>0</v>
       </c>
       <c r="D31">
-        <v>650</v>
+        <v>40</v>
       </c>
       <c r="E31" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="F31" t="s">
         <v>7</v>
@@ -1522,16 +1528,16 @@
         <v>102</v>
       </c>
       <c r="B32" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C32">
         <v>0</v>
       </c>
       <c r="D32">
-        <v>550</v>
+        <v>650</v>
       </c>
       <c r="E32" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="F32" t="s">
         <v>7</v>
@@ -1542,16 +1548,16 @@
         <v>102</v>
       </c>
       <c r="B33" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C33">
         <v>0</v>
       </c>
       <c r="D33">
-        <v>600</v>
+        <v>550</v>
       </c>
       <c r="E33" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F33" t="s">
         <v>7</v>
@@ -1562,16 +1568,16 @@
         <v>102</v>
       </c>
       <c r="B34" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C34">
         <v>0</v>
       </c>
       <c r="D34">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="E34" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F34" t="s">
         <v>7</v>
@@ -1582,16 +1588,16 @@
         <v>102</v>
       </c>
       <c r="B35" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C35">
         <v>0</v>
       </c>
       <c r="D35">
-        <v>550</v>
+        <v>300</v>
       </c>
       <c r="E35" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F35" t="s">
         <v>7</v>
@@ -1602,16 +1608,16 @@
         <v>102</v>
       </c>
       <c r="B36" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C36">
         <v>0</v>
       </c>
       <c r="D36">
-        <v>500</v>
+        <v>550</v>
       </c>
       <c r="E36" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="F36" t="s">
         <v>7</v>
@@ -1619,19 +1625,19 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B37" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C37">
         <v>0</v>
       </c>
       <c r="D37">
-        <v>5</v>
+        <v>500</v>
       </c>
       <c r="E37" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="F37" t="s">
         <v>7</v>
@@ -1642,16 +1648,16 @@
         <v>103</v>
       </c>
       <c r="B38" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C38">
         <v>0</v>
       </c>
       <c r="D38">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E38" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F38" t="s">
         <v>7</v>
@@ -1662,16 +1668,16 @@
         <v>103</v>
       </c>
       <c r="B39" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C39">
         <v>0</v>
       </c>
       <c r="D39">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E39" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="F39" t="s">
         <v>7</v>
@@ -1682,16 +1688,16 @@
         <v>103</v>
       </c>
       <c r="B40" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C40">
         <v>0</v>
       </c>
       <c r="D40">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E40" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="F40" t="s">
         <v>7</v>
@@ -1702,16 +1708,16 @@
         <v>103</v>
       </c>
       <c r="B41" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C41">
         <v>0</v>
       </c>
       <c r="D41">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E41" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="F41" t="s">
         <v>7</v>
@@ -1722,16 +1728,16 @@
         <v>103</v>
       </c>
       <c r="B42" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C42">
         <v>0</v>
       </c>
       <c r="D42">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E42" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F42" t="s">
         <v>7</v>
@@ -1742,16 +1748,16 @@
         <v>103</v>
       </c>
       <c r="B43" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C43">
         <v>0</v>
       </c>
       <c r="D43">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E43" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F43" t="s">
         <v>7</v>
@@ -1762,7 +1768,7 @@
         <v>103</v>
       </c>
       <c r="B44" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C44">
         <v>0</v>
@@ -1771,7 +1777,7 @@
         <v>10</v>
       </c>
       <c r="E44" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F44" t="s">
         <v>7</v>
@@ -1782,16 +1788,16 @@
         <v>103</v>
       </c>
       <c r="B45" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C45">
         <v>0</v>
       </c>
       <c r="D45">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="E45" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F45" t="s">
         <v>7</v>
@@ -1802,16 +1808,16 @@
         <v>103</v>
       </c>
       <c r="B46" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C46">
         <v>0</v>
       </c>
       <c r="D46">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="E46" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F46" t="s">
         <v>7</v>
@@ -1822,16 +1828,16 @@
         <v>103</v>
       </c>
       <c r="B47" t="s">
-        <v>119</v>
+        <v>77</v>
       </c>
       <c r="C47">
         <v>0</v>
       </c>
       <c r="D47">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E47" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F47" t="s">
         <v>7</v>
@@ -1842,16 +1848,16 @@
         <v>103</v>
       </c>
       <c r="B48" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C48">
         <v>0</v>
       </c>
       <c r="D48">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="E48" t="s">
-        <v>120</v>
+        <v>79</v>
       </c>
       <c r="F48" t="s">
         <v>7</v>
@@ -1862,16 +1868,16 @@
         <v>103</v>
       </c>
       <c r="B49" t="s">
-        <v>80</v>
+        <v>118</v>
       </c>
       <c r="C49">
         <v>0</v>
       </c>
       <c r="D49">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="E49" t="s">
-        <v>81</v>
+        <v>120</v>
       </c>
       <c r="F49" t="s">
         <v>7</v>
@@ -1882,16 +1888,16 @@
         <v>103</v>
       </c>
       <c r="B50" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C50">
         <v>0</v>
       </c>
       <c r="D50">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="E50" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="F50" t="s">
         <v>7</v>
@@ -1902,16 +1908,16 @@
         <v>103</v>
       </c>
       <c r="B51" t="s">
-        <v>109</v>
+        <v>82</v>
       </c>
       <c r="C51">
         <v>0</v>
       </c>
       <c r="D51">
-        <v>53</v>
+        <v>10</v>
       </c>
       <c r="E51" t="s">
-        <v>108</v>
+        <v>83</v>
       </c>
       <c r="F51" t="s">
         <v>7</v>
@@ -1922,16 +1928,16 @@
         <v>103</v>
       </c>
       <c r="B52" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C52">
         <v>0</v>
       </c>
       <c r="D52">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="E52" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="F52" t="s">
         <v>7</v>
@@ -1942,16 +1948,16 @@
         <v>103</v>
       </c>
       <c r="B53" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C53">
         <v>0</v>
       </c>
       <c r="D53">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="E53" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="F53" t="s">
         <v>7</v>
@@ -1962,7 +1968,7 @@
         <v>103</v>
       </c>
       <c r="B54" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C54">
         <v>0</v>
@@ -1971,7 +1977,7 @@
         <v>52</v>
       </c>
       <c r="E54" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="F54" t="s">
         <v>7</v>
@@ -1982,16 +1988,16 @@
         <v>103</v>
       </c>
       <c r="B55" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="C55">
         <v>0</v>
       </c>
       <c r="D55">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="E55" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="F55" t="s">
         <v>7</v>
@@ -2002,16 +2008,16 @@
         <v>103</v>
       </c>
       <c r="B56" t="s">
-        <v>135</v>
+        <v>121</v>
       </c>
       <c r="C56">
         <v>0</v>
       </c>
       <c r="D56">
-        <v>25</v>
+        <v>57</v>
       </c>
       <c r="E56" t="s">
-        <v>136</v>
+        <v>122</v>
       </c>
       <c r="F56" t="s">
         <v>7</v>
@@ -2022,16 +2028,16 @@
         <v>103</v>
       </c>
       <c r="B57" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C57">
         <v>0</v>
       </c>
       <c r="D57">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="E57" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F57" t="s">
         <v>7</v>
@@ -2042,7 +2048,7 @@
         <v>103</v>
       </c>
       <c r="B58" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="C58">
         <v>0</v>
@@ -2051,7 +2057,7 @@
         <v>10</v>
       </c>
       <c r="E58" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="F58" t="s">
         <v>7</v>
@@ -2062,16 +2068,16 @@
         <v>103</v>
       </c>
       <c r="B59" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="C59">
         <v>0</v>
       </c>
       <c r="D59">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E59" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F59" t="s">
         <v>7</v>
@@ -2082,16 +2088,16 @@
         <v>103</v>
       </c>
       <c r="B60" t="s">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="C60">
         <v>0</v>
       </c>
       <c r="D60">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E60" t="s">
-        <v>124</v>
+        <v>139</v>
       </c>
       <c r="F60" t="s">
         <v>7</v>
@@ -2102,16 +2108,16 @@
         <v>103</v>
       </c>
       <c r="B61" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="C61">
         <v>0</v>
       </c>
       <c r="D61">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="E61" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="F61" t="s">
         <v>7</v>
@@ -2122,16 +2128,16 @@
         <v>103</v>
       </c>
       <c r="B62" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="C62">
         <v>0</v>
       </c>
       <c r="D62">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E62" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="F62" t="s">
         <v>7</v>
@@ -2139,19 +2145,19 @@
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B63" t="s">
-        <v>84</v>
+        <v>116</v>
       </c>
       <c r="C63">
         <v>0</v>
       </c>
       <c r="D63">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E63" t="s">
-        <v>85</v>
+        <v>117</v>
       </c>
       <c r="F63" t="s">
         <v>7</v>
@@ -2162,7 +2168,7 @@
         <v>101</v>
       </c>
       <c r="B64" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C64">
         <v>0</v>
@@ -2171,7 +2177,7 @@
         <v>10</v>
       </c>
       <c r="E64" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="F64" t="s">
         <v>7</v>
@@ -2182,7 +2188,7 @@
         <v>101</v>
       </c>
       <c r="B65" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C65">
         <v>0</v>
@@ -2191,7 +2197,7 @@
         <v>10</v>
       </c>
       <c r="E65" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F65" t="s">
         <v>7</v>
@@ -2202,16 +2208,16 @@
         <v>101</v>
       </c>
       <c r="B66" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C66">
         <v>0</v>
       </c>
       <c r="D66">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E66" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="F66" t="s">
         <v>7</v>
@@ -2222,7 +2228,7 @@
         <v>101</v>
       </c>
       <c r="B67" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C67">
         <v>0</v>
@@ -2231,7 +2237,7 @@
         <v>20</v>
       </c>
       <c r="E67" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F67" t="s">
         <v>7</v>
@@ -2242,7 +2248,7 @@
         <v>101</v>
       </c>
       <c r="B68" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="C68">
         <v>0</v>
@@ -2251,7 +2257,7 @@
         <v>20</v>
       </c>
       <c r="E68" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="F68" t="s">
         <v>7</v>
@@ -2262,7 +2268,7 @@
         <v>101</v>
       </c>
       <c r="B69" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="C69">
         <v>0</v>
@@ -2271,7 +2277,7 @@
         <v>20</v>
       </c>
       <c r="E69" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="F69" t="s">
         <v>7</v>
@@ -2282,7 +2288,7 @@
         <v>101</v>
       </c>
       <c r="B70" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C70">
         <v>0</v>
@@ -2291,7 +2297,7 @@
         <v>20</v>
       </c>
       <c r="E70" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F70" t="s">
         <v>7</v>
@@ -2302,7 +2308,7 @@
         <v>101</v>
       </c>
       <c r="B71" t="s">
-        <v>125</v>
+        <v>105</v>
       </c>
       <c r="C71">
         <v>0</v>
@@ -2311,7 +2317,7 @@
         <v>20</v>
       </c>
       <c r="E71" t="s">
-        <v>126</v>
+        <v>107</v>
       </c>
       <c r="F71" t="s">
         <v>7</v>
@@ -2322,16 +2328,16 @@
         <v>101</v>
       </c>
       <c r="B72" t="s">
-        <v>159</v>
+        <v>125</v>
       </c>
       <c r="C72">
         <v>0</v>
       </c>
       <c r="D72">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E72" t="s">
-        <v>95</v>
+        <v>126</v>
       </c>
       <c r="F72" t="s">
         <v>7</v>
@@ -2342,7 +2348,7 @@
         <v>101</v>
       </c>
       <c r="B73" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C73">
         <v>0</v>
@@ -2351,7 +2357,7 @@
         <v>30</v>
       </c>
       <c r="E73" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F73" t="s">
         <v>7</v>
@@ -2362,16 +2368,16 @@
         <v>101</v>
       </c>
       <c r="B74" t="s">
-        <v>96</v>
+        <v>160</v>
       </c>
       <c r="C74">
         <v>0</v>
       </c>
       <c r="D74">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="E74" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="F74" t="s">
         <v>7</v>
@@ -2382,7 +2388,7 @@
         <v>101</v>
       </c>
       <c r="B75" t="s">
-        <v>161</v>
+        <v>96</v>
       </c>
       <c r="C75">
         <v>0</v>
@@ -2391,7 +2397,7 @@
         <v>35</v>
       </c>
       <c r="E75" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F75" t="s">
         <v>7</v>
@@ -2402,16 +2408,16 @@
         <v>101</v>
       </c>
       <c r="B76" t="s">
-        <v>141</v>
+        <v>161</v>
       </c>
       <c r="C76">
         <v>0</v>
       </c>
       <c r="D76">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="E76" t="s">
-        <v>132</v>
+        <v>98</v>
       </c>
       <c r="F76" t="s">
         <v>7</v>
@@ -2422,16 +2428,16 @@
         <v>101</v>
       </c>
       <c r="B77" t="s">
-        <v>129</v>
+        <v>141</v>
       </c>
       <c r="C77">
         <v>0</v>
       </c>
       <c r="D77">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="E77" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="F77" t="s">
         <v>7</v>
@@ -2442,16 +2448,16 @@
         <v>101</v>
       </c>
       <c r="B78" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C78">
         <v>0</v>
       </c>
       <c r="D78">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="E78" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="F78" t="s">
         <v>7</v>
@@ -2462,16 +2468,16 @@
         <v>101</v>
       </c>
       <c r="B79" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="C79">
         <v>0</v>
       </c>
       <c r="D79">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="E79" t="s">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="F79" t="s">
         <v>7</v>
@@ -2482,16 +2488,16 @@
         <v>101</v>
       </c>
       <c r="B80" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C80">
         <v>0</v>
       </c>
       <c r="D80">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="E80" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F80" t="s">
         <v>7</v>
@@ -2502,18 +2508,38 @@
         <v>101</v>
       </c>
       <c r="B81" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C81">
         <v>0</v>
       </c>
       <c r="D81">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="E81" t="s">
         <v>145</v>
       </c>
       <c r="F81" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A82" t="s">
+        <v>101</v>
+      </c>
+      <c r="B82" t="s">
+        <v>144</v>
+      </c>
+      <c r="C82">
+        <v>0</v>
+      </c>
+      <c r="D82">
+        <v>20</v>
+      </c>
+      <c r="E82" t="s">
+        <v>145</v>
+      </c>
+      <c r="F82" t="s">
         <v>7</v>
       </c>
     </row>

--- a/DhalisMenu_cat.xlsx
+++ b/DhalisMenu_cat.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Documents\Custom Office Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66974879-192E-43EC-872D-38D728E46FDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DC779B3-EB51-455B-8EC8-B3B94DBB9705}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$69</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$71</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="170">
   <si>
     <t>Item</t>
   </si>
@@ -517,10 +517,22 @@
     <t>Momo's Veg  Fry's.jpg</t>
   </si>
   <si>
-    <t>Chowmein &amp; Momos &amp; Chilly Patato</t>
-  </si>
-  <si>
     <t>Chowmine And Cilly.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20 RS/30rs Chowmein &amp; Momos &amp; Chilly Patato </t>
+  </si>
+  <si>
+    <t>Veg Man churiyan Dry</t>
+  </si>
+  <si>
+    <t>Veg Man churiyan Gravy</t>
+  </si>
+  <si>
+    <t>Veg Man churiyan Dry.jpg</t>
+  </si>
+  <si>
+    <t>Veg Man churiyan Gravy.jpg</t>
   </si>
 </sst>
 </file>
@@ -893,7 +905,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F82"/>
+  <dimension ref="A1:F84"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="8.81640625" bestFit="1" customWidth="1"/>
@@ -1028,7 +1040,7 @@
         <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C7">
         <v>20</v>
@@ -1037,7 +1049,7 @@
         <v>30</v>
       </c>
       <c r="E7" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F7" t="s">
         <v>7</v>
@@ -1148,16 +1160,16 @@
         <v>7</v>
       </c>
       <c r="B13" t="s">
-        <v>12</v>
+        <v>166</v>
       </c>
       <c r="C13">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="D13">
-        <v>90</v>
+        <v>160</v>
       </c>
       <c r="E13" t="s">
-        <v>13</v>
+        <v>168</v>
       </c>
       <c r="F13" t="s">
         <v>7</v>
@@ -1168,16 +1180,16 @@
         <v>7</v>
       </c>
       <c r="B14" t="s">
-        <v>14</v>
+        <v>167</v>
       </c>
       <c r="C14">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="D14">
-        <v>90</v>
+        <v>175</v>
       </c>
       <c r="E14" t="s">
-        <v>15</v>
+        <v>169</v>
       </c>
       <c r="F14" t="s">
         <v>7</v>
@@ -1188,7 +1200,7 @@
         <v>7</v>
       </c>
       <c r="B15" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C15">
         <v>0</v>
@@ -1197,7 +1209,7 @@
         <v>90</v>
       </c>
       <c r="E15" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="F15" t="s">
         <v>7</v>
@@ -1208,7 +1220,7 @@
         <v>7</v>
       </c>
       <c r="B16" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C16">
         <v>0</v>
@@ -1217,7 +1229,7 @@
         <v>90</v>
       </c>
       <c r="E16" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F16" t="s">
         <v>7</v>
@@ -1228,7 +1240,7 @@
         <v>7</v>
       </c>
       <c r="B17" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C17">
         <v>0</v>
@@ -1237,7 +1249,7 @@
         <v>90</v>
       </c>
       <c r="E17" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="F17" t="s">
         <v>7</v>
@@ -1248,16 +1260,16 @@
         <v>7</v>
       </c>
       <c r="B18" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C18">
         <v>0</v>
       </c>
       <c r="D18">
-        <v>350</v>
+        <v>90</v>
       </c>
       <c r="E18" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F18" t="s">
         <v>7</v>
@@ -1268,16 +1280,16 @@
         <v>7</v>
       </c>
       <c r="B19" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C19">
         <v>0</v>
       </c>
       <c r="D19">
-        <v>150</v>
+        <v>90</v>
       </c>
       <c r="E19" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F19" t="s">
         <v>7</v>
@@ -1288,16 +1300,16 @@
         <v>7</v>
       </c>
       <c r="B20" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C20">
         <v>0</v>
       </c>
       <c r="D20">
-        <v>150</v>
+        <v>350</v>
       </c>
       <c r="E20" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="F20" t="s">
         <v>7</v>
@@ -1308,16 +1320,16 @@
         <v>7</v>
       </c>
       <c r="B21" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C21">
         <v>0</v>
       </c>
       <c r="D21">
-        <v>175</v>
+        <v>150</v>
       </c>
       <c r="E21" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F21" t="s">
         <v>7</v>
@@ -1328,16 +1340,16 @@
         <v>7</v>
       </c>
       <c r="B22" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C22">
         <v>0</v>
       </c>
       <c r="D22">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="E22" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="F22" t="s">
         <v>7</v>
@@ -1348,16 +1360,16 @@
         <v>7</v>
       </c>
       <c r="B23" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C23">
         <v>0</v>
       </c>
       <c r="D23">
-        <v>100</v>
+        <v>175</v>
       </c>
       <c r="E23" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="F23" t="s">
         <v>7</v>
@@ -1368,16 +1380,16 @@
         <v>7</v>
       </c>
       <c r="B24" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C24">
         <v>0</v>
       </c>
       <c r="D24">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="E24" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="F24" t="s">
         <v>7</v>
@@ -1388,16 +1400,16 @@
         <v>7</v>
       </c>
       <c r="B25" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C25">
         <v>0</v>
       </c>
       <c r="D25">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="E25" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="F25" t="s">
         <v>7</v>
@@ -1408,7 +1420,7 @@
         <v>7</v>
       </c>
       <c r="B26" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C26">
         <v>0</v>
@@ -1417,7 +1429,7 @@
         <v>100</v>
       </c>
       <c r="E26" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="F26" t="s">
         <v>7</v>
@@ -1428,16 +1440,16 @@
         <v>7</v>
       </c>
       <c r="B27" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C27">
         <v>0</v>
       </c>
       <c r="D27">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="E27" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="F27" t="s">
         <v>7</v>
@@ -1448,16 +1460,16 @@
         <v>7</v>
       </c>
       <c r="B28" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="C28">
         <v>0</v>
       </c>
       <c r="D28">
-        <v>28</v>
+        <v>100</v>
       </c>
       <c r="E28" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="F28" t="s">
         <v>7</v>
@@ -1468,16 +1480,16 @@
         <v>7</v>
       </c>
       <c r="B29" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C29">
         <v>0</v>
       </c>
       <c r="D29">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E29" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="F29" t="s">
         <v>7</v>
@@ -1485,19 +1497,19 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>102</v>
+        <v>7</v>
       </c>
       <c r="B30" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C30">
         <v>0</v>
       </c>
       <c r="D30">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E30" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="F30" t="s">
         <v>7</v>
@@ -1505,19 +1517,19 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>102</v>
+        <v>7</v>
       </c>
       <c r="B31" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C31">
         <v>0</v>
       </c>
       <c r="D31">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="E31" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="F31" t="s">
         <v>7</v>
@@ -1528,16 +1540,16 @@
         <v>102</v>
       </c>
       <c r="B32" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C32">
         <v>0</v>
       </c>
       <c r="D32">
-        <v>650</v>
+        <v>25</v>
       </c>
       <c r="E32" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="F32" t="s">
         <v>7</v>
@@ -1548,16 +1560,16 @@
         <v>102</v>
       </c>
       <c r="B33" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="C33">
         <v>0</v>
       </c>
       <c r="D33">
-        <v>550</v>
+        <v>40</v>
       </c>
       <c r="E33" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="F33" t="s">
         <v>7</v>
@@ -1568,16 +1580,16 @@
         <v>102</v>
       </c>
       <c r="B34" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="C34">
         <v>0</v>
       </c>
       <c r="D34">
-        <v>600</v>
+        <v>650</v>
       </c>
       <c r="E34" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="F34" t="s">
         <v>7</v>
@@ -1588,13 +1600,13 @@
         <v>102</v>
       </c>
       <c r="B35" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C35">
         <v>0</v>
       </c>
       <c r="D35">
-        <v>300</v>
+        <v>550</v>
       </c>
       <c r="E35" t="s">
         <v>53</v>
@@ -1608,16 +1620,16 @@
         <v>102</v>
       </c>
       <c r="B36" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C36">
         <v>0</v>
       </c>
       <c r="D36">
-        <v>550</v>
+        <v>600</v>
       </c>
       <c r="E36" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="F36" t="s">
         <v>7</v>
@@ -1628,16 +1640,16 @@
         <v>102</v>
       </c>
       <c r="B37" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C37">
         <v>0</v>
       </c>
       <c r="D37">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="E37" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F37" t="s">
         <v>7</v>
@@ -1645,19 +1657,19 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B38" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C38">
         <v>0</v>
       </c>
       <c r="D38">
-        <v>5</v>
+        <v>550</v>
       </c>
       <c r="E38" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="F38" t="s">
         <v>7</v>
@@ -1665,19 +1677,19 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B39" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C39">
         <v>0</v>
       </c>
       <c r="D39">
-        <v>10</v>
+        <v>500</v>
       </c>
       <c r="E39" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="F39" t="s">
         <v>7</v>
@@ -1688,16 +1700,16 @@
         <v>103</v>
       </c>
       <c r="B40" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C40">
         <v>0</v>
       </c>
       <c r="D40">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E40" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="F40" t="s">
         <v>7</v>
@@ -1708,16 +1720,16 @@
         <v>103</v>
       </c>
       <c r="B41" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C41">
         <v>0</v>
       </c>
       <c r="D41">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E41" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="F41" t="s">
         <v>7</v>
@@ -1728,16 +1740,16 @@
         <v>103</v>
       </c>
       <c r="B42" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C42">
         <v>0</v>
       </c>
       <c r="D42">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E42" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="F42" t="s">
         <v>7</v>
@@ -1748,16 +1760,16 @@
         <v>103</v>
       </c>
       <c r="B43" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C43">
         <v>0</v>
       </c>
       <c r="D43">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E43" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="F43" t="s">
         <v>7</v>
@@ -1768,7 +1780,7 @@
         <v>103</v>
       </c>
       <c r="B44" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="C44">
         <v>0</v>
@@ -1777,7 +1789,7 @@
         <v>10</v>
       </c>
       <c r="E44" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="F44" t="s">
         <v>7</v>
@@ -1788,16 +1800,16 @@
         <v>103</v>
       </c>
       <c r="B45" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C45">
         <v>0</v>
       </c>
       <c r="D45">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E45" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="F45" t="s">
         <v>7</v>
@@ -1808,16 +1820,16 @@
         <v>103</v>
       </c>
       <c r="B46" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C46">
         <v>0</v>
       </c>
       <c r="D46">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="E46" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="F46" t="s">
         <v>7</v>
@@ -1828,16 +1840,16 @@
         <v>103</v>
       </c>
       <c r="B47" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C47">
         <v>0</v>
       </c>
       <c r="D47">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E47" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="F47" t="s">
         <v>7</v>
@@ -1848,16 +1860,16 @@
         <v>103</v>
       </c>
       <c r="B48" t="s">
-        <v>119</v>
+        <v>75</v>
       </c>
       <c r="C48">
         <v>0</v>
       </c>
       <c r="D48">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="E48" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="F48" t="s">
         <v>7</v>
@@ -1868,16 +1880,16 @@
         <v>103</v>
       </c>
       <c r="B49" t="s">
-        <v>118</v>
+        <v>77</v>
       </c>
       <c r="C49">
         <v>0</v>
       </c>
       <c r="D49">
-        <v>45</v>
+        <v>5</v>
       </c>
       <c r="E49" t="s">
-        <v>120</v>
+        <v>78</v>
       </c>
       <c r="F49" t="s">
         <v>7</v>
@@ -1888,16 +1900,16 @@
         <v>103</v>
       </c>
       <c r="B50" t="s">
-        <v>80</v>
+        <v>119</v>
       </c>
       <c r="C50">
         <v>0</v>
       </c>
       <c r="D50">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="E50" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="F50" t="s">
         <v>7</v>
@@ -1908,16 +1920,16 @@
         <v>103</v>
       </c>
       <c r="B51" t="s">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="C51">
         <v>0</v>
       </c>
       <c r="D51">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="E51" t="s">
-        <v>83</v>
+        <v>120</v>
       </c>
       <c r="F51" t="s">
         <v>7</v>
@@ -1928,16 +1940,16 @@
         <v>103</v>
       </c>
       <c r="B52" t="s">
-        <v>109</v>
+        <v>80</v>
       </c>
       <c r="C52">
         <v>0</v>
       </c>
       <c r="D52">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="E52" t="s">
-        <v>108</v>
+        <v>81</v>
       </c>
       <c r="F52" t="s">
         <v>7</v>
@@ -1948,16 +1960,16 @@
         <v>103</v>
       </c>
       <c r="B53" t="s">
-        <v>110</v>
+        <v>82</v>
       </c>
       <c r="C53">
         <v>0</v>
       </c>
       <c r="D53">
-        <v>62</v>
+        <v>10</v>
       </c>
       <c r="E53" t="s">
-        <v>111</v>
+        <v>83</v>
       </c>
       <c r="F53" t="s">
         <v>7</v>
@@ -1968,16 +1980,16 @@
         <v>103</v>
       </c>
       <c r="B54" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C54">
         <v>0</v>
       </c>
       <c r="D54">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E54" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="F54" t="s">
         <v>7</v>
@@ -1988,16 +2000,16 @@
         <v>103</v>
       </c>
       <c r="B55" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="C55">
         <v>0</v>
       </c>
       <c r="D55">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="E55" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="F55" t="s">
         <v>7</v>
@@ -2008,16 +2020,16 @@
         <v>103</v>
       </c>
       <c r="B56" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="C56">
         <v>0</v>
       </c>
       <c r="D56">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="E56" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="F56" t="s">
         <v>7</v>
@@ -2028,16 +2040,16 @@
         <v>103</v>
       </c>
       <c r="B57" t="s">
-        <v>135</v>
+        <v>114</v>
       </c>
       <c r="C57">
         <v>0</v>
       </c>
       <c r="D57">
-        <v>25</v>
+        <v>52</v>
       </c>
       <c r="E57" t="s">
-        <v>136</v>
+        <v>115</v>
       </c>
       <c r="F57" t="s">
         <v>7</v>
@@ -2048,16 +2060,16 @@
         <v>103</v>
       </c>
       <c r="B58" t="s">
-        <v>133</v>
+        <v>121</v>
       </c>
       <c r="C58">
         <v>0</v>
       </c>
       <c r="D58">
-        <v>10</v>
+        <v>57</v>
       </c>
       <c r="E58" t="s">
-        <v>137</v>
+        <v>122</v>
       </c>
       <c r="F58" t="s">
         <v>7</v>
@@ -2068,16 +2080,16 @@
         <v>103</v>
       </c>
       <c r="B59" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="C59">
         <v>0</v>
       </c>
       <c r="D59">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="E59" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="F59" t="s">
         <v>7</v>
@@ -2088,16 +2100,16 @@
         <v>103</v>
       </c>
       <c r="B60" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C60">
         <v>0</v>
       </c>
       <c r="D60">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E60" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="F60" t="s">
         <v>7</v>
@@ -2108,16 +2120,16 @@
         <v>103</v>
       </c>
       <c r="B61" t="s">
-        <v>123</v>
+        <v>138</v>
       </c>
       <c r="C61">
         <v>0</v>
       </c>
       <c r="D61">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="E61" t="s">
-        <v>124</v>
+        <v>140</v>
       </c>
       <c r="F61" t="s">
         <v>7</v>
@@ -2128,16 +2140,16 @@
         <v>103</v>
       </c>
       <c r="B62" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="C62">
         <v>0</v>
       </c>
       <c r="D62">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E62" t="s">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="F62" t="s">
         <v>7</v>
@@ -2148,16 +2160,16 @@
         <v>103</v>
       </c>
       <c r="B63" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="C63">
         <v>0</v>
       </c>
       <c r="D63">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="E63" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="F63" t="s">
         <v>7</v>
@@ -2165,10 +2177,10 @@
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B64" t="s">
-        <v>84</v>
+        <v>127</v>
       </c>
       <c r="C64">
         <v>0</v>
@@ -2177,7 +2189,7 @@
         <v>10</v>
       </c>
       <c r="E64" t="s">
-        <v>85</v>
+        <v>128</v>
       </c>
       <c r="F64" t="s">
         <v>7</v>
@@ -2185,19 +2197,19 @@
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B65" t="s">
-        <v>86</v>
+        <v>116</v>
       </c>
       <c r="C65">
         <v>0</v>
       </c>
       <c r="D65">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E65" t="s">
-        <v>87</v>
+        <v>117</v>
       </c>
       <c r="F65" t="s">
         <v>7</v>
@@ -2208,7 +2220,7 @@
         <v>101</v>
       </c>
       <c r="B66" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="C66">
         <v>0</v>
@@ -2217,7 +2229,7 @@
         <v>10</v>
       </c>
       <c r="E66" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="F66" t="s">
         <v>7</v>
@@ -2228,16 +2240,16 @@
         <v>101</v>
       </c>
       <c r="B67" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C67">
         <v>0</v>
       </c>
       <c r="D67">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E67" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="F67" t="s">
         <v>7</v>
@@ -2248,16 +2260,16 @@
         <v>101</v>
       </c>
       <c r="B68" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="C68">
         <v>0</v>
       </c>
       <c r="D68">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E68" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="F68" t="s">
         <v>7</v>
@@ -2268,7 +2280,7 @@
         <v>101</v>
       </c>
       <c r="B69" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="C69">
         <v>0</v>
@@ -2277,7 +2289,7 @@
         <v>20</v>
       </c>
       <c r="E69" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="F69" t="s">
         <v>7</v>
@@ -2288,7 +2300,7 @@
         <v>101</v>
       </c>
       <c r="B70" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="C70">
         <v>0</v>
@@ -2297,7 +2309,7 @@
         <v>20</v>
       </c>
       <c r="E70" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="F70" t="s">
         <v>7</v>
@@ -2308,7 +2320,7 @@
         <v>101</v>
       </c>
       <c r="B71" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="C71">
         <v>0</v>
@@ -2317,7 +2329,7 @@
         <v>20</v>
       </c>
       <c r="E71" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="F71" t="s">
         <v>7</v>
@@ -2328,7 +2340,7 @@
         <v>101</v>
       </c>
       <c r="B72" t="s">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="C72">
         <v>0</v>
@@ -2337,7 +2349,7 @@
         <v>20</v>
       </c>
       <c r="E72" t="s">
-        <v>126</v>
+        <v>106</v>
       </c>
       <c r="F72" t="s">
         <v>7</v>
@@ -2348,16 +2360,16 @@
         <v>101</v>
       </c>
       <c r="B73" t="s">
-        <v>159</v>
+        <v>105</v>
       </c>
       <c r="C73">
         <v>0</v>
       </c>
       <c r="D73">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E73" t="s">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="F73" t="s">
         <v>7</v>
@@ -2368,16 +2380,16 @@
         <v>101</v>
       </c>
       <c r="B74" t="s">
-        <v>160</v>
+        <v>125</v>
       </c>
       <c r="C74">
         <v>0</v>
       </c>
       <c r="D74">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E74" t="s">
-        <v>94</v>
+        <v>126</v>
       </c>
       <c r="F74" t="s">
         <v>7</v>
@@ -2388,16 +2400,16 @@
         <v>101</v>
       </c>
       <c r="B75" t="s">
-        <v>96</v>
+        <v>159</v>
       </c>
       <c r="C75">
         <v>0</v>
       </c>
       <c r="D75">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="E75" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F75" t="s">
         <v>7</v>
@@ -2408,16 +2420,16 @@
         <v>101</v>
       </c>
       <c r="B76" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C76">
         <v>0</v>
       </c>
       <c r="D76">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="E76" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="F76" t="s">
         <v>7</v>
@@ -2428,16 +2440,16 @@
         <v>101</v>
       </c>
       <c r="B77" t="s">
-        <v>141</v>
+        <v>96</v>
       </c>
       <c r="C77">
         <v>0</v>
       </c>
       <c r="D77">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="E77" t="s">
-        <v>132</v>
+        <v>97</v>
       </c>
       <c r="F77" t="s">
         <v>7</v>
@@ -2448,16 +2460,16 @@
         <v>101</v>
       </c>
       <c r="B78" t="s">
-        <v>129</v>
+        <v>161</v>
       </c>
       <c r="C78">
         <v>0</v>
       </c>
       <c r="D78">
-        <v>65</v>
+        <v>35</v>
       </c>
       <c r="E78" t="s">
-        <v>130</v>
+        <v>98</v>
       </c>
       <c r="F78" t="s">
         <v>7</v>
@@ -2468,13 +2480,13 @@
         <v>101</v>
       </c>
       <c r="B79" t="s">
-        <v>131</v>
+        <v>141</v>
       </c>
       <c r="C79">
         <v>0</v>
       </c>
       <c r="D79">
-        <v>85</v>
+        <v>50</v>
       </c>
       <c r="E79" t="s">
         <v>132</v>
@@ -2488,16 +2500,16 @@
         <v>101</v>
       </c>
       <c r="B80" t="s">
-        <v>142</v>
+        <v>129</v>
       </c>
       <c r="C80">
         <v>0</v>
       </c>
       <c r="D80">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="E80" t="s">
-        <v>146</v>
+        <v>130</v>
       </c>
       <c r="F80" t="s">
         <v>7</v>
@@ -2508,16 +2520,16 @@
         <v>101</v>
       </c>
       <c r="B81" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
       <c r="C81">
         <v>0</v>
       </c>
       <c r="D81">
-        <v>30</v>
+        <v>85</v>
       </c>
       <c r="E81" t="s">
-        <v>145</v>
+        <v>132</v>
       </c>
       <c r="F81" t="s">
         <v>7</v>
@@ -2528,18 +2540,58 @@
         <v>101</v>
       </c>
       <c r="B82" t="s">
+        <v>142</v>
+      </c>
+      <c r="C82">
+        <v>0</v>
+      </c>
+      <c r="D82">
+        <v>100</v>
+      </c>
+      <c r="E82" t="s">
+        <v>146</v>
+      </c>
+      <c r="F82" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A83" t="s">
+        <v>101</v>
+      </c>
+      <c r="B83" t="s">
+        <v>143</v>
+      </c>
+      <c r="C83">
+        <v>0</v>
+      </c>
+      <c r="D83">
+        <v>30</v>
+      </c>
+      <c r="E83" t="s">
+        <v>145</v>
+      </c>
+      <c r="F83" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A84" t="s">
+        <v>101</v>
+      </c>
+      <c r="B84" t="s">
         <v>144</v>
       </c>
-      <c r="C82">
-        <v>0</v>
-      </c>
-      <c r="D82">
+      <c r="C84">
+        <v>0</v>
+      </c>
+      <c r="D84">
         <v>20</v>
       </c>
-      <c r="E82" t="s">
+      <c r="E84" t="s">
         <v>145</v>
       </c>
-      <c r="F82" t="s">
+      <c r="F84" t="s">
         <v>7</v>
       </c>
     </row>

--- a/DhalisMenu_cat.xlsx
+++ b/DhalisMenu_cat.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Documents\Custom Office Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DC779B3-EB51-455B-8EC8-B3B94DBB9705}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{894162A4-7804-4630-B24D-B84A6F520D44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1506,7 +1506,7 @@
         <v>0</v>
       </c>
       <c r="D30">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E30" t="s">
         <v>43</v>

--- a/DhalisMenu_cat.xlsx
+++ b/DhalisMenu_cat.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Documents\Custom Office Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{894162A4-7804-4630-B24D-B84A6F520D44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFF2E468-78A8-4A89-BEC8-7C006EA27016}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$71</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$73</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="346" uniqueCount="172">
   <si>
     <t>Item</t>
   </si>
@@ -40,24 +40,15 @@
     <t>Category</t>
   </si>
   <si>
-    <t xml:space="preserve">Aloo tikki Burger </t>
-  </si>
-  <si>
     <t>Burger Aloo tikki.png</t>
   </si>
   <si>
     <t>Fast Food</t>
   </si>
   <si>
-    <t>Aloo tikki chees Burger</t>
-  </si>
-  <si>
     <t>XL Burger Aloo tikki chees.jpeg</t>
   </si>
   <si>
-    <t>Paneer tikki chees Burger</t>
-  </si>
-  <si>
     <t>Brioche Bun Burger Paneer tikki chees.jpeg</t>
   </si>
   <si>
@@ -478,12 +469,6 @@
     <t>Momo's Vegs</t>
   </si>
   <si>
-    <t>Singapore Chowmein</t>
-  </si>
-  <si>
-    <t>Chowmein</t>
-  </si>
-  <si>
     <t>Chill Potato.jpg</t>
   </si>
   <si>
@@ -520,19 +505,40 @@
     <t>Chowmine And Cilly.jpg</t>
   </si>
   <si>
-    <t xml:space="preserve">20 RS/30rs Chowmein &amp; Momos &amp; Chilly Patato </t>
-  </si>
-  <si>
-    <t>Veg Man churiyan Dry</t>
-  </si>
-  <si>
-    <t>Veg Man churiyan Gravy</t>
-  </si>
-  <si>
     <t>Veg Man churiyan Dry.jpg</t>
   </si>
   <si>
     <t>Veg Man churiyan Gravy.jpg</t>
+  </si>
+  <si>
+    <t>Maha Tikki Burger</t>
+  </si>
+  <si>
+    <t>Maha Tikki Burger chees Burger</t>
+  </si>
+  <si>
+    <t>Crispy Junior Aloo Tikki cheese Burger</t>
+  </si>
+  <si>
+    <t>Crispy Junior Aloo Tikki Burger</t>
+  </si>
+  <si>
+    <t>Veg Manchurian Dry</t>
+  </si>
+  <si>
+    <t>Veg Manchurian Gravy</t>
+  </si>
+  <si>
+    <t>Paneer tikki cheese Burger</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20 RS/30rs Chow Mein &amp; Momos &amp; Chilly Potato </t>
+  </si>
+  <si>
+    <t>Chow Mein</t>
+  </si>
+  <si>
+    <t>Singapore Chow Mein</t>
   </si>
 </sst>
 </file>
@@ -905,7 +911,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F84"/>
+  <dimension ref="A1:F86"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="8.81640625" bestFit="1" customWidth="1"/>
@@ -937,170 +943,170 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B2" t="s">
+        <v>165</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2">
+        <v>40</v>
+      </c>
+      <c r="E2" t="s">
         <v>5</v>
       </c>
-      <c r="C2">
-        <v>0</v>
-      </c>
-      <c r="D2">
-        <v>60</v>
-      </c>
-      <c r="E2" t="s">
-        <v>6</v>
-      </c>
       <c r="F2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" t="s">
+        <v>164</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <v>50</v>
+      </c>
+      <c r="E3" t="s">
         <v>7</v>
       </c>
-      <c r="B3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3">
-        <v>0</v>
-      </c>
-      <c r="D3">
-        <v>80</v>
-      </c>
-      <c r="E3" t="s">
-        <v>9</v>
-      </c>
       <c r="F3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
+        <v>162</v>
       </c>
       <c r="C4">
         <v>0</v>
       </c>
       <c r="D4">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="E4" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>148</v>
+        <v>163</v>
       </c>
       <c r="C5">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="D5">
         <v>80</v>
       </c>
       <c r="E5" t="s">
-        <v>153</v>
+        <v>7</v>
       </c>
       <c r="F5" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>149</v>
+        <v>168</v>
       </c>
       <c r="C6">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="D6">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="E6" t="s">
-        <v>154</v>
+        <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>165</v>
+        <v>145</v>
       </c>
       <c r="C7">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="D7">
-        <v>30</v>
+        <v>80</v>
       </c>
       <c r="E7" t="s">
-        <v>164</v>
+        <v>148</v>
       </c>
       <c r="F7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="C8">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="D8">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="E8" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="F8" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>151</v>
+        <v>169</v>
       </c>
       <c r="C9">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="D9">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="E9" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F9" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B10" t="s">
-        <v>150</v>
+        <v>170</v>
       </c>
       <c r="C10">
         <v>40</v>
@@ -1109,35 +1115,35 @@
         <v>80</v>
       </c>
       <c r="E10" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="F10" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B11" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="C11">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="D11">
         <v>100</v>
       </c>
       <c r="E11" t="s">
-        <v>163</v>
+        <v>153</v>
       </c>
       <c r="F11" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B12" t="s">
         <v>147</v>
@@ -1149,98 +1155,98 @@
         <v>80</v>
       </c>
       <c r="E12" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="F12" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B13" t="s">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="C13">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="D13">
-        <v>160</v>
+        <v>100</v>
       </c>
       <c r="E13" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="F13" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B14" t="s">
-        <v>167</v>
+        <v>144</v>
       </c>
       <c r="C14">
-        <v>90</v>
+        <v>40</v>
       </c>
       <c r="D14">
-        <v>175</v>
+        <v>80</v>
       </c>
       <c r="E14" t="s">
-        <v>169</v>
+        <v>151</v>
       </c>
       <c r="F14" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B15" t="s">
-        <v>12</v>
+        <v>166</v>
       </c>
       <c r="C15">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="D15">
-        <v>90</v>
+        <v>160</v>
       </c>
       <c r="E15" t="s">
-        <v>13</v>
+        <v>160</v>
       </c>
       <c r="F15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B16" t="s">
-        <v>14</v>
+        <v>167</v>
       </c>
       <c r="C16">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="D16">
-        <v>90</v>
+        <v>175</v>
       </c>
       <c r="E16" t="s">
-        <v>15</v>
+        <v>161</v>
       </c>
       <c r="F16" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B17" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="C17">
         <v>0</v>
@@ -1249,18 +1255,18 @@
         <v>90</v>
       </c>
       <c r="E17" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="F17" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B18" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="C18">
         <v>0</v>
@@ -1269,18 +1275,18 @@
         <v>90</v>
       </c>
       <c r="E18" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="F18" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B19" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="C19">
         <v>0</v>
@@ -1289,178 +1295,178 @@
         <v>90</v>
       </c>
       <c r="E19" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="F19" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B20" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="C20">
         <v>0</v>
       </c>
       <c r="D20">
-        <v>350</v>
+        <v>90</v>
       </c>
       <c r="E20" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="F20" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B21" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="C21">
         <v>0</v>
       </c>
       <c r="D21">
-        <v>150</v>
+        <v>90</v>
       </c>
       <c r="E21" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="F21" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B22" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="C22">
         <v>0</v>
       </c>
       <c r="D22">
-        <v>150</v>
+        <v>350</v>
       </c>
       <c r="E22" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="F22" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B23" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="C23">
         <v>0</v>
       </c>
       <c r="D23">
-        <v>175</v>
+        <v>150</v>
       </c>
       <c r="E23" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="F23" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B24" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="C24">
         <v>0</v>
       </c>
       <c r="D24">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="E24" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="F24" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B25" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="C25">
         <v>0</v>
       </c>
       <c r="D25">
-        <v>100</v>
+        <v>175</v>
       </c>
       <c r="E25" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="F25" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B26" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="C26">
         <v>0</v>
       </c>
       <c r="D26">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="E26" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="F26" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B27" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="C27">
         <v>0</v>
       </c>
       <c r="D27">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="E27" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="F27" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B28" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="C28">
         <v>0</v>
@@ -1469,358 +1475,358 @@
         <v>100</v>
       </c>
       <c r="E28" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="F28" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B29" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="C29">
         <v>0</v>
       </c>
       <c r="D29">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="E29" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="F29" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B30" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="C30">
         <v>0</v>
       </c>
       <c r="D30">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="E30" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="F30" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B31" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="C31">
         <v>0</v>
       </c>
       <c r="D31">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E31" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="F31" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>102</v>
+        <v>6</v>
       </c>
       <c r="B32" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="C32">
         <v>0</v>
       </c>
       <c r="D32">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E32" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="F32" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>102</v>
+        <v>6</v>
       </c>
       <c r="B33" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="C33">
         <v>0</v>
       </c>
       <c r="D33">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="E33" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="F33" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="B34" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="C34">
         <v>0</v>
       </c>
       <c r="D34">
-        <v>650</v>
+        <v>25</v>
       </c>
       <c r="E34" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="F34" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="B35" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="C35">
         <v>0</v>
       </c>
       <c r="D35">
-        <v>550</v>
+        <v>40</v>
       </c>
       <c r="E35" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="F35" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="B36" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="C36">
         <v>0</v>
       </c>
       <c r="D36">
-        <v>600</v>
+        <v>650</v>
       </c>
       <c r="E36" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="F36" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="B37" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="C37">
         <v>0</v>
       </c>
       <c r="D37">
-        <v>300</v>
+        <v>550</v>
       </c>
       <c r="E37" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="F37" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="B38" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="C38">
         <v>0</v>
       </c>
       <c r="D38">
-        <v>550</v>
+        <v>600</v>
       </c>
       <c r="E38" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F38" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="B39" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="C39">
         <v>0</v>
       </c>
       <c r="D39">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="E39" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="F39" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="B40" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="C40">
         <v>0</v>
       </c>
       <c r="D40">
-        <v>5</v>
+        <v>550</v>
       </c>
       <c r="E40" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="F40" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="B41" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="C41">
         <v>0</v>
       </c>
       <c r="D41">
-        <v>10</v>
+        <v>500</v>
       </c>
       <c r="E41" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="F41" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="B42" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="C42">
         <v>0</v>
       </c>
       <c r="D42">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E42" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="F42" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="B43" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="C43">
         <v>0</v>
       </c>
       <c r="D43">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E43" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="F43" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="B44" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="C44">
         <v>0</v>
       </c>
       <c r="D44">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E44" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="F44" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="B45" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="C45">
         <v>0</v>
       </c>
       <c r="D45">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E45" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="F45" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="B46" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="C46">
         <v>0</v>
@@ -1829,398 +1835,398 @@
         <v>10</v>
       </c>
       <c r="E46" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="F46" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="B47" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="C47">
         <v>0</v>
       </c>
       <c r="D47">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E47" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="F47" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="B48" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="C48">
         <v>0</v>
       </c>
       <c r="D48">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="E48" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="F48" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="B49" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="C49">
         <v>0</v>
       </c>
       <c r="D49">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E49" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="F49" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="B50" t="s">
-        <v>119</v>
+        <v>72</v>
       </c>
       <c r="C50">
         <v>0</v>
       </c>
       <c r="D50">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="E50" t="s">
-        <v>79</v>
+        <v>73</v>
       </c>
       <c r="F50" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="B51" t="s">
-        <v>118</v>
+        <v>74</v>
       </c>
       <c r="C51">
         <v>0</v>
       </c>
       <c r="D51">
-        <v>45</v>
+        <v>5</v>
       </c>
       <c r="E51" t="s">
-        <v>120</v>
+        <v>75</v>
       </c>
       <c r="F51" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="B52" t="s">
-        <v>80</v>
+        <v>116</v>
       </c>
       <c r="C52">
         <v>0</v>
       </c>
       <c r="D52">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="E52" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="F52" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="B53" t="s">
-        <v>82</v>
+        <v>115</v>
       </c>
       <c r="C53">
         <v>0</v>
       </c>
       <c r="D53">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="E53" t="s">
-        <v>83</v>
+        <v>117</v>
       </c>
       <c r="F53" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="B54" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
       <c r="C54">
         <v>0</v>
       </c>
       <c r="D54">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="E54" t="s">
-        <v>108</v>
+        <v>78</v>
       </c>
       <c r="F54" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="B55" t="s">
-        <v>110</v>
+        <v>79</v>
       </c>
       <c r="C55">
         <v>0</v>
       </c>
       <c r="D55">
-        <v>62</v>
+        <v>10</v>
       </c>
       <c r="E55" t="s">
-        <v>111</v>
+        <v>80</v>
       </c>
       <c r="F55" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="B56" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="C56">
         <v>0</v>
       </c>
       <c r="D56">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E56" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="F56" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="B57" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="C57">
         <v>0</v>
       </c>
       <c r="D57">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="E57" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="F57" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="B58" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="C58">
         <v>0</v>
       </c>
       <c r="D58">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="E58" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="F58" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="B59" t="s">
-        <v>135</v>
+        <v>111</v>
       </c>
       <c r="C59">
         <v>0</v>
       </c>
       <c r="D59">
-        <v>25</v>
+        <v>52</v>
       </c>
       <c r="E59" t="s">
-        <v>136</v>
+        <v>112</v>
       </c>
       <c r="F59" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="B60" t="s">
-        <v>133</v>
+        <v>118</v>
       </c>
       <c r="C60">
         <v>0</v>
       </c>
       <c r="D60">
-        <v>10</v>
+        <v>57</v>
       </c>
       <c r="E60" t="s">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="F60" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="B61" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="C61">
         <v>0</v>
       </c>
       <c r="D61">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="E61" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="F61" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="B62" t="s">
+        <v>130</v>
+      </c>
+      <c r="C62">
+        <v>0</v>
+      </c>
+      <c r="D62">
+        <v>10</v>
+      </c>
+      <c r="E62" t="s">
         <v>134</v>
       </c>
-      <c r="C62">
-        <v>0</v>
-      </c>
-      <c r="D62">
-        <v>5</v>
-      </c>
-      <c r="E62" t="s">
-        <v>139</v>
-      </c>
       <c r="F62" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="B63" t="s">
-        <v>123</v>
+        <v>135</v>
       </c>
       <c r="C63">
         <v>0</v>
       </c>
       <c r="D63">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="E63" t="s">
-        <v>124</v>
+        <v>137</v>
       </c>
       <c r="F63" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="B64" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="C64">
         <v>0</v>
       </c>
       <c r="D64">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E64" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="F64" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="B65" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="C65">
         <v>0</v>
       </c>
       <c r="D65">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="E65" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="F65" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B66" t="s">
-        <v>84</v>
+        <v>124</v>
       </c>
       <c r="C66">
         <v>0</v>
@@ -2229,38 +2235,38 @@
         <v>10</v>
       </c>
       <c r="E66" t="s">
-        <v>85</v>
+        <v>125</v>
       </c>
       <c r="F66" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B67" t="s">
-        <v>86</v>
+        <v>113</v>
       </c>
       <c r="C67">
         <v>0</v>
       </c>
       <c r="D67">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E67" t="s">
-        <v>87</v>
+        <v>114</v>
       </c>
       <c r="F67" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="B68" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="C68">
         <v>0</v>
@@ -2269,58 +2275,58 @@
         <v>10</v>
       </c>
       <c r="E68" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="F68" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="B69" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="C69">
         <v>0</v>
       </c>
       <c r="D69">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E69" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="F69" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="B70" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="C70">
         <v>0</v>
       </c>
       <c r="D70">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E70" t="s">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="F70" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="B71" t="s">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c r="C71">
         <v>0</v>
@@ -2329,18 +2335,18 @@
         <v>20</v>
       </c>
       <c r="E71" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="F71" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="B72" t="s">
-        <v>104</v>
+        <v>89</v>
       </c>
       <c r="C72">
         <v>0</v>
@@ -2349,18 +2355,18 @@
         <v>20</v>
       </c>
       <c r="E72" t="s">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="F72" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="B73" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="C73">
         <v>0</v>
@@ -2369,18 +2375,18 @@
         <v>20</v>
       </c>
       <c r="E73" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="F73" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
+        <v>98</v>
+      </c>
+      <c r="B74" t="s">
         <v>101</v>
-      </c>
-      <c r="B74" t="s">
-        <v>125</v>
       </c>
       <c r="C74">
         <v>0</v>
@@ -2389,210 +2395,250 @@
         <v>20</v>
       </c>
       <c r="E74" t="s">
-        <v>126</v>
+        <v>103</v>
       </c>
       <c r="F74" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="B75" t="s">
-        <v>159</v>
+        <v>102</v>
       </c>
       <c r="C75">
         <v>0</v>
       </c>
       <c r="D75">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E75" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="F75" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="B76" t="s">
-        <v>160</v>
+        <v>122</v>
       </c>
       <c r="C76">
         <v>0</v>
       </c>
       <c r="D76">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E76" t="s">
-        <v>94</v>
+        <v>123</v>
       </c>
       <c r="F76" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="B77" t="s">
-        <v>96</v>
+        <v>154</v>
       </c>
       <c r="C77">
         <v>0</v>
       </c>
       <c r="D77">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="E77" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="F77" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="B78" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="C78">
         <v>0</v>
       </c>
       <c r="D78">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="E78" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="F78" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="B79" t="s">
-        <v>141</v>
+        <v>93</v>
       </c>
       <c r="C79">
         <v>0</v>
       </c>
       <c r="D79">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="E79" t="s">
-        <v>132</v>
+        <v>94</v>
       </c>
       <c r="F79" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="B80" t="s">
-        <v>129</v>
+        <v>156</v>
       </c>
       <c r="C80">
         <v>0</v>
       </c>
       <c r="D80">
-        <v>65</v>
+        <v>35</v>
       </c>
       <c r="E80" t="s">
-        <v>130</v>
+        <v>95</v>
       </c>
       <c r="F80" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="B81" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="C81">
         <v>0</v>
       </c>
       <c r="D81">
-        <v>85</v>
+        <v>50</v>
       </c>
       <c r="E81" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="F81" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="B82" t="s">
-        <v>142</v>
+        <v>126</v>
       </c>
       <c r="C82">
         <v>0</v>
       </c>
       <c r="D82">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="E82" t="s">
-        <v>146</v>
+        <v>127</v>
       </c>
       <c r="F82" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="B83" t="s">
-        <v>143</v>
+        <v>128</v>
       </c>
       <c r="C83">
         <v>0</v>
       </c>
       <c r="D83">
-        <v>30</v>
+        <v>85</v>
       </c>
       <c r="E83" t="s">
-        <v>145</v>
+        <v>129</v>
       </c>
       <c r="F83" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="B84" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="C84">
         <v>0</v>
       </c>
       <c r="D84">
+        <v>100</v>
+      </c>
+      <c r="E84" t="s">
+        <v>143</v>
+      </c>
+      <c r="F84" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A85" t="s">
+        <v>98</v>
+      </c>
+      <c r="B85" t="s">
+        <v>140</v>
+      </c>
+      <c r="C85">
+        <v>0</v>
+      </c>
+      <c r="D85">
+        <v>30</v>
+      </c>
+      <c r="E85" t="s">
+        <v>142</v>
+      </c>
+      <c r="F85" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A86" t="s">
+        <v>98</v>
+      </c>
+      <c r="B86" t="s">
+        <v>141</v>
+      </c>
+      <c r="C86">
+        <v>0</v>
+      </c>
+      <c r="D86">
         <v>20</v>
       </c>
-      <c r="E84" t="s">
-        <v>145</v>
-      </c>
-      <c r="F84" t="s">
-        <v>7</v>
+      <c r="E86" t="s">
+        <v>142</v>
+      </c>
+      <c r="F86" t="s">
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/DhalisMenu_cat.xlsx
+++ b/DhalisMenu_cat.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Documents\Custom Office Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFF2E468-78A8-4A89-BEC8-7C006EA27016}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5296F708-0D75-441E-BB7E-8CB34EB17869}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -514,9 +514,6 @@
     <t>Maha Tikki Burger</t>
   </si>
   <si>
-    <t>Maha Tikki Burger chees Burger</t>
-  </si>
-  <si>
     <t>Crispy Junior Aloo Tikki cheese Burger</t>
   </si>
   <si>
@@ -539,6 +536,9 @@
   </si>
   <si>
     <t>Singapore Chow Mein</t>
+  </si>
+  <si>
+    <t>Maha Tikki Double Chees Burger</t>
   </si>
 </sst>
 </file>
@@ -946,13 +946,13 @@
         <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C2">
         <v>0</v>
       </c>
       <c r="D2">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
@@ -966,13 +966,13 @@
         <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C3">
         <v>0</v>
       </c>
       <c r="D3">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="E3" t="s">
         <v>7</v>
@@ -1006,7 +1006,7 @@
         <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -1026,7 +1026,7 @@
         <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -1086,7 +1086,7 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C9">
         <v>20</v>
@@ -1106,7 +1106,7 @@
         <v>6</v>
       </c>
       <c r="B10" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C10">
         <v>40</v>
@@ -1126,7 +1126,7 @@
         <v>6</v>
       </c>
       <c r="B11" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C11">
         <v>60</v>
@@ -1206,7 +1206,7 @@
         <v>6</v>
       </c>
       <c r="B15" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C15">
         <v>80</v>
@@ -1226,7 +1226,7 @@
         <v>6</v>
       </c>
       <c r="B16" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C16">
         <v>90</v>
@@ -2606,13 +2606,13 @@
         <v>98</v>
       </c>
       <c r="B85" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C85">
         <v>0</v>
       </c>
       <c r="D85">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E85" t="s">
         <v>142</v>
@@ -2626,13 +2626,13 @@
         <v>98</v>
       </c>
       <c r="B86" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C86">
         <v>0</v>
       </c>
       <c r="D86">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="E86" t="s">
         <v>142</v>

--- a/DhalisMenu_cat.xlsx
+++ b/DhalisMenu_cat.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Documents\Custom Office Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5296F708-0D75-441E-BB7E-8CB34EB17869}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D550C10A-DCE7-442F-90B2-F2AAD1936EF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="346" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="174">
   <si>
     <t>Item</t>
   </si>
@@ -539,6 +539,12 @@
   </si>
   <si>
     <t>Maha Tikki Double Chees Burger</t>
+  </si>
+  <si>
+    <t>NON Stop</t>
+  </si>
+  <si>
+    <t>NONStop.jpeg</t>
   </si>
 </sst>
 </file>
@@ -911,7 +917,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F86"/>
+  <dimension ref="A1:F87"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="8.81640625" bestFit="1" customWidth="1"/>
@@ -2566,16 +2572,16 @@
         <v>98</v>
       </c>
       <c r="B83" t="s">
-        <v>128</v>
+        <v>172</v>
       </c>
       <c r="C83">
         <v>0</v>
       </c>
       <c r="D83">
-        <v>85</v>
+        <v>60</v>
       </c>
       <c r="E83" t="s">
-        <v>129</v>
+        <v>173</v>
       </c>
       <c r="F83" t="s">
         <v>6</v>
@@ -2586,16 +2592,16 @@
         <v>98</v>
       </c>
       <c r="B84" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="C84">
         <v>0</v>
       </c>
       <c r="D84">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="E84" t="s">
-        <v>143</v>
+        <v>129</v>
       </c>
       <c r="F84" t="s">
         <v>6</v>
@@ -2606,16 +2612,16 @@
         <v>98</v>
       </c>
       <c r="B85" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C85">
         <v>0</v>
       </c>
       <c r="D85">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="E85" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F85" t="s">
         <v>6</v>
@@ -2626,18 +2632,38 @@
         <v>98</v>
       </c>
       <c r="B86" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C86">
         <v>0</v>
       </c>
       <c r="D86">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E86" t="s">
         <v>142</v>
       </c>
       <c r="F86" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A87" t="s">
+        <v>98</v>
+      </c>
+      <c r="B87" t="s">
+        <v>140</v>
+      </c>
+      <c r="C87">
+        <v>0</v>
+      </c>
+      <c r="D87">
+        <v>30</v>
+      </c>
+      <c r="E87" t="s">
+        <v>142</v>
+      </c>
+      <c r="F87" t="s">
         <v>6</v>
       </c>
     </row>

--- a/DhalisMenu_cat.xlsx
+++ b/DhalisMenu_cat.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Documents\Custom Office Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D550C10A-DCE7-442F-90B2-F2AAD1936EF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E885021-DA53-4A89-8C5A-FE0CA62E5504}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$73</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$75</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="178">
   <si>
     <t>Item</t>
   </si>
@@ -545,6 +545,18 @@
   </si>
   <si>
     <t>NONStop.jpeg</t>
+  </si>
+  <si>
+    <t>Kinder Joy</t>
+  </si>
+  <si>
+    <t>Kinderjoy.jpeg</t>
+  </si>
+  <si>
+    <t>Jain Sikanji</t>
+  </si>
+  <si>
+    <t>JainSikanji.jpg</t>
   </si>
 </sst>
 </file>
@@ -917,7 +929,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F87"/>
+  <dimension ref="A1:F89"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="8.81640625" bestFit="1" customWidth="1"/>
@@ -2232,16 +2244,16 @@
         <v>100</v>
       </c>
       <c r="B66" t="s">
-        <v>124</v>
+        <v>174</v>
       </c>
       <c r="C66">
         <v>0</v>
       </c>
       <c r="D66">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="E66" t="s">
-        <v>125</v>
+        <v>175</v>
       </c>
       <c r="F66" t="s">
         <v>6</v>
@@ -2252,16 +2264,16 @@
         <v>100</v>
       </c>
       <c r="B67" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="C67">
         <v>0</v>
       </c>
       <c r="D67">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E67" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="F67" t="s">
         <v>6</v>
@@ -2269,19 +2281,19 @@
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B68" t="s">
-        <v>81</v>
+        <v>113</v>
       </c>
       <c r="C68">
         <v>0</v>
       </c>
       <c r="D68">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E68" t="s">
-        <v>82</v>
+        <v>114</v>
       </c>
       <c r="F68" t="s">
         <v>6</v>
@@ -2292,7 +2304,7 @@
         <v>98</v>
       </c>
       <c r="B69" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C69">
         <v>0</v>
@@ -2301,7 +2313,7 @@
         <v>10</v>
       </c>
       <c r="E69" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F69" t="s">
         <v>6</v>
@@ -2312,7 +2324,7 @@
         <v>98</v>
       </c>
       <c r="B70" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C70">
         <v>0</v>
@@ -2321,7 +2333,7 @@
         <v>10</v>
       </c>
       <c r="E70" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F70" t="s">
         <v>6</v>
@@ -2332,16 +2344,16 @@
         <v>98</v>
       </c>
       <c r="B71" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C71">
         <v>0</v>
       </c>
       <c r="D71">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E71" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F71" t="s">
         <v>6</v>
@@ -2352,16 +2364,16 @@
         <v>98</v>
       </c>
       <c r="B72" t="s">
-        <v>89</v>
+        <v>176</v>
       </c>
       <c r="C72">
         <v>0</v>
       </c>
       <c r="D72">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E72" t="s">
-        <v>90</v>
+        <v>177</v>
       </c>
       <c r="F72" t="s">
         <v>6</v>
@@ -2372,7 +2384,7 @@
         <v>98</v>
       </c>
       <c r="B73" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="C73">
         <v>0</v>
@@ -2381,7 +2393,7 @@
         <v>20</v>
       </c>
       <c r="E73" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="F73" t="s">
         <v>6</v>
@@ -2392,7 +2404,7 @@
         <v>98</v>
       </c>
       <c r="B74" t="s">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="C74">
         <v>0</v>
@@ -2401,7 +2413,7 @@
         <v>20</v>
       </c>
       <c r="E74" t="s">
-        <v>103</v>
+        <v>90</v>
       </c>
       <c r="F74" t="s">
         <v>6</v>
@@ -2412,7 +2424,7 @@
         <v>98</v>
       </c>
       <c r="B75" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="C75">
         <v>0</v>
@@ -2421,7 +2433,7 @@
         <v>20</v>
       </c>
       <c r="E75" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="F75" t="s">
         <v>6</v>
@@ -2432,7 +2444,7 @@
         <v>98</v>
       </c>
       <c r="B76" t="s">
-        <v>122</v>
+        <v>101</v>
       </c>
       <c r="C76">
         <v>0</v>
@@ -2441,7 +2453,7 @@
         <v>20</v>
       </c>
       <c r="E76" t="s">
-        <v>123</v>
+        <v>103</v>
       </c>
       <c r="F76" t="s">
         <v>6</v>
@@ -2452,16 +2464,16 @@
         <v>98</v>
       </c>
       <c r="B77" t="s">
-        <v>154</v>
+        <v>102</v>
       </c>
       <c r="C77">
         <v>0</v>
       </c>
       <c r="D77">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E77" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="F77" t="s">
         <v>6</v>
@@ -2472,16 +2484,16 @@
         <v>98</v>
       </c>
       <c r="B78" t="s">
-        <v>155</v>
+        <v>122</v>
       </c>
       <c r="C78">
         <v>0</v>
       </c>
       <c r="D78">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E78" t="s">
-        <v>91</v>
+        <v>123</v>
       </c>
       <c r="F78" t="s">
         <v>6</v>
@@ -2492,16 +2504,16 @@
         <v>98</v>
       </c>
       <c r="B79" t="s">
-        <v>93</v>
+        <v>154</v>
       </c>
       <c r="C79">
         <v>0</v>
       </c>
       <c r="D79">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="E79" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="F79" t="s">
         <v>6</v>
@@ -2512,16 +2524,16 @@
         <v>98</v>
       </c>
       <c r="B80" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C80">
         <v>0</v>
       </c>
       <c r="D80">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="E80" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="F80" t="s">
         <v>6</v>
@@ -2532,16 +2544,16 @@
         <v>98</v>
       </c>
       <c r="B81" t="s">
-        <v>138</v>
+        <v>93</v>
       </c>
       <c r="C81">
         <v>0</v>
       </c>
       <c r="D81">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="E81" t="s">
-        <v>129</v>
+        <v>94</v>
       </c>
       <c r="F81" t="s">
         <v>6</v>
@@ -2552,16 +2564,16 @@
         <v>98</v>
       </c>
       <c r="B82" t="s">
-        <v>126</v>
+        <v>156</v>
       </c>
       <c r="C82">
         <v>0</v>
       </c>
       <c r="D82">
-        <v>65</v>
+        <v>35</v>
       </c>
       <c r="E82" t="s">
-        <v>127</v>
+        <v>95</v>
       </c>
       <c r="F82" t="s">
         <v>6</v>
@@ -2572,16 +2584,16 @@
         <v>98</v>
       </c>
       <c r="B83" t="s">
-        <v>172</v>
+        <v>138</v>
       </c>
       <c r="C83">
         <v>0</v>
       </c>
       <c r="D83">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="E83" t="s">
-        <v>173</v>
+        <v>129</v>
       </c>
       <c r="F83" t="s">
         <v>6</v>
@@ -2592,16 +2604,16 @@
         <v>98</v>
       </c>
       <c r="B84" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C84">
         <v>0</v>
       </c>
       <c r="D84">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="E84" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="F84" t="s">
         <v>6</v>
@@ -2612,16 +2624,16 @@
         <v>98</v>
       </c>
       <c r="B85" t="s">
-        <v>139</v>
+        <v>172</v>
       </c>
       <c r="C85">
         <v>0</v>
       </c>
       <c r="D85">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="E85" t="s">
-        <v>143</v>
+        <v>173</v>
       </c>
       <c r="F85" t="s">
         <v>6</v>
@@ -2632,16 +2644,16 @@
         <v>98</v>
       </c>
       <c r="B86" t="s">
-        <v>141</v>
+        <v>128</v>
       </c>
       <c r="C86">
         <v>0</v>
       </c>
       <c r="D86">
-        <v>20</v>
+        <v>85</v>
       </c>
       <c r="E86" t="s">
-        <v>142</v>
+        <v>129</v>
       </c>
       <c r="F86" t="s">
         <v>6</v>
@@ -2652,18 +2664,58 @@
         <v>98</v>
       </c>
       <c r="B87" t="s">
+        <v>139</v>
+      </c>
+      <c r="C87">
+        <v>0</v>
+      </c>
+      <c r="D87">
+        <v>100</v>
+      </c>
+      <c r="E87" t="s">
+        <v>143</v>
+      </c>
+      <c r="F87" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A88" t="s">
+        <v>98</v>
+      </c>
+      <c r="B88" t="s">
+        <v>141</v>
+      </c>
+      <c r="C88">
+        <v>0</v>
+      </c>
+      <c r="D88">
+        <v>20</v>
+      </c>
+      <c r="E88" t="s">
+        <v>142</v>
+      </c>
+      <c r="F88" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A89" t="s">
+        <v>98</v>
+      </c>
+      <c r="B89" t="s">
         <v>140</v>
       </c>
-      <c r="C87">
-        <v>0</v>
-      </c>
-      <c r="D87">
+      <c r="C89">
+        <v>0</v>
+      </c>
+      <c r="D89">
         <v>30</v>
       </c>
-      <c r="E87" t="s">
+      <c r="E89" t="s">
         <v>142</v>
       </c>
-      <c r="F87" t="s">
+      <c r="F89" t="s">
         <v>6</v>
       </c>
     </row>

--- a/DhalisMenu_cat.xlsx
+++ b/DhalisMenu_cat.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Documents\Custom Office Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E885021-DA53-4A89-8C5A-FE0CA62E5504}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D366423-BF8A-47BC-BD76-184A8A2E1950}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -544,9 +544,6 @@
     <t>NON Stop</t>
   </si>
   <si>
-    <t>NONStop.jpeg</t>
-  </si>
-  <si>
     <t>Kinder Joy</t>
   </si>
   <si>
@@ -557,6 +554,9 @@
   </si>
   <si>
     <t>JainSikanji.jpg</t>
+  </si>
+  <si>
+    <t>NonStop-jpeg.jpeg</t>
   </si>
 </sst>
 </file>
@@ -2244,7 +2244,7 @@
         <v>100</v>
       </c>
       <c r="B66" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C66">
         <v>0</v>
@@ -2253,7 +2253,7 @@
         <v>50</v>
       </c>
       <c r="E66" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F66" t="s">
         <v>6</v>
@@ -2364,7 +2364,7 @@
         <v>98</v>
       </c>
       <c r="B72" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C72">
         <v>0</v>
@@ -2373,7 +2373,7 @@
         <v>10</v>
       </c>
       <c r="E72" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F72" t="s">
         <v>6</v>
@@ -2633,7 +2633,7 @@
         <v>60</v>
       </c>
       <c r="E85" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="F85" t="s">
         <v>6</v>

--- a/DhalisMenu_cat.xlsx
+++ b/DhalisMenu_cat.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Documents\Custom Office Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D366423-BF8A-47BC-BD76-184A8A2E1950}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4875D979-43B8-440B-95D8-91CE20BF44DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -556,7 +556,7 @@
     <t>JainSikanji.jpg</t>
   </si>
   <si>
-    <t>NonStop-jpeg.jpeg</t>
+    <t>NonStop-jpeg.jpg</t>
   </si>
 </sst>
 </file>

--- a/DhalisMenu_cat.xlsx
+++ b/DhalisMenu_cat.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Documents\Custom Office Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4875D979-43B8-440B-95D8-91CE20BF44DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65D7FF57-9BB1-49B3-8FC4-B99B1273DE84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -547,9 +547,6 @@
     <t>Kinder Joy</t>
   </si>
   <si>
-    <t>Kinderjoy.jpeg</t>
-  </si>
-  <si>
     <t>Jain Sikanji</t>
   </si>
   <si>
@@ -557,6 +554,9 @@
   </si>
   <si>
     <t>NonStop-jpeg.jpg</t>
+  </si>
+  <si>
+    <t>Kinderjoy.jpg</t>
   </si>
 </sst>
 </file>
@@ -2253,7 +2253,7 @@
         <v>50</v>
       </c>
       <c r="E66" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="F66" t="s">
         <v>6</v>
@@ -2364,7 +2364,7 @@
         <v>98</v>
       </c>
       <c r="B72" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C72">
         <v>0</v>
@@ -2373,7 +2373,7 @@
         <v>10</v>
       </c>
       <c r="E72" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F72" t="s">
         <v>6</v>
@@ -2633,7 +2633,7 @@
         <v>60</v>
       </c>
       <c r="E85" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F85" t="s">
         <v>6</v>

--- a/DhalisMenu_cat.xlsx
+++ b/DhalisMenu_cat.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Documents\Custom Office Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65D7FF57-9BB1-49B3-8FC4-B99B1273DE84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2400ACF9-8731-4B31-BCE3-684AC9B24894}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="180">
   <si>
     <t>Item</t>
   </si>
@@ -490,9 +490,6 @@
     <t>Dite Coke  Can 30 rs</t>
   </si>
   <si>
-    <t>Thumsup Can 30 rs</t>
-  </si>
-  <si>
     <t>Campa Energy Can 35Rs</t>
   </si>
   <si>
@@ -557,6 +554,15 @@
   </si>
   <si>
     <t>Kinderjoy.jpg</t>
+  </si>
+  <si>
+    <t>Red Bull</t>
+  </si>
+  <si>
+    <t>RedBull.jpg</t>
+  </si>
+  <si>
+    <t>Thumsup Can 40 rs</t>
   </si>
 </sst>
 </file>
@@ -929,7 +935,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F89"/>
+  <dimension ref="A1:F90"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="8.81640625" bestFit="1" customWidth="1"/>
@@ -964,7 +970,7 @@
         <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -984,7 +990,7 @@
         <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -1004,7 +1010,7 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -1024,7 +1030,7 @@
         <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -1044,7 +1050,7 @@
         <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C6">
         <v>0</v>
@@ -1104,7 +1110,7 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C9">
         <v>20</v>
@@ -1113,7 +1119,7 @@
         <v>30</v>
       </c>
       <c r="E9" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F9" t="s">
         <v>6</v>
@@ -1124,7 +1130,7 @@
         <v>6</v>
       </c>
       <c r="B10" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C10">
         <v>40</v>
@@ -1144,7 +1150,7 @@
         <v>6</v>
       </c>
       <c r="B11" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C11">
         <v>60</v>
@@ -1184,7 +1190,7 @@
         <v>6</v>
       </c>
       <c r="B13" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C13">
         <v>50</v>
@@ -1193,7 +1199,7 @@
         <v>100</v>
       </c>
       <c r="E13" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F13" t="s">
         <v>6</v>
@@ -1224,7 +1230,7 @@
         <v>6</v>
       </c>
       <c r="B15" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C15">
         <v>80</v>
@@ -1233,7 +1239,7 @@
         <v>160</v>
       </c>
       <c r="E15" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F15" t="s">
         <v>6</v>
@@ -1244,7 +1250,7 @@
         <v>6</v>
       </c>
       <c r="B16" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C16">
         <v>90</v>
@@ -1253,7 +1259,7 @@
         <v>175</v>
       </c>
       <c r="E16" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F16" t="s">
         <v>6</v>
@@ -1590,7 +1596,7 @@
         <v>0</v>
       </c>
       <c r="D33">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="E33" t="s">
         <v>42</v>
@@ -2244,7 +2250,7 @@
         <v>100</v>
       </c>
       <c r="B66" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C66">
         <v>0</v>
@@ -2253,7 +2259,7 @@
         <v>50</v>
       </c>
       <c r="E66" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F66" t="s">
         <v>6</v>
@@ -2364,7 +2370,7 @@
         <v>98</v>
       </c>
       <c r="B72" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C72">
         <v>0</v>
@@ -2373,7 +2379,7 @@
         <v>10</v>
       </c>
       <c r="E72" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F72" t="s">
         <v>6</v>
@@ -2524,13 +2530,13 @@
         <v>98</v>
       </c>
       <c r="B80" t="s">
-        <v>155</v>
+        <v>179</v>
       </c>
       <c r="C80">
         <v>0</v>
       </c>
       <c r="D80">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="E80" t="s">
         <v>91</v>
@@ -2544,7 +2550,7 @@
         <v>98</v>
       </c>
       <c r="B81" t="s">
-        <v>93</v>
+        <v>155</v>
       </c>
       <c r="C81">
         <v>0</v>
@@ -2553,7 +2559,7 @@
         <v>35</v>
       </c>
       <c r="E81" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F81" t="s">
         <v>6</v>
@@ -2564,16 +2570,16 @@
         <v>98</v>
       </c>
       <c r="B82" t="s">
-        <v>156</v>
+        <v>126</v>
       </c>
       <c r="C82">
         <v>0</v>
       </c>
       <c r="D82">
-        <v>35</v>
+        <v>65</v>
       </c>
       <c r="E82" t="s">
-        <v>95</v>
+        <v>127</v>
       </c>
       <c r="F82" t="s">
         <v>6</v>
@@ -2584,16 +2590,16 @@
         <v>98</v>
       </c>
       <c r="B83" t="s">
-        <v>138</v>
+        <v>171</v>
       </c>
       <c r="C83">
         <v>0</v>
       </c>
       <c r="D83">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="E83" t="s">
-        <v>129</v>
+        <v>175</v>
       </c>
       <c r="F83" t="s">
         <v>6</v>
@@ -2604,16 +2610,16 @@
         <v>98</v>
       </c>
       <c r="B84" t="s">
-        <v>126</v>
+        <v>177</v>
       </c>
       <c r="C84">
         <v>0</v>
       </c>
       <c r="D84">
-        <v>65</v>
+        <v>125</v>
       </c>
       <c r="E84" t="s">
-        <v>127</v>
+        <v>178</v>
       </c>
       <c r="F84" t="s">
         <v>6</v>
@@ -2624,16 +2630,16 @@
         <v>98</v>
       </c>
       <c r="B85" t="s">
-        <v>172</v>
+        <v>93</v>
       </c>
       <c r="C85">
         <v>0</v>
       </c>
       <c r="D85">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="E85" t="s">
-        <v>176</v>
+        <v>94</v>
       </c>
       <c r="F85" t="s">
         <v>6</v>
@@ -2644,13 +2650,13 @@
         <v>98</v>
       </c>
       <c r="B86" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="C86">
         <v>0</v>
       </c>
       <c r="D86">
-        <v>85</v>
+        <v>50</v>
       </c>
       <c r="E86" t="s">
         <v>129</v>
@@ -2664,16 +2670,16 @@
         <v>98</v>
       </c>
       <c r="B87" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="C87">
         <v>0</v>
       </c>
       <c r="D87">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="E87" t="s">
-        <v>143</v>
+        <v>129</v>
       </c>
       <c r="F87" t="s">
         <v>6</v>
@@ -2684,16 +2690,16 @@
         <v>98</v>
       </c>
       <c r="B88" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C88">
         <v>0</v>
       </c>
       <c r="D88">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="E88" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F88" t="s">
         <v>6</v>
@@ -2704,18 +2710,38 @@
         <v>98</v>
       </c>
       <c r="B89" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C89">
         <v>0</v>
       </c>
       <c r="D89">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E89" t="s">
         <v>142</v>
       </c>
       <c r="F89" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A90" t="s">
+        <v>98</v>
+      </c>
+      <c r="B90" t="s">
+        <v>140</v>
+      </c>
+      <c r="C90">
+        <v>0</v>
+      </c>
+      <c r="D90">
+        <v>30</v>
+      </c>
+      <c r="E90" t="s">
+        <v>142</v>
+      </c>
+      <c r="F90" t="s">
         <v>6</v>
       </c>
     </row>

--- a/DhalisMenu_cat.xlsx
+++ b/DhalisMenu_cat.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Documents\Custom Office Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2400ACF9-8731-4B31-BCE3-684AC9B24894}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DB2D1BE-3BE8-401E-8A4A-23B666A14479}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1556,7 +1556,7 @@
         <v>0</v>
       </c>
       <c r="D31">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="E31" t="s">
         <v>38</v>

--- a/DhalisMenu_cat.xlsx
+++ b/DhalisMenu_cat.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Documents\Custom Office Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DB2D1BE-3BE8-401E-8A4A-23B666A14479}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B91C1DBB-64E3-4E1C-80DD-7BBD1E5E2B0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$75</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$78</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="186">
   <si>
     <t>Item</t>
   </si>
@@ -563,6 +563,24 @@
   </si>
   <si>
     <t>Thumsup Can 40 rs</t>
+  </si>
+  <si>
+    <t>Glass</t>
+  </si>
+  <si>
+    <t>Disposable Glass.jpeg</t>
+  </si>
+  <si>
+    <t>Glass Packets</t>
+  </si>
+  <si>
+    <t>Maza40</t>
+  </si>
+  <si>
+    <t>Maza50</t>
+  </si>
+  <si>
+    <t>Maza100</t>
   </si>
 </sst>
 </file>
@@ -935,7 +953,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F90"/>
+  <dimension ref="A1:F95"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="8.81640625" bestFit="1" customWidth="1"/>
@@ -2370,16 +2388,16 @@
         <v>98</v>
       </c>
       <c r="B72" t="s">
-        <v>173</v>
+        <v>183</v>
       </c>
       <c r="C72">
         <v>0</v>
       </c>
       <c r="D72">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="E72" t="s">
-        <v>174</v>
+        <v>86</v>
       </c>
       <c r="F72" t="s">
         <v>6</v>
@@ -2390,16 +2408,16 @@
         <v>98</v>
       </c>
       <c r="B73" t="s">
-        <v>87</v>
+        <v>184</v>
       </c>
       <c r="C73">
         <v>0</v>
       </c>
       <c r="D73">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="E73" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F73" t="s">
         <v>6</v>
@@ -2410,16 +2428,16 @@
         <v>98</v>
       </c>
       <c r="B74" t="s">
-        <v>89</v>
+        <v>185</v>
       </c>
       <c r="C74">
         <v>0</v>
       </c>
       <c r="D74">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="E74" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="F74" t="s">
         <v>6</v>
@@ -2430,16 +2448,16 @@
         <v>98</v>
       </c>
       <c r="B75" t="s">
-        <v>96</v>
+        <v>173</v>
       </c>
       <c r="C75">
         <v>0</v>
       </c>
       <c r="D75">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E75" t="s">
-        <v>97</v>
+        <v>174</v>
       </c>
       <c r="F75" t="s">
         <v>6</v>
@@ -2450,7 +2468,7 @@
         <v>98</v>
       </c>
       <c r="B76" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="C76">
         <v>0</v>
@@ -2459,7 +2477,7 @@
         <v>20</v>
       </c>
       <c r="E76" t="s">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="F76" t="s">
         <v>6</v>
@@ -2470,7 +2488,7 @@
         <v>98</v>
       </c>
       <c r="B77" t="s">
-        <v>102</v>
+        <v>89</v>
       </c>
       <c r="C77">
         <v>0</v>
@@ -2479,7 +2497,7 @@
         <v>20</v>
       </c>
       <c r="E77" t="s">
-        <v>104</v>
+        <v>90</v>
       </c>
       <c r="F77" t="s">
         <v>6</v>
@@ -2490,7 +2508,7 @@
         <v>98</v>
       </c>
       <c r="B78" t="s">
-        <v>122</v>
+        <v>96</v>
       </c>
       <c r="C78">
         <v>0</v>
@@ -2499,7 +2517,7 @@
         <v>20</v>
       </c>
       <c r="E78" t="s">
-        <v>123</v>
+        <v>97</v>
       </c>
       <c r="F78" t="s">
         <v>6</v>
@@ -2510,16 +2528,16 @@
         <v>98</v>
       </c>
       <c r="B79" t="s">
-        <v>154</v>
+        <v>101</v>
       </c>
       <c r="C79">
         <v>0</v>
       </c>
       <c r="D79">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E79" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="F79" t="s">
         <v>6</v>
@@ -2530,16 +2548,16 @@
         <v>98</v>
       </c>
       <c r="B80" t="s">
-        <v>179</v>
+        <v>102</v>
       </c>
       <c r="C80">
         <v>0</v>
       </c>
       <c r="D80">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="E80" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="F80" t="s">
         <v>6</v>
@@ -2550,16 +2568,16 @@
         <v>98</v>
       </c>
       <c r="B81" t="s">
-        <v>155</v>
+        <v>122</v>
       </c>
       <c r="C81">
         <v>0</v>
       </c>
       <c r="D81">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="E81" t="s">
-        <v>95</v>
+        <v>123</v>
       </c>
       <c r="F81" t="s">
         <v>6</v>
@@ -2570,16 +2588,16 @@
         <v>98</v>
       </c>
       <c r="B82" t="s">
-        <v>126</v>
+        <v>154</v>
       </c>
       <c r="C82">
         <v>0</v>
       </c>
       <c r="D82">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="E82" t="s">
-        <v>127</v>
+        <v>92</v>
       </c>
       <c r="F82" t="s">
         <v>6</v>
@@ -2590,16 +2608,16 @@
         <v>98</v>
       </c>
       <c r="B83" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="C83">
         <v>0</v>
       </c>
       <c r="D83">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="E83" t="s">
-        <v>175</v>
+        <v>91</v>
       </c>
       <c r="F83" t="s">
         <v>6</v>
@@ -2610,16 +2628,16 @@
         <v>98</v>
       </c>
       <c r="B84" t="s">
-        <v>177</v>
+        <v>155</v>
       </c>
       <c r="C84">
         <v>0</v>
       </c>
       <c r="D84">
-        <v>125</v>
+        <v>35</v>
       </c>
       <c r="E84" t="s">
-        <v>178</v>
+        <v>95</v>
       </c>
       <c r="F84" t="s">
         <v>6</v>
@@ -2630,16 +2648,16 @@
         <v>98</v>
       </c>
       <c r="B85" t="s">
-        <v>93</v>
+        <v>126</v>
       </c>
       <c r="C85">
         <v>0</v>
       </c>
       <c r="D85">
-        <v>35</v>
+        <v>65</v>
       </c>
       <c r="E85" t="s">
-        <v>94</v>
+        <v>127</v>
       </c>
       <c r="F85" t="s">
         <v>6</v>
@@ -2650,16 +2668,16 @@
         <v>98</v>
       </c>
       <c r="B86" t="s">
-        <v>138</v>
+        <v>171</v>
       </c>
       <c r="C86">
         <v>0</v>
       </c>
       <c r="D86">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="E86" t="s">
-        <v>129</v>
+        <v>175</v>
       </c>
       <c r="F86" t="s">
         <v>6</v>
@@ -2670,16 +2688,16 @@
         <v>98</v>
       </c>
       <c r="B87" t="s">
-        <v>128</v>
+        <v>177</v>
       </c>
       <c r="C87">
         <v>0</v>
       </c>
       <c r="D87">
-        <v>85</v>
+        <v>125</v>
       </c>
       <c r="E87" t="s">
-        <v>129</v>
+        <v>178</v>
       </c>
       <c r="F87" t="s">
         <v>6</v>
@@ -2690,16 +2708,16 @@
         <v>98</v>
       </c>
       <c r="B88" t="s">
-        <v>139</v>
+        <v>93</v>
       </c>
       <c r="C88">
         <v>0</v>
       </c>
       <c r="D88">
-        <v>100</v>
+        <v>35</v>
       </c>
       <c r="E88" t="s">
-        <v>143</v>
+        <v>94</v>
       </c>
       <c r="F88" t="s">
         <v>6</v>
@@ -2710,16 +2728,16 @@
         <v>98</v>
       </c>
       <c r="B89" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C89">
         <v>0</v>
       </c>
       <c r="D89">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="E89" t="s">
-        <v>142</v>
+        <v>129</v>
       </c>
       <c r="F89" t="s">
         <v>6</v>
@@ -2730,18 +2748,118 @@
         <v>98</v>
       </c>
       <c r="B90" t="s">
+        <v>128</v>
+      </c>
+      <c r="C90">
+        <v>0</v>
+      </c>
+      <c r="D90">
+        <v>85</v>
+      </c>
+      <c r="E90" t="s">
+        <v>129</v>
+      </c>
+      <c r="F90" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A91" t="s">
+        <v>98</v>
+      </c>
+      <c r="B91" t="s">
+        <v>139</v>
+      </c>
+      <c r="C91">
+        <v>0</v>
+      </c>
+      <c r="D91">
+        <v>100</v>
+      </c>
+      <c r="E91" t="s">
+        <v>143</v>
+      </c>
+      <c r="F91" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A92" t="s">
+        <v>98</v>
+      </c>
+      <c r="B92" t="s">
+        <v>141</v>
+      </c>
+      <c r="C92">
+        <v>0</v>
+      </c>
+      <c r="D92">
+        <v>20</v>
+      </c>
+      <c r="E92" t="s">
+        <v>142</v>
+      </c>
+      <c r="F92" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A93" t="s">
+        <v>98</v>
+      </c>
+      <c r="B93" t="s">
         <v>140</v>
       </c>
-      <c r="C90">
-        <v>0</v>
-      </c>
-      <c r="D90">
+      <c r="C93">
+        <v>0</v>
+      </c>
+      <c r="D93">
         <v>30</v>
       </c>
-      <c r="E90" t="s">
+      <c r="E93" t="s">
         <v>142</v>
       </c>
-      <c r="F90" t="s">
+      <c r="F93" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A94" t="s">
+        <v>98</v>
+      </c>
+      <c r="B94" t="s">
+        <v>180</v>
+      </c>
+      <c r="C94">
+        <v>5</v>
+      </c>
+      <c r="D94">
+        <v>10</v>
+      </c>
+      <c r="E94" t="s">
+        <v>181</v>
+      </c>
+      <c r="F94" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A95" t="s">
+        <v>98</v>
+      </c>
+      <c r="B95" t="s">
+        <v>182</v>
+      </c>
+      <c r="C95">
+        <v>0</v>
+      </c>
+      <c r="D95">
+        <v>40</v>
+      </c>
+      <c r="E95" t="s">
+        <v>181</v>
+      </c>
+      <c r="F95" t="s">
         <v>6</v>
       </c>
     </row>

--- a/DhalisMenu_cat.xlsx
+++ b/DhalisMenu_cat.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Documents\Custom Office Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B91C1DBB-64E3-4E1C-80DD-7BBD1E5E2B0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B355602B-DA3A-4987-A2E4-A6E671608607}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$78</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$79</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="386" uniqueCount="188">
   <si>
     <t>Item</t>
   </si>
@@ -581,6 +581,12 @@
   </si>
   <si>
     <t>Maza100</t>
+  </si>
+  <si>
+    <t>Maza20</t>
+  </si>
+  <si>
+    <t>Maza.jpg</t>
   </si>
 </sst>
 </file>
@@ -953,7 +959,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F95"/>
+  <dimension ref="A1:F96"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="8.81640625" bestFit="1" customWidth="1"/>
@@ -2388,16 +2394,16 @@
         <v>98</v>
       </c>
       <c r="B72" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="C72">
         <v>0</v>
       </c>
       <c r="D72">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="E72" t="s">
-        <v>86</v>
+        <v>187</v>
       </c>
       <c r="F72" t="s">
         <v>6</v>
@@ -2408,16 +2414,16 @@
         <v>98</v>
       </c>
       <c r="B73" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C73">
         <v>0</v>
       </c>
       <c r="D73">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="E73" t="s">
-        <v>86</v>
+        <v>187</v>
       </c>
       <c r="F73" t="s">
         <v>6</v>
@@ -2428,16 +2434,16 @@
         <v>98</v>
       </c>
       <c r="B74" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C74">
         <v>0</v>
       </c>
       <c r="D74">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="E74" t="s">
-        <v>86</v>
+        <v>187</v>
       </c>
       <c r="F74" t="s">
         <v>6</v>
@@ -2448,16 +2454,16 @@
         <v>98</v>
       </c>
       <c r="B75" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="C75">
         <v>0</v>
       </c>
       <c r="D75">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="E75" t="s">
-        <v>174</v>
+        <v>187</v>
       </c>
       <c r="F75" t="s">
         <v>6</v>
@@ -2468,16 +2474,16 @@
         <v>98</v>
       </c>
       <c r="B76" t="s">
-        <v>87</v>
+        <v>173</v>
       </c>
       <c r="C76">
         <v>0</v>
       </c>
       <c r="D76">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E76" t="s">
-        <v>88</v>
+        <v>174</v>
       </c>
       <c r="F76" t="s">
         <v>6</v>
@@ -2488,7 +2494,7 @@
         <v>98</v>
       </c>
       <c r="B77" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C77">
         <v>0</v>
@@ -2497,7 +2503,7 @@
         <v>20</v>
       </c>
       <c r="E77" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F77" t="s">
         <v>6</v>
@@ -2508,7 +2514,7 @@
         <v>98</v>
       </c>
       <c r="B78" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="C78">
         <v>0</v>
@@ -2517,7 +2523,7 @@
         <v>20</v>
       </c>
       <c r="E78" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="F78" t="s">
         <v>6</v>
@@ -2528,7 +2534,7 @@
         <v>98</v>
       </c>
       <c r="B79" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="C79">
         <v>0</v>
@@ -2537,7 +2543,7 @@
         <v>20</v>
       </c>
       <c r="E79" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="F79" t="s">
         <v>6</v>
@@ -2548,7 +2554,7 @@
         <v>98</v>
       </c>
       <c r="B80" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C80">
         <v>0</v>
@@ -2557,7 +2563,7 @@
         <v>20</v>
       </c>
       <c r="E80" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F80" t="s">
         <v>6</v>
@@ -2568,7 +2574,7 @@
         <v>98</v>
       </c>
       <c r="B81" t="s">
-        <v>122</v>
+        <v>102</v>
       </c>
       <c r="C81">
         <v>0</v>
@@ -2577,7 +2583,7 @@
         <v>20</v>
       </c>
       <c r="E81" t="s">
-        <v>123</v>
+        <v>104</v>
       </c>
       <c r="F81" t="s">
         <v>6</v>
@@ -2588,16 +2594,16 @@
         <v>98</v>
       </c>
       <c r="B82" t="s">
-        <v>154</v>
+        <v>122</v>
       </c>
       <c r="C82">
         <v>0</v>
       </c>
       <c r="D82">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E82" t="s">
-        <v>92</v>
+        <v>123</v>
       </c>
       <c r="F82" t="s">
         <v>6</v>
@@ -2608,16 +2614,16 @@
         <v>98</v>
       </c>
       <c r="B83" t="s">
-        <v>179</v>
+        <v>154</v>
       </c>
       <c r="C83">
         <v>0</v>
       </c>
       <c r="D83">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="E83" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F83" t="s">
         <v>6</v>
@@ -2628,16 +2634,16 @@
         <v>98</v>
       </c>
       <c r="B84" t="s">
-        <v>155</v>
+        <v>179</v>
       </c>
       <c r="C84">
         <v>0</v>
       </c>
       <c r="D84">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E84" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="F84" t="s">
         <v>6</v>
@@ -2648,16 +2654,16 @@
         <v>98</v>
       </c>
       <c r="B85" t="s">
-        <v>126</v>
+        <v>155</v>
       </c>
       <c r="C85">
         <v>0</v>
       </c>
       <c r="D85">
-        <v>65</v>
+        <v>35</v>
       </c>
       <c r="E85" t="s">
-        <v>127</v>
+        <v>95</v>
       </c>
       <c r="F85" t="s">
         <v>6</v>
@@ -2668,16 +2674,16 @@
         <v>98</v>
       </c>
       <c r="B86" t="s">
-        <v>171</v>
+        <v>126</v>
       </c>
       <c r="C86">
         <v>0</v>
       </c>
       <c r="D86">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="E86" t="s">
-        <v>175</v>
+        <v>127</v>
       </c>
       <c r="F86" t="s">
         <v>6</v>
@@ -2688,16 +2694,16 @@
         <v>98</v>
       </c>
       <c r="B87" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="C87">
         <v>0</v>
       </c>
       <c r="D87">
-        <v>125</v>
+        <v>60</v>
       </c>
       <c r="E87" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="F87" t="s">
         <v>6</v>
@@ -2708,16 +2714,16 @@
         <v>98</v>
       </c>
       <c r="B88" t="s">
-        <v>93</v>
+        <v>177</v>
       </c>
       <c r="C88">
         <v>0</v>
       </c>
       <c r="D88">
-        <v>35</v>
+        <v>125</v>
       </c>
       <c r="E88" t="s">
-        <v>94</v>
+        <v>178</v>
       </c>
       <c r="F88" t="s">
         <v>6</v>
@@ -2728,16 +2734,16 @@
         <v>98</v>
       </c>
       <c r="B89" t="s">
-        <v>138</v>
+        <v>93</v>
       </c>
       <c r="C89">
         <v>0</v>
       </c>
       <c r="D89">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="E89" t="s">
-        <v>129</v>
+        <v>94</v>
       </c>
       <c r="F89" t="s">
         <v>6</v>
@@ -2748,13 +2754,13 @@
         <v>98</v>
       </c>
       <c r="B90" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="C90">
         <v>0</v>
       </c>
       <c r="D90">
-        <v>85</v>
+        <v>50</v>
       </c>
       <c r="E90" t="s">
         <v>129</v>
@@ -2768,16 +2774,16 @@
         <v>98</v>
       </c>
       <c r="B91" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="C91">
         <v>0</v>
       </c>
       <c r="D91">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="E91" t="s">
-        <v>143</v>
+        <v>129</v>
       </c>
       <c r="F91" t="s">
         <v>6</v>
@@ -2788,16 +2794,16 @@
         <v>98</v>
       </c>
       <c r="B92" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C92">
         <v>0</v>
       </c>
       <c r="D92">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="E92" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F92" t="s">
         <v>6</v>
@@ -2808,13 +2814,13 @@
         <v>98</v>
       </c>
       <c r="B93" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C93">
         <v>0</v>
       </c>
       <c r="D93">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E93" t="s">
         <v>142</v>
@@ -2828,16 +2834,16 @@
         <v>98</v>
       </c>
       <c r="B94" t="s">
-        <v>180</v>
+        <v>140</v>
       </c>
       <c r="C94">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D94">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="E94" t="s">
-        <v>181</v>
+        <v>142</v>
       </c>
       <c r="F94" t="s">
         <v>6</v>
@@ -2848,18 +2854,38 @@
         <v>98</v>
       </c>
       <c r="B95" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C95">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D95">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="E95" t="s">
         <v>181</v>
       </c>
       <c r="F95" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A96" t="s">
+        <v>98</v>
+      </c>
+      <c r="B96" t="s">
+        <v>182</v>
+      </c>
+      <c r="C96">
+        <v>0</v>
+      </c>
+      <c r="D96">
+        <v>40</v>
+      </c>
+      <c r="E96" t="s">
+        <v>181</v>
+      </c>
+      <c r="F96" t="s">
         <v>6</v>
       </c>
     </row>

--- a/DhalisMenu_cat.xlsx
+++ b/DhalisMenu_cat.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Documents\Custom Office Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B355602B-DA3A-4987-A2E4-A6E671608607}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FDDC7EF-C1BE-4082-B977-2997A9237412}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$79</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$76</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
 </workbook>
@@ -2394,16 +2394,16 @@
         <v>98</v>
       </c>
       <c r="B72" t="s">
-        <v>186</v>
+        <v>173</v>
       </c>
       <c r="C72">
         <v>0</v>
       </c>
       <c r="D72">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E72" t="s">
-        <v>187</v>
+        <v>174</v>
       </c>
       <c r="F72" t="s">
         <v>6</v>
@@ -2414,16 +2414,16 @@
         <v>98</v>
       </c>
       <c r="B73" t="s">
-        <v>183</v>
+        <v>87</v>
       </c>
       <c r="C73">
         <v>0</v>
       </c>
       <c r="D73">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="E73" t="s">
-        <v>187</v>
+        <v>88</v>
       </c>
       <c r="F73" t="s">
         <v>6</v>
@@ -2434,16 +2434,16 @@
         <v>98</v>
       </c>
       <c r="B74" t="s">
-        <v>184</v>
+        <v>89</v>
       </c>
       <c r="C74">
         <v>0</v>
       </c>
       <c r="D74">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="E74" t="s">
-        <v>187</v>
+        <v>90</v>
       </c>
       <c r="F74" t="s">
         <v>6</v>
@@ -2454,13 +2454,13 @@
         <v>98</v>
       </c>
       <c r="B75" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C75">
         <v>0</v>
       </c>
       <c r="D75">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="E75" t="s">
         <v>187</v>
@@ -2474,16 +2474,16 @@
         <v>98</v>
       </c>
       <c r="B76" t="s">
-        <v>173</v>
+        <v>96</v>
       </c>
       <c r="C76">
         <v>0</v>
       </c>
       <c r="D76">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E76" t="s">
-        <v>174</v>
+        <v>97</v>
       </c>
       <c r="F76" t="s">
         <v>6</v>
@@ -2494,7 +2494,7 @@
         <v>98</v>
       </c>
       <c r="B77" t="s">
-        <v>87</v>
+        <v>101</v>
       </c>
       <c r="C77">
         <v>0</v>
@@ -2503,7 +2503,7 @@
         <v>20</v>
       </c>
       <c r="E77" t="s">
-        <v>88</v>
+        <v>103</v>
       </c>
       <c r="F77" t="s">
         <v>6</v>
@@ -2514,7 +2514,7 @@
         <v>98</v>
       </c>
       <c r="B78" t="s">
-        <v>89</v>
+        <v>102</v>
       </c>
       <c r="C78">
         <v>0</v>
@@ -2523,7 +2523,7 @@
         <v>20</v>
       </c>
       <c r="E78" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="F78" t="s">
         <v>6</v>
@@ -2534,7 +2534,7 @@
         <v>98</v>
       </c>
       <c r="B79" t="s">
-        <v>96</v>
+        <v>122</v>
       </c>
       <c r="C79">
         <v>0</v>
@@ -2543,7 +2543,7 @@
         <v>20</v>
       </c>
       <c r="E79" t="s">
-        <v>97</v>
+        <v>123</v>
       </c>
       <c r="F79" t="s">
         <v>6</v>
@@ -2554,16 +2554,16 @@
         <v>98</v>
       </c>
       <c r="B80" t="s">
-        <v>101</v>
+        <v>154</v>
       </c>
       <c r="C80">
         <v>0</v>
       </c>
       <c r="D80">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="E80" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="F80" t="s">
         <v>6</v>
@@ -2574,16 +2574,16 @@
         <v>98</v>
       </c>
       <c r="B81" t="s">
-        <v>102</v>
+        <v>179</v>
       </c>
       <c r="C81">
         <v>0</v>
       </c>
       <c r="D81">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="E81" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="F81" t="s">
         <v>6</v>
@@ -2594,16 +2594,16 @@
         <v>98</v>
       </c>
       <c r="B82" t="s">
-        <v>122</v>
+        <v>155</v>
       </c>
       <c r="C82">
         <v>0</v>
       </c>
       <c r="D82">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="E82" t="s">
-        <v>123</v>
+        <v>95</v>
       </c>
       <c r="F82" t="s">
         <v>6</v>
@@ -2614,16 +2614,16 @@
         <v>98</v>
       </c>
       <c r="B83" t="s">
-        <v>154</v>
+        <v>126</v>
       </c>
       <c r="C83">
         <v>0</v>
       </c>
       <c r="D83">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="E83" t="s">
-        <v>92</v>
+        <v>127</v>
       </c>
       <c r="F83" t="s">
         <v>6</v>
@@ -2634,16 +2634,16 @@
         <v>98</v>
       </c>
       <c r="B84" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="C84">
         <v>0</v>
       </c>
       <c r="D84">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="E84" t="s">
-        <v>91</v>
+        <v>175</v>
       </c>
       <c r="F84" t="s">
         <v>6</v>
@@ -2654,16 +2654,16 @@
         <v>98</v>
       </c>
       <c r="B85" t="s">
-        <v>155</v>
+        <v>177</v>
       </c>
       <c r="C85">
         <v>0</v>
       </c>
       <c r="D85">
-        <v>35</v>
+        <v>125</v>
       </c>
       <c r="E85" t="s">
-        <v>95</v>
+        <v>178</v>
       </c>
       <c r="F85" t="s">
         <v>6</v>
@@ -2674,16 +2674,16 @@
         <v>98</v>
       </c>
       <c r="B86" t="s">
-        <v>126</v>
+        <v>93</v>
       </c>
       <c r="C86">
         <v>0</v>
       </c>
       <c r="D86">
-        <v>65</v>
+        <v>35</v>
       </c>
       <c r="E86" t="s">
-        <v>127</v>
+        <v>94</v>
       </c>
       <c r="F86" t="s">
         <v>6</v>
@@ -2694,16 +2694,16 @@
         <v>98</v>
       </c>
       <c r="B87" t="s">
-        <v>171</v>
+        <v>138</v>
       </c>
       <c r="C87">
         <v>0</v>
       </c>
       <c r="D87">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="E87" t="s">
-        <v>175</v>
+        <v>129</v>
       </c>
       <c r="F87" t="s">
         <v>6</v>
@@ -2714,16 +2714,16 @@
         <v>98</v>
       </c>
       <c r="B88" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="C88">
         <v>0</v>
       </c>
       <c r="D88">
-        <v>125</v>
+        <v>40</v>
       </c>
       <c r="E88" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="F88" t="s">
         <v>6</v>
@@ -2734,16 +2734,16 @@
         <v>98</v>
       </c>
       <c r="B89" t="s">
-        <v>93</v>
+        <v>184</v>
       </c>
       <c r="C89">
         <v>0</v>
       </c>
       <c r="D89">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="E89" t="s">
-        <v>94</v>
+        <v>187</v>
       </c>
       <c r="F89" t="s">
         <v>6</v>
@@ -2754,13 +2754,13 @@
         <v>98</v>
       </c>
       <c r="B90" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="C90">
         <v>0</v>
       </c>
       <c r="D90">
-        <v>50</v>
+        <v>85</v>
       </c>
       <c r="E90" t="s">
         <v>129</v>
@@ -2774,16 +2774,16 @@
         <v>98</v>
       </c>
       <c r="B91" t="s">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="C91">
         <v>0</v>
       </c>
       <c r="D91">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="E91" t="s">
-        <v>129</v>
+        <v>143</v>
       </c>
       <c r="F91" t="s">
         <v>6</v>
@@ -2794,7 +2794,7 @@
         <v>98</v>
       </c>
       <c r="B92" t="s">
-        <v>139</v>
+        <v>185</v>
       </c>
       <c r="C92">
         <v>0</v>
@@ -2803,7 +2803,7 @@
         <v>100</v>
       </c>
       <c r="E92" t="s">
-        <v>143</v>
+        <v>187</v>
       </c>
       <c r="F92" t="s">
         <v>6</v>

--- a/DhalisMenu_cat.xlsx
+++ b/DhalisMenu_cat.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Documents\Custom Office Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FDDC7EF-C1BE-4082-B977-2997A9237412}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61614B4B-2B55-42E4-B614-F77E9EE3FE88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$76</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$77</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="386" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="190">
   <si>
     <t>Item</t>
   </si>
@@ -587,6 +587,12 @@
   </si>
   <si>
     <t>Maza.jpg</t>
+  </si>
+  <si>
+    <t>Combo</t>
+  </si>
+  <si>
+    <t>Chat GPT2.png</t>
   </si>
 </sst>
 </file>
@@ -959,7 +965,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F96"/>
+  <dimension ref="A1:F97"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="8.81640625" bestFit="1" customWidth="1"/>
@@ -1294,16 +1300,16 @@
         <v>6</v>
       </c>
       <c r="B17" t="s">
-        <v>9</v>
+        <v>188</v>
       </c>
       <c r="C17">
         <v>0</v>
       </c>
       <c r="D17">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="E17" t="s">
-        <v>10</v>
+        <v>189</v>
       </c>
       <c r="F17" t="s">
         <v>6</v>
@@ -1314,7 +1320,7 @@
         <v>6</v>
       </c>
       <c r="B18" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C18">
         <v>0</v>
@@ -1323,7 +1329,7 @@
         <v>90</v>
       </c>
       <c r="E18" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F18" t="s">
         <v>6</v>
@@ -1334,7 +1340,7 @@
         <v>6</v>
       </c>
       <c r="B19" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C19">
         <v>0</v>
@@ -1343,7 +1349,7 @@
         <v>90</v>
       </c>
       <c r="E19" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F19" t="s">
         <v>6</v>
@@ -1354,7 +1360,7 @@
         <v>6</v>
       </c>
       <c r="B20" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C20">
         <v>0</v>
@@ -1363,7 +1369,7 @@
         <v>90</v>
       </c>
       <c r="E20" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F20" t="s">
         <v>6</v>
@@ -1374,7 +1380,7 @@
         <v>6</v>
       </c>
       <c r="B21" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C21">
         <v>0</v>
@@ -1383,7 +1389,7 @@
         <v>90</v>
       </c>
       <c r="E21" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F21" t="s">
         <v>6</v>
@@ -1394,16 +1400,16 @@
         <v>6</v>
       </c>
       <c r="B22" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C22">
         <v>0</v>
       </c>
       <c r="D22">
-        <v>350</v>
+        <v>90</v>
       </c>
       <c r="E22" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F22" t="s">
         <v>6</v>
@@ -1414,16 +1420,16 @@
         <v>6</v>
       </c>
       <c r="B23" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C23">
         <v>0</v>
       </c>
       <c r="D23">
-        <v>150</v>
+        <v>350</v>
       </c>
       <c r="E23" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F23" t="s">
         <v>6</v>
@@ -1434,7 +1440,7 @@
         <v>6</v>
       </c>
       <c r="B24" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C24">
         <v>0</v>
@@ -1443,7 +1449,7 @@
         <v>150</v>
       </c>
       <c r="E24" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F24" t="s">
         <v>6</v>
@@ -1454,16 +1460,16 @@
         <v>6</v>
       </c>
       <c r="B25" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C25">
         <v>0</v>
       </c>
       <c r="D25">
-        <v>175</v>
+        <v>150</v>
       </c>
       <c r="E25" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F25" t="s">
         <v>6</v>
@@ -1474,16 +1480,16 @@
         <v>6</v>
       </c>
       <c r="B26" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C26">
         <v>0</v>
       </c>
       <c r="D26">
-        <v>200</v>
+        <v>175</v>
       </c>
       <c r="E26" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F26" t="s">
         <v>6</v>
@@ -1494,16 +1500,16 @@
         <v>6</v>
       </c>
       <c r="B27" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C27">
         <v>0</v>
       </c>
       <c r="D27">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="E27" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F27" t="s">
         <v>6</v>
@@ -1514,7 +1520,7 @@
         <v>6</v>
       </c>
       <c r="B28" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C28">
         <v>0</v>
@@ -1523,7 +1529,7 @@
         <v>100</v>
       </c>
       <c r="E28" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F28" t="s">
         <v>6</v>
@@ -1534,16 +1540,16 @@
         <v>6</v>
       </c>
       <c r="B29" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C29">
         <v>0</v>
       </c>
       <c r="D29">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="E29" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F29" t="s">
         <v>6</v>
@@ -1554,16 +1560,16 @@
         <v>6</v>
       </c>
       <c r="B30" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C30">
         <v>0</v>
       </c>
       <c r="D30">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="E30" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F30" t="s">
         <v>6</v>
@@ -1574,16 +1580,16 @@
         <v>6</v>
       </c>
       <c r="B31" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C31">
         <v>0</v>
       </c>
       <c r="D31">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="E31" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F31" t="s">
         <v>6</v>
@@ -1594,16 +1600,16 @@
         <v>6</v>
       </c>
       <c r="B32" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C32">
         <v>0</v>
       </c>
       <c r="D32">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E32" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F32" t="s">
         <v>6</v>
@@ -1614,16 +1620,16 @@
         <v>6</v>
       </c>
       <c r="B33" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C33">
         <v>0</v>
       </c>
       <c r="D33">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="E33" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F33" t="s">
         <v>6</v>
@@ -1631,19 +1637,19 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>99</v>
+        <v>6</v>
       </c>
       <c r="B34" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C34">
         <v>0</v>
       </c>
       <c r="D34">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="E34" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F34" t="s">
         <v>6</v>
@@ -1654,16 +1660,16 @@
         <v>99</v>
       </c>
       <c r="B35" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C35">
         <v>0</v>
       </c>
       <c r="D35">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="E35" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="F35" t="s">
         <v>6</v>
@@ -1674,16 +1680,16 @@
         <v>99</v>
       </c>
       <c r="B36" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C36">
         <v>0</v>
       </c>
       <c r="D36">
-        <v>650</v>
+        <v>40</v>
       </c>
       <c r="E36" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F36" t="s">
         <v>6</v>
@@ -1694,16 +1700,16 @@
         <v>99</v>
       </c>
       <c r="B37" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C37">
         <v>0</v>
       </c>
       <c r="D37">
-        <v>550</v>
+        <v>650</v>
       </c>
       <c r="E37" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F37" t="s">
         <v>6</v>
@@ -1714,16 +1720,16 @@
         <v>99</v>
       </c>
       <c r="B38" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C38">
         <v>0</v>
       </c>
       <c r="D38">
-        <v>600</v>
+        <v>550</v>
       </c>
       <c r="E38" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F38" t="s">
         <v>6</v>
@@ -1734,16 +1740,16 @@
         <v>99</v>
       </c>
       <c r="B39" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C39">
         <v>0</v>
       </c>
       <c r="D39">
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="E39" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F39" t="s">
         <v>6</v>
@@ -1754,16 +1760,16 @@
         <v>99</v>
       </c>
       <c r="B40" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C40">
         <v>0</v>
       </c>
       <c r="D40">
-        <v>550</v>
+        <v>300</v>
       </c>
       <c r="E40" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F40" t="s">
         <v>6</v>
@@ -1774,16 +1780,16 @@
         <v>99</v>
       </c>
       <c r="B41" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C41">
         <v>0</v>
       </c>
       <c r="D41">
-        <v>500</v>
+        <v>550</v>
       </c>
       <c r="E41" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="F41" t="s">
         <v>6</v>
@@ -1791,19 +1797,19 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B42" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C42">
         <v>0</v>
       </c>
       <c r="D42">
-        <v>5</v>
+        <v>500</v>
       </c>
       <c r="E42" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="F42" t="s">
         <v>6</v>
@@ -1814,16 +1820,16 @@
         <v>100</v>
       </c>
       <c r="B43" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C43">
         <v>0</v>
       </c>
       <c r="D43">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E43" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F43" t="s">
         <v>6</v>
@@ -1834,16 +1840,16 @@
         <v>100</v>
       </c>
       <c r="B44" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C44">
         <v>0</v>
       </c>
       <c r="D44">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E44" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F44" t="s">
         <v>6</v>
@@ -1854,16 +1860,16 @@
         <v>100</v>
       </c>
       <c r="B45" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C45">
         <v>0</v>
       </c>
       <c r="D45">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E45" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F45" t="s">
         <v>6</v>
@@ -1874,16 +1880,16 @@
         <v>100</v>
       </c>
       <c r="B46" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C46">
         <v>0</v>
       </c>
       <c r="D46">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E46" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="F46" t="s">
         <v>6</v>
@@ -1894,16 +1900,16 @@
         <v>100</v>
       </c>
       <c r="B47" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C47">
         <v>0</v>
       </c>
       <c r="D47">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E47" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="F47" t="s">
         <v>6</v>
@@ -1914,16 +1920,16 @@
         <v>100</v>
       </c>
       <c r="B48" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C48">
         <v>0</v>
       </c>
       <c r="D48">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E48" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F48" t="s">
         <v>6</v>
@@ -1934,7 +1940,7 @@
         <v>100</v>
       </c>
       <c r="B49" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C49">
         <v>0</v>
@@ -1943,7 +1949,7 @@
         <v>10</v>
       </c>
       <c r="E49" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F49" t="s">
         <v>6</v>
@@ -1954,16 +1960,16 @@
         <v>100</v>
       </c>
       <c r="B50" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C50">
         <v>0</v>
       </c>
       <c r="D50">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="E50" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F50" t="s">
         <v>6</v>
@@ -1974,16 +1980,16 @@
         <v>100</v>
       </c>
       <c r="B51" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C51">
         <v>0</v>
       </c>
       <c r="D51">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="E51" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F51" t="s">
         <v>6</v>
@@ -1994,16 +2000,16 @@
         <v>100</v>
       </c>
       <c r="B52" t="s">
-        <v>116</v>
+        <v>74</v>
       </c>
       <c r="C52">
         <v>0</v>
       </c>
       <c r="D52">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E52" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F52" t="s">
         <v>6</v>
@@ -2014,16 +2020,16 @@
         <v>100</v>
       </c>
       <c r="B53" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C53">
         <v>0</v>
       </c>
       <c r="D53">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="E53" t="s">
-        <v>117</v>
+        <v>76</v>
       </c>
       <c r="F53" t="s">
         <v>6</v>
@@ -2034,16 +2040,16 @@
         <v>100</v>
       </c>
       <c r="B54" t="s">
-        <v>77</v>
+        <v>115</v>
       </c>
       <c r="C54">
         <v>0</v>
       </c>
       <c r="D54">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="E54" t="s">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="F54" t="s">
         <v>6</v>
@@ -2054,16 +2060,16 @@
         <v>100</v>
       </c>
       <c r="B55" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C55">
         <v>0</v>
       </c>
       <c r="D55">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="E55" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F55" t="s">
         <v>6</v>
@@ -2074,16 +2080,16 @@
         <v>100</v>
       </c>
       <c r="B56" t="s">
-        <v>106</v>
+        <v>79</v>
       </c>
       <c r="C56">
         <v>0</v>
       </c>
       <c r="D56">
-        <v>53</v>
+        <v>10</v>
       </c>
       <c r="E56" t="s">
-        <v>105</v>
+        <v>80</v>
       </c>
       <c r="F56" t="s">
         <v>6</v>
@@ -2094,16 +2100,16 @@
         <v>100</v>
       </c>
       <c r="B57" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C57">
         <v>0</v>
       </c>
       <c r="D57">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="E57" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="F57" t="s">
         <v>6</v>
@@ -2114,16 +2120,16 @@
         <v>100</v>
       </c>
       <c r="B58" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C58">
         <v>0</v>
       </c>
       <c r="D58">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="E58" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="F58" t="s">
         <v>6</v>
@@ -2134,7 +2140,7 @@
         <v>100</v>
       </c>
       <c r="B59" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C59">
         <v>0</v>
@@ -2143,7 +2149,7 @@
         <v>52</v>
       </c>
       <c r="E59" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="F59" t="s">
         <v>6</v>
@@ -2154,16 +2160,16 @@
         <v>100</v>
       </c>
       <c r="B60" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="C60">
         <v>0</v>
       </c>
       <c r="D60">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="E60" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="F60" t="s">
         <v>6</v>
@@ -2174,16 +2180,16 @@
         <v>100</v>
       </c>
       <c r="B61" t="s">
-        <v>132</v>
+        <v>118</v>
       </c>
       <c r="C61">
         <v>0</v>
       </c>
       <c r="D61">
-        <v>25</v>
+        <v>57</v>
       </c>
       <c r="E61" t="s">
-        <v>133</v>
+        <v>119</v>
       </c>
       <c r="F61" t="s">
         <v>6</v>
@@ -2194,16 +2200,16 @@
         <v>100</v>
       </c>
       <c r="B62" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C62">
         <v>0</v>
       </c>
       <c r="D62">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="E62" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F62" t="s">
         <v>6</v>
@@ -2214,7 +2220,7 @@
         <v>100</v>
       </c>
       <c r="B63" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="C63">
         <v>0</v>
@@ -2223,7 +2229,7 @@
         <v>10</v>
       </c>
       <c r="E63" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="F63" t="s">
         <v>6</v>
@@ -2234,16 +2240,16 @@
         <v>100</v>
       </c>
       <c r="B64" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="C64">
         <v>0</v>
       </c>
       <c r="D64">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E64" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F64" t="s">
         <v>6</v>
@@ -2254,16 +2260,16 @@
         <v>100</v>
       </c>
       <c r="B65" t="s">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="C65">
         <v>0</v>
       </c>
       <c r="D65">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E65" t="s">
-        <v>121</v>
+        <v>136</v>
       </c>
       <c r="F65" t="s">
         <v>6</v>
@@ -2274,16 +2280,16 @@
         <v>100</v>
       </c>
       <c r="B66" t="s">
-        <v>172</v>
+        <v>120</v>
       </c>
       <c r="C66">
         <v>0</v>
       </c>
       <c r="D66">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="E66" t="s">
-        <v>176</v>
+        <v>121</v>
       </c>
       <c r="F66" t="s">
         <v>6</v>
@@ -2294,16 +2300,16 @@
         <v>100</v>
       </c>
       <c r="B67" t="s">
-        <v>124</v>
+        <v>172</v>
       </c>
       <c r="C67">
         <v>0</v>
       </c>
       <c r="D67">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="E67" t="s">
-        <v>125</v>
+        <v>176</v>
       </c>
       <c r="F67" t="s">
         <v>6</v>
@@ -2314,16 +2320,16 @@
         <v>100</v>
       </c>
       <c r="B68" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="C68">
         <v>0</v>
       </c>
       <c r="D68">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E68" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="F68" t="s">
         <v>6</v>
@@ -2331,19 +2337,19 @@
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B69" t="s">
-        <v>81</v>
+        <v>113</v>
       </c>
       <c r="C69">
         <v>0</v>
       </c>
       <c r="D69">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E69" t="s">
-        <v>82</v>
+        <v>114</v>
       </c>
       <c r="F69" t="s">
         <v>6</v>
@@ -2354,7 +2360,7 @@
         <v>98</v>
       </c>
       <c r="B70" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C70">
         <v>0</v>
@@ -2363,7 +2369,7 @@
         <v>10</v>
       </c>
       <c r="E70" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F70" t="s">
         <v>6</v>
@@ -2374,7 +2380,7 @@
         <v>98</v>
       </c>
       <c r="B71" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C71">
         <v>0</v>
@@ -2383,7 +2389,7 @@
         <v>10</v>
       </c>
       <c r="E71" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F71" t="s">
         <v>6</v>
@@ -2394,7 +2400,7 @@
         <v>98</v>
       </c>
       <c r="B72" t="s">
-        <v>173</v>
+        <v>85</v>
       </c>
       <c r="C72">
         <v>0</v>
@@ -2403,7 +2409,7 @@
         <v>10</v>
       </c>
       <c r="E72" t="s">
-        <v>174</v>
+        <v>86</v>
       </c>
       <c r="F72" t="s">
         <v>6</v>
@@ -2414,16 +2420,16 @@
         <v>98</v>
       </c>
       <c r="B73" t="s">
-        <v>87</v>
+        <v>173</v>
       </c>
       <c r="C73">
         <v>0</v>
       </c>
       <c r="D73">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E73" t="s">
-        <v>88</v>
+        <v>174</v>
       </c>
       <c r="F73" t="s">
         <v>6</v>
@@ -2434,7 +2440,7 @@
         <v>98</v>
       </c>
       <c r="B74" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C74">
         <v>0</v>
@@ -2443,7 +2449,7 @@
         <v>20</v>
       </c>
       <c r="E74" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F74" t="s">
         <v>6</v>
@@ -2454,7 +2460,7 @@
         <v>98</v>
       </c>
       <c r="B75" t="s">
-        <v>186</v>
+        <v>89</v>
       </c>
       <c r="C75">
         <v>0</v>
@@ -2463,7 +2469,7 @@
         <v>20</v>
       </c>
       <c r="E75" t="s">
-        <v>187</v>
+        <v>90</v>
       </c>
       <c r="F75" t="s">
         <v>6</v>
@@ -2474,7 +2480,7 @@
         <v>98</v>
       </c>
       <c r="B76" t="s">
-        <v>96</v>
+        <v>186</v>
       </c>
       <c r="C76">
         <v>0</v>
@@ -2483,7 +2489,7 @@
         <v>20</v>
       </c>
       <c r="E76" t="s">
-        <v>97</v>
+        <v>187</v>
       </c>
       <c r="F76" t="s">
         <v>6</v>
@@ -2494,7 +2500,7 @@
         <v>98</v>
       </c>
       <c r="B77" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="C77">
         <v>0</v>
@@ -2503,7 +2509,7 @@
         <v>20</v>
       </c>
       <c r="E77" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="F77" t="s">
         <v>6</v>
@@ -2514,7 +2520,7 @@
         <v>98</v>
       </c>
       <c r="B78" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C78">
         <v>0</v>
@@ -2523,7 +2529,7 @@
         <v>20</v>
       </c>
       <c r="E78" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F78" t="s">
         <v>6</v>
@@ -2534,7 +2540,7 @@
         <v>98</v>
       </c>
       <c r="B79" t="s">
-        <v>122</v>
+        <v>102</v>
       </c>
       <c r="C79">
         <v>0</v>
@@ -2543,7 +2549,7 @@
         <v>20</v>
       </c>
       <c r="E79" t="s">
-        <v>123</v>
+        <v>104</v>
       </c>
       <c r="F79" t="s">
         <v>6</v>
@@ -2554,16 +2560,16 @@
         <v>98</v>
       </c>
       <c r="B80" t="s">
-        <v>154</v>
+        <v>122</v>
       </c>
       <c r="C80">
         <v>0</v>
       </c>
       <c r="D80">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E80" t="s">
-        <v>92</v>
+        <v>123</v>
       </c>
       <c r="F80" t="s">
         <v>6</v>
@@ -2574,16 +2580,16 @@
         <v>98</v>
       </c>
       <c r="B81" t="s">
-        <v>179</v>
+        <v>154</v>
       </c>
       <c r="C81">
         <v>0</v>
       </c>
       <c r="D81">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="E81" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F81" t="s">
         <v>6</v>
@@ -2594,16 +2600,16 @@
         <v>98</v>
       </c>
       <c r="B82" t="s">
-        <v>155</v>
+        <v>179</v>
       </c>
       <c r="C82">
         <v>0</v>
       </c>
       <c r="D82">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E82" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="F82" t="s">
         <v>6</v>
@@ -2614,16 +2620,16 @@
         <v>98</v>
       </c>
       <c r="B83" t="s">
-        <v>126</v>
+        <v>155</v>
       </c>
       <c r="C83">
         <v>0</v>
       </c>
       <c r="D83">
-        <v>65</v>
+        <v>35</v>
       </c>
       <c r="E83" t="s">
-        <v>127</v>
+        <v>95</v>
       </c>
       <c r="F83" t="s">
         <v>6</v>
@@ -2634,16 +2640,16 @@
         <v>98</v>
       </c>
       <c r="B84" t="s">
-        <v>171</v>
+        <v>126</v>
       </c>
       <c r="C84">
         <v>0</v>
       </c>
       <c r="D84">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="E84" t="s">
-        <v>175</v>
+        <v>127</v>
       </c>
       <c r="F84" t="s">
         <v>6</v>
@@ -2654,16 +2660,16 @@
         <v>98</v>
       </c>
       <c r="B85" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="C85">
         <v>0</v>
       </c>
       <c r="D85">
-        <v>125</v>
+        <v>60</v>
       </c>
       <c r="E85" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="F85" t="s">
         <v>6</v>
@@ -2674,16 +2680,16 @@
         <v>98</v>
       </c>
       <c r="B86" t="s">
-        <v>93</v>
+        <v>177</v>
       </c>
       <c r="C86">
         <v>0</v>
       </c>
       <c r="D86">
-        <v>35</v>
+        <v>125</v>
       </c>
       <c r="E86" t="s">
-        <v>94</v>
+        <v>178</v>
       </c>
       <c r="F86" t="s">
         <v>6</v>
@@ -2694,16 +2700,16 @@
         <v>98</v>
       </c>
       <c r="B87" t="s">
-        <v>138</v>
+        <v>93</v>
       </c>
       <c r="C87">
         <v>0</v>
       </c>
       <c r="D87">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="E87" t="s">
-        <v>129</v>
+        <v>94</v>
       </c>
       <c r="F87" t="s">
         <v>6</v>
@@ -2714,16 +2720,16 @@
         <v>98</v>
       </c>
       <c r="B88" t="s">
-        <v>183</v>
+        <v>138</v>
       </c>
       <c r="C88">
         <v>0</v>
       </c>
       <c r="D88">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="E88" t="s">
-        <v>187</v>
+        <v>129</v>
       </c>
       <c r="F88" t="s">
         <v>6</v>
@@ -2734,13 +2740,13 @@
         <v>98</v>
       </c>
       <c r="B89" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C89">
         <v>0</v>
       </c>
       <c r="D89">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="E89" t="s">
         <v>187</v>
@@ -2754,16 +2760,16 @@
         <v>98</v>
       </c>
       <c r="B90" t="s">
-        <v>128</v>
+        <v>184</v>
       </c>
       <c r="C90">
         <v>0</v>
       </c>
       <c r="D90">
-        <v>85</v>
+        <v>50</v>
       </c>
       <c r="E90" t="s">
-        <v>129</v>
+        <v>187</v>
       </c>
       <c r="F90" t="s">
         <v>6</v>
@@ -2774,16 +2780,16 @@
         <v>98</v>
       </c>
       <c r="B91" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="C91">
         <v>0</v>
       </c>
       <c r="D91">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="E91" t="s">
-        <v>143</v>
+        <v>129</v>
       </c>
       <c r="F91" t="s">
         <v>6</v>
@@ -2794,7 +2800,7 @@
         <v>98</v>
       </c>
       <c r="B92" t="s">
-        <v>185</v>
+        <v>139</v>
       </c>
       <c r="C92">
         <v>0</v>
@@ -2803,7 +2809,7 @@
         <v>100</v>
       </c>
       <c r="E92" t="s">
-        <v>187</v>
+        <v>143</v>
       </c>
       <c r="F92" t="s">
         <v>6</v>
@@ -2814,16 +2820,16 @@
         <v>98</v>
       </c>
       <c r="B93" t="s">
-        <v>141</v>
+        <v>185</v>
       </c>
       <c r="C93">
         <v>0</v>
       </c>
       <c r="D93">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="E93" t="s">
-        <v>142</v>
+        <v>187</v>
       </c>
       <c r="F93" t="s">
         <v>6</v>
@@ -2834,13 +2840,13 @@
         <v>98</v>
       </c>
       <c r="B94" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C94">
         <v>0</v>
       </c>
       <c r="D94">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E94" t="s">
         <v>142</v>
@@ -2854,16 +2860,16 @@
         <v>98</v>
       </c>
       <c r="B95" t="s">
-        <v>180</v>
+        <v>140</v>
       </c>
       <c r="C95">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D95">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="E95" t="s">
-        <v>181</v>
+        <v>142</v>
       </c>
       <c r="F95" t="s">
         <v>6</v>
@@ -2874,18 +2880,38 @@
         <v>98</v>
       </c>
       <c r="B96" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C96">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D96">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="E96" t="s">
         <v>181</v>
       </c>
       <c r="F96" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A97" t="s">
+        <v>98</v>
+      </c>
+      <c r="B97" t="s">
+        <v>182</v>
+      </c>
+      <c r="C97">
+        <v>0</v>
+      </c>
+      <c r="D97">
+        <v>40</v>
+      </c>
+      <c r="E97" t="s">
+        <v>181</v>
+      </c>
+      <c r="F97" t="s">
         <v>6</v>
       </c>
     </row>

--- a/DhalisMenu_cat.xlsx
+++ b/DhalisMenu_cat.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Documents\Custom Office Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61614B4B-2B55-42E4-B614-F77E9EE3FE88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9D5E094-C4B6-45E3-BA6E-A1F5EAADC3F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="191">
   <si>
     <t>Item</t>
   </si>
@@ -593,6 +593,9 @@
   </si>
   <si>
     <t>Chat GPT2.png</t>
+  </si>
+  <si>
+    <t>Water Bottle 10</t>
   </si>
 </sst>
 </file>
@@ -965,7 +968,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F97"/>
+  <dimension ref="A1:F98"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="8.81640625" bestFit="1" customWidth="1"/>
@@ -1006,7 +1009,7 @@
         <v>0</v>
       </c>
       <c r="D2">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
@@ -1026,7 +1029,7 @@
         <v>0</v>
       </c>
       <c r="D3">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="E3" t="s">
         <v>7</v>
@@ -2840,13 +2843,13 @@
         <v>98</v>
       </c>
       <c r="B94" t="s">
-        <v>141</v>
+        <v>190</v>
       </c>
       <c r="C94">
         <v>0</v>
       </c>
       <c r="D94">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E94" t="s">
         <v>142</v>
@@ -2860,13 +2863,13 @@
         <v>98</v>
       </c>
       <c r="B95" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C95">
         <v>0</v>
       </c>
       <c r="D95">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E95" t="s">
         <v>142</v>
@@ -2880,16 +2883,16 @@
         <v>98</v>
       </c>
       <c r="B96" t="s">
-        <v>180</v>
+        <v>140</v>
       </c>
       <c r="C96">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D96">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="E96" t="s">
-        <v>181</v>
+        <v>142</v>
       </c>
       <c r="F96" t="s">
         <v>6</v>
@@ -2900,18 +2903,38 @@
         <v>98</v>
       </c>
       <c r="B97" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C97">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D97">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="E97" t="s">
         <v>181</v>
       </c>
       <c r="F97" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A98" t="s">
+        <v>98</v>
+      </c>
+      <c r="B98" t="s">
+        <v>182</v>
+      </c>
+      <c r="C98">
+        <v>0</v>
+      </c>
+      <c r="D98">
+        <v>40</v>
+      </c>
+      <c r="E98" t="s">
+        <v>181</v>
+      </c>
+      <c r="F98" t="s">
         <v>6</v>
       </c>
     </row>

--- a/DhalisMenu_cat.xlsx
+++ b/DhalisMenu_cat.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Documents\Custom Office Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9D5E094-C4B6-45E3-BA6E-A1F5EAADC3F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{327BC888-E25B-4CD1-9426-83065ED9729B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,14 +16,14 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$77</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$78</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="398" uniqueCount="193">
   <si>
     <t>Item</t>
   </si>
@@ -596,6 +596,12 @@
   </si>
   <si>
     <t>Water Bottle 10</t>
+  </si>
+  <si>
+    <t>Maggi 15rs</t>
+  </si>
+  <si>
+    <t>Maggi.jpg</t>
   </si>
 </sst>
 </file>
@@ -968,7 +974,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F98"/>
+  <dimension ref="A1:F99"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="8.81640625" bestFit="1" customWidth="1"/>
@@ -2103,16 +2109,16 @@
         <v>100</v>
       </c>
       <c r="B57" t="s">
-        <v>106</v>
+        <v>191</v>
       </c>
       <c r="C57">
         <v>0</v>
       </c>
       <c r="D57">
-        <v>53</v>
+        <v>15</v>
       </c>
       <c r="E57" t="s">
-        <v>105</v>
+        <v>192</v>
       </c>
       <c r="F57" t="s">
         <v>6</v>
@@ -2123,16 +2129,16 @@
         <v>100</v>
       </c>
       <c r="B58" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C58">
         <v>0</v>
       </c>
       <c r="D58">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="E58" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="F58" t="s">
         <v>6</v>
@@ -2143,16 +2149,16 @@
         <v>100</v>
       </c>
       <c r="B59" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C59">
         <v>0</v>
       </c>
       <c r="D59">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="E59" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="F59" t="s">
         <v>6</v>
@@ -2163,7 +2169,7 @@
         <v>100</v>
       </c>
       <c r="B60" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C60">
         <v>0</v>
@@ -2172,7 +2178,7 @@
         <v>52</v>
       </c>
       <c r="E60" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="F60" t="s">
         <v>6</v>
@@ -2183,16 +2189,16 @@
         <v>100</v>
       </c>
       <c r="B61" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="C61">
         <v>0</v>
       </c>
       <c r="D61">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="E61" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="F61" t="s">
         <v>6</v>
@@ -2203,16 +2209,16 @@
         <v>100</v>
       </c>
       <c r="B62" t="s">
-        <v>132</v>
+        <v>118</v>
       </c>
       <c r="C62">
         <v>0</v>
       </c>
       <c r="D62">
-        <v>25</v>
+        <v>57</v>
       </c>
       <c r="E62" t="s">
-        <v>133</v>
+        <v>119</v>
       </c>
       <c r="F62" t="s">
         <v>6</v>
@@ -2223,16 +2229,16 @@
         <v>100</v>
       </c>
       <c r="B63" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C63">
         <v>0</v>
       </c>
       <c r="D63">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="E63" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F63" t="s">
         <v>6</v>
@@ -2243,7 +2249,7 @@
         <v>100</v>
       </c>
       <c r="B64" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="C64">
         <v>0</v>
@@ -2252,7 +2258,7 @@
         <v>10</v>
       </c>
       <c r="E64" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="F64" t="s">
         <v>6</v>
@@ -2263,16 +2269,16 @@
         <v>100</v>
       </c>
       <c r="B65" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="C65">
         <v>0</v>
       </c>
       <c r="D65">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E65" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F65" t="s">
         <v>6</v>
@@ -2283,16 +2289,16 @@
         <v>100</v>
       </c>
       <c r="B66" t="s">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="C66">
         <v>0</v>
       </c>
       <c r="D66">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E66" t="s">
-        <v>121</v>
+        <v>136</v>
       </c>
       <c r="F66" t="s">
         <v>6</v>
@@ -2303,16 +2309,16 @@
         <v>100</v>
       </c>
       <c r="B67" t="s">
-        <v>172</v>
+        <v>120</v>
       </c>
       <c r="C67">
         <v>0</v>
       </c>
       <c r="D67">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="E67" t="s">
-        <v>176</v>
+        <v>121</v>
       </c>
       <c r="F67" t="s">
         <v>6</v>
@@ -2323,16 +2329,16 @@
         <v>100</v>
       </c>
       <c r="B68" t="s">
-        <v>124</v>
+        <v>172</v>
       </c>
       <c r="C68">
         <v>0</v>
       </c>
       <c r="D68">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="E68" t="s">
-        <v>125</v>
+        <v>176</v>
       </c>
       <c r="F68" t="s">
         <v>6</v>
@@ -2343,16 +2349,16 @@
         <v>100</v>
       </c>
       <c r="B69" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="C69">
         <v>0</v>
       </c>
       <c r="D69">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E69" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="F69" t="s">
         <v>6</v>
@@ -2360,19 +2366,19 @@
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B70" t="s">
-        <v>81</v>
+        <v>113</v>
       </c>
       <c r="C70">
         <v>0</v>
       </c>
       <c r="D70">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E70" t="s">
-        <v>82</v>
+        <v>114</v>
       </c>
       <c r="F70" t="s">
         <v>6</v>
@@ -2383,7 +2389,7 @@
         <v>98</v>
       </c>
       <c r="B71" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C71">
         <v>0</v>
@@ -2392,7 +2398,7 @@
         <v>10</v>
       </c>
       <c r="E71" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F71" t="s">
         <v>6</v>
@@ -2403,7 +2409,7 @@
         <v>98</v>
       </c>
       <c r="B72" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C72">
         <v>0</v>
@@ -2412,7 +2418,7 @@
         <v>10</v>
       </c>
       <c r="E72" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F72" t="s">
         <v>6</v>
@@ -2423,7 +2429,7 @@
         <v>98</v>
       </c>
       <c r="B73" t="s">
-        <v>173</v>
+        <v>85</v>
       </c>
       <c r="C73">
         <v>0</v>
@@ -2432,7 +2438,7 @@
         <v>10</v>
       </c>
       <c r="E73" t="s">
-        <v>174</v>
+        <v>86</v>
       </c>
       <c r="F73" t="s">
         <v>6</v>
@@ -2443,16 +2449,16 @@
         <v>98</v>
       </c>
       <c r="B74" t="s">
-        <v>87</v>
+        <v>173</v>
       </c>
       <c r="C74">
         <v>0</v>
       </c>
       <c r="D74">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E74" t="s">
-        <v>88</v>
+        <v>174</v>
       </c>
       <c r="F74" t="s">
         <v>6</v>
@@ -2463,7 +2469,7 @@
         <v>98</v>
       </c>
       <c r="B75" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C75">
         <v>0</v>
@@ -2472,7 +2478,7 @@
         <v>20</v>
       </c>
       <c r="E75" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F75" t="s">
         <v>6</v>
@@ -2483,7 +2489,7 @@
         <v>98</v>
       </c>
       <c r="B76" t="s">
-        <v>186</v>
+        <v>89</v>
       </c>
       <c r="C76">
         <v>0</v>
@@ -2492,7 +2498,7 @@
         <v>20</v>
       </c>
       <c r="E76" t="s">
-        <v>187</v>
+        <v>90</v>
       </c>
       <c r="F76" t="s">
         <v>6</v>
@@ -2503,7 +2509,7 @@
         <v>98</v>
       </c>
       <c r="B77" t="s">
-        <v>96</v>
+        <v>186</v>
       </c>
       <c r="C77">
         <v>0</v>
@@ -2512,7 +2518,7 @@
         <v>20</v>
       </c>
       <c r="E77" t="s">
-        <v>97</v>
+        <v>187</v>
       </c>
       <c r="F77" t="s">
         <v>6</v>
@@ -2523,7 +2529,7 @@
         <v>98</v>
       </c>
       <c r="B78" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="C78">
         <v>0</v>
@@ -2532,7 +2538,7 @@
         <v>20</v>
       </c>
       <c r="E78" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="F78" t="s">
         <v>6</v>
@@ -2543,7 +2549,7 @@
         <v>98</v>
       </c>
       <c r="B79" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C79">
         <v>0</v>
@@ -2552,7 +2558,7 @@
         <v>20</v>
       </c>
       <c r="E79" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F79" t="s">
         <v>6</v>
@@ -2563,7 +2569,7 @@
         <v>98</v>
       </c>
       <c r="B80" t="s">
-        <v>122</v>
+        <v>102</v>
       </c>
       <c r="C80">
         <v>0</v>
@@ -2572,7 +2578,7 @@
         <v>20</v>
       </c>
       <c r="E80" t="s">
-        <v>123</v>
+        <v>104</v>
       </c>
       <c r="F80" t="s">
         <v>6</v>
@@ -2583,16 +2589,16 @@
         <v>98</v>
       </c>
       <c r="B81" t="s">
-        <v>154</v>
+        <v>122</v>
       </c>
       <c r="C81">
         <v>0</v>
       </c>
       <c r="D81">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E81" t="s">
-        <v>92</v>
+        <v>123</v>
       </c>
       <c r="F81" t="s">
         <v>6</v>
@@ -2603,16 +2609,16 @@
         <v>98</v>
       </c>
       <c r="B82" t="s">
-        <v>179</v>
+        <v>154</v>
       </c>
       <c r="C82">
         <v>0</v>
       </c>
       <c r="D82">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="E82" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F82" t="s">
         <v>6</v>
@@ -2623,16 +2629,16 @@
         <v>98</v>
       </c>
       <c r="B83" t="s">
-        <v>155</v>
+        <v>179</v>
       </c>
       <c r="C83">
         <v>0</v>
       </c>
       <c r="D83">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E83" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="F83" t="s">
         <v>6</v>
@@ -2643,16 +2649,16 @@
         <v>98</v>
       </c>
       <c r="B84" t="s">
-        <v>126</v>
+        <v>155</v>
       </c>
       <c r="C84">
         <v>0</v>
       </c>
       <c r="D84">
-        <v>65</v>
+        <v>35</v>
       </c>
       <c r="E84" t="s">
-        <v>127</v>
+        <v>95</v>
       </c>
       <c r="F84" t="s">
         <v>6</v>
@@ -2663,16 +2669,16 @@
         <v>98</v>
       </c>
       <c r="B85" t="s">
-        <v>171</v>
+        <v>126</v>
       </c>
       <c r="C85">
         <v>0</v>
       </c>
       <c r="D85">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="E85" t="s">
-        <v>175</v>
+        <v>127</v>
       </c>
       <c r="F85" t="s">
         <v>6</v>
@@ -2683,16 +2689,16 @@
         <v>98</v>
       </c>
       <c r="B86" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="C86">
         <v>0</v>
       </c>
       <c r="D86">
-        <v>125</v>
+        <v>60</v>
       </c>
       <c r="E86" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="F86" t="s">
         <v>6</v>
@@ -2703,16 +2709,16 @@
         <v>98</v>
       </c>
       <c r="B87" t="s">
-        <v>93</v>
+        <v>177</v>
       </c>
       <c r="C87">
         <v>0</v>
       </c>
       <c r="D87">
-        <v>35</v>
+        <v>125</v>
       </c>
       <c r="E87" t="s">
-        <v>94</v>
+        <v>178</v>
       </c>
       <c r="F87" t="s">
         <v>6</v>
@@ -2723,16 +2729,16 @@
         <v>98</v>
       </c>
       <c r="B88" t="s">
-        <v>138</v>
+        <v>93</v>
       </c>
       <c r="C88">
         <v>0</v>
       </c>
       <c r="D88">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="E88" t="s">
-        <v>129</v>
+        <v>94</v>
       </c>
       <c r="F88" t="s">
         <v>6</v>
@@ -2743,16 +2749,16 @@
         <v>98</v>
       </c>
       <c r="B89" t="s">
-        <v>183</v>
+        <v>138</v>
       </c>
       <c r="C89">
         <v>0</v>
       </c>
       <c r="D89">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="E89" t="s">
-        <v>187</v>
+        <v>129</v>
       </c>
       <c r="F89" t="s">
         <v>6</v>
@@ -2763,13 +2769,13 @@
         <v>98</v>
       </c>
       <c r="B90" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C90">
         <v>0</v>
       </c>
       <c r="D90">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="E90" t="s">
         <v>187</v>
@@ -2783,16 +2789,16 @@
         <v>98</v>
       </c>
       <c r="B91" t="s">
-        <v>128</v>
+        <v>184</v>
       </c>
       <c r="C91">
         <v>0</v>
       </c>
       <c r="D91">
-        <v>85</v>
+        <v>50</v>
       </c>
       <c r="E91" t="s">
-        <v>129</v>
+        <v>187</v>
       </c>
       <c r="F91" t="s">
         <v>6</v>
@@ -2803,16 +2809,16 @@
         <v>98</v>
       </c>
       <c r="B92" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="C92">
         <v>0</v>
       </c>
       <c r="D92">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="E92" t="s">
-        <v>143</v>
+        <v>129</v>
       </c>
       <c r="F92" t="s">
         <v>6</v>
@@ -2823,7 +2829,7 @@
         <v>98</v>
       </c>
       <c r="B93" t="s">
-        <v>185</v>
+        <v>139</v>
       </c>
       <c r="C93">
         <v>0</v>
@@ -2832,7 +2838,7 @@
         <v>100</v>
       </c>
       <c r="E93" t="s">
-        <v>187</v>
+        <v>143</v>
       </c>
       <c r="F93" t="s">
         <v>6</v>
@@ -2843,16 +2849,16 @@
         <v>98</v>
       </c>
       <c r="B94" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="C94">
         <v>0</v>
       </c>
       <c r="D94">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="E94" t="s">
-        <v>142</v>
+        <v>187</v>
       </c>
       <c r="F94" t="s">
         <v>6</v>
@@ -2863,13 +2869,13 @@
         <v>98</v>
       </c>
       <c r="B95" t="s">
-        <v>141</v>
+        <v>190</v>
       </c>
       <c r="C95">
         <v>0</v>
       </c>
       <c r="D95">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E95" t="s">
         <v>142</v>
@@ -2883,13 +2889,13 @@
         <v>98</v>
       </c>
       <c r="B96" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C96">
         <v>0</v>
       </c>
       <c r="D96">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E96" t="s">
         <v>142</v>
@@ -2903,16 +2909,16 @@
         <v>98</v>
       </c>
       <c r="B97" t="s">
-        <v>180</v>
+        <v>140</v>
       </c>
       <c r="C97">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D97">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="E97" t="s">
-        <v>181</v>
+        <v>142</v>
       </c>
       <c r="F97" t="s">
         <v>6</v>
@@ -2923,18 +2929,38 @@
         <v>98</v>
       </c>
       <c r="B98" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C98">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D98">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="E98" t="s">
         <v>181</v>
       </c>
       <c r="F98" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A99" t="s">
+        <v>98</v>
+      </c>
+      <c r="B99" t="s">
+        <v>182</v>
+      </c>
+      <c r="C99">
+        <v>0</v>
+      </c>
+      <c r="D99">
+        <v>40</v>
+      </c>
+      <c r="E99" t="s">
+        <v>181</v>
+      </c>
+      <c r="F99" t="s">
         <v>6</v>
       </c>
     </row>

--- a/DhalisMenu_cat.xlsx
+++ b/DhalisMenu_cat.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Documents\Custom Office Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{327BC888-E25B-4CD1-9426-83065ED9729B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DD2F75C-3FF0-4C4B-84EE-A8D553B829EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$78</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$79</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
 </workbook>
@@ -2389,7 +2389,7 @@
         <v>98</v>
       </c>
       <c r="B71" t="s">
-        <v>81</v>
+        <v>190</v>
       </c>
       <c r="C71">
         <v>0</v>
@@ -2398,7 +2398,7 @@
         <v>10</v>
       </c>
       <c r="E71" t="s">
-        <v>82</v>
+        <v>142</v>
       </c>
       <c r="F71" t="s">
         <v>6</v>
@@ -2409,7 +2409,7 @@
         <v>98</v>
       </c>
       <c r="B72" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C72">
         <v>0</v>
@@ -2418,7 +2418,7 @@
         <v>10</v>
       </c>
       <c r="E72" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F72" t="s">
         <v>6</v>
@@ -2429,7 +2429,7 @@
         <v>98</v>
       </c>
       <c r="B73" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C73">
         <v>0</v>
@@ -2438,7 +2438,7 @@
         <v>10</v>
       </c>
       <c r="E73" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F73" t="s">
         <v>6</v>
@@ -2449,7 +2449,7 @@
         <v>98</v>
       </c>
       <c r="B74" t="s">
-        <v>173</v>
+        <v>85</v>
       </c>
       <c r="C74">
         <v>0</v>
@@ -2458,7 +2458,7 @@
         <v>10</v>
       </c>
       <c r="E74" t="s">
-        <v>174</v>
+        <v>86</v>
       </c>
       <c r="F74" t="s">
         <v>6</v>
@@ -2469,16 +2469,16 @@
         <v>98</v>
       </c>
       <c r="B75" t="s">
-        <v>87</v>
+        <v>173</v>
       </c>
       <c r="C75">
         <v>0</v>
       </c>
       <c r="D75">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E75" t="s">
-        <v>88</v>
+        <v>174</v>
       </c>
       <c r="F75" t="s">
         <v>6</v>
@@ -2489,7 +2489,7 @@
         <v>98</v>
       </c>
       <c r="B76" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C76">
         <v>0</v>
@@ -2498,7 +2498,7 @@
         <v>20</v>
       </c>
       <c r="E76" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F76" t="s">
         <v>6</v>
@@ -2509,7 +2509,7 @@
         <v>98</v>
       </c>
       <c r="B77" t="s">
-        <v>186</v>
+        <v>89</v>
       </c>
       <c r="C77">
         <v>0</v>
@@ -2518,7 +2518,7 @@
         <v>20</v>
       </c>
       <c r="E77" t="s">
-        <v>187</v>
+        <v>90</v>
       </c>
       <c r="F77" t="s">
         <v>6</v>
@@ -2529,7 +2529,7 @@
         <v>98</v>
       </c>
       <c r="B78" t="s">
-        <v>96</v>
+        <v>186</v>
       </c>
       <c r="C78">
         <v>0</v>
@@ -2538,7 +2538,7 @@
         <v>20</v>
       </c>
       <c r="E78" t="s">
-        <v>97</v>
+        <v>187</v>
       </c>
       <c r="F78" t="s">
         <v>6</v>
@@ -2549,7 +2549,7 @@
         <v>98</v>
       </c>
       <c r="B79" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="C79">
         <v>0</v>
@@ -2558,7 +2558,7 @@
         <v>20</v>
       </c>
       <c r="E79" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="F79" t="s">
         <v>6</v>
@@ -2569,7 +2569,7 @@
         <v>98</v>
       </c>
       <c r="B80" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C80">
         <v>0</v>
@@ -2578,7 +2578,7 @@
         <v>20</v>
       </c>
       <c r="E80" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F80" t="s">
         <v>6</v>
@@ -2589,7 +2589,7 @@
         <v>98</v>
       </c>
       <c r="B81" t="s">
-        <v>122</v>
+        <v>102</v>
       </c>
       <c r="C81">
         <v>0</v>
@@ -2598,7 +2598,7 @@
         <v>20</v>
       </c>
       <c r="E81" t="s">
-        <v>123</v>
+        <v>104</v>
       </c>
       <c r="F81" t="s">
         <v>6</v>
@@ -2609,16 +2609,16 @@
         <v>98</v>
       </c>
       <c r="B82" t="s">
-        <v>154</v>
+        <v>122</v>
       </c>
       <c r="C82">
         <v>0</v>
       </c>
       <c r="D82">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E82" t="s">
-        <v>92</v>
+        <v>123</v>
       </c>
       <c r="F82" t="s">
         <v>6</v>
@@ -2629,16 +2629,16 @@
         <v>98</v>
       </c>
       <c r="B83" t="s">
-        <v>179</v>
+        <v>154</v>
       </c>
       <c r="C83">
         <v>0</v>
       </c>
       <c r="D83">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="E83" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F83" t="s">
         <v>6</v>
@@ -2649,16 +2649,16 @@
         <v>98</v>
       </c>
       <c r="B84" t="s">
-        <v>155</v>
+        <v>179</v>
       </c>
       <c r="C84">
         <v>0</v>
       </c>
       <c r="D84">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E84" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="F84" t="s">
         <v>6</v>
@@ -2669,16 +2669,16 @@
         <v>98</v>
       </c>
       <c r="B85" t="s">
-        <v>126</v>
+        <v>155</v>
       </c>
       <c r="C85">
         <v>0</v>
       </c>
       <c r="D85">
-        <v>65</v>
+        <v>35</v>
       </c>
       <c r="E85" t="s">
-        <v>127</v>
+        <v>95</v>
       </c>
       <c r="F85" t="s">
         <v>6</v>
@@ -2689,16 +2689,16 @@
         <v>98</v>
       </c>
       <c r="B86" t="s">
-        <v>171</v>
+        <v>126</v>
       </c>
       <c r="C86">
         <v>0</v>
       </c>
       <c r="D86">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="E86" t="s">
-        <v>175</v>
+        <v>127</v>
       </c>
       <c r="F86" t="s">
         <v>6</v>
@@ -2709,16 +2709,16 @@
         <v>98</v>
       </c>
       <c r="B87" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="C87">
         <v>0</v>
       </c>
       <c r="D87">
-        <v>125</v>
+        <v>60</v>
       </c>
       <c r="E87" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="F87" t="s">
         <v>6</v>
@@ -2729,16 +2729,16 @@
         <v>98</v>
       </c>
       <c r="B88" t="s">
-        <v>93</v>
+        <v>177</v>
       </c>
       <c r="C88">
         <v>0</v>
       </c>
       <c r="D88">
-        <v>35</v>
+        <v>125</v>
       </c>
       <c r="E88" t="s">
-        <v>94</v>
+        <v>178</v>
       </c>
       <c r="F88" t="s">
         <v>6</v>
@@ -2749,16 +2749,16 @@
         <v>98</v>
       </c>
       <c r="B89" t="s">
-        <v>138</v>
+        <v>93</v>
       </c>
       <c r="C89">
         <v>0</v>
       </c>
       <c r="D89">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="E89" t="s">
-        <v>129</v>
+        <v>94</v>
       </c>
       <c r="F89" t="s">
         <v>6</v>
@@ -2769,16 +2769,16 @@
         <v>98</v>
       </c>
       <c r="B90" t="s">
-        <v>183</v>
+        <v>138</v>
       </c>
       <c r="C90">
         <v>0</v>
       </c>
       <c r="D90">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="E90" t="s">
-        <v>187</v>
+        <v>129</v>
       </c>
       <c r="F90" t="s">
         <v>6</v>
@@ -2789,13 +2789,13 @@
         <v>98</v>
       </c>
       <c r="B91" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C91">
         <v>0</v>
       </c>
       <c r="D91">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="E91" t="s">
         <v>187</v>
@@ -2809,16 +2809,16 @@
         <v>98</v>
       </c>
       <c r="B92" t="s">
-        <v>128</v>
+        <v>184</v>
       </c>
       <c r="C92">
         <v>0</v>
       </c>
       <c r="D92">
-        <v>85</v>
+        <v>50</v>
       </c>
       <c r="E92" t="s">
-        <v>129</v>
+        <v>187</v>
       </c>
       <c r="F92" t="s">
         <v>6</v>
@@ -2829,16 +2829,16 @@
         <v>98</v>
       </c>
       <c r="B93" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="C93">
         <v>0</v>
       </c>
       <c r="D93">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="E93" t="s">
-        <v>143</v>
+        <v>129</v>
       </c>
       <c r="F93" t="s">
         <v>6</v>
@@ -2849,7 +2849,7 @@
         <v>98</v>
       </c>
       <c r="B94" t="s">
-        <v>185</v>
+        <v>139</v>
       </c>
       <c r="C94">
         <v>0</v>
@@ -2858,7 +2858,7 @@
         <v>100</v>
       </c>
       <c r="E94" t="s">
-        <v>187</v>
+        <v>143</v>
       </c>
       <c r="F94" t="s">
         <v>6</v>
@@ -2869,16 +2869,16 @@
         <v>98</v>
       </c>
       <c r="B95" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="C95">
         <v>0</v>
       </c>
       <c r="D95">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="E95" t="s">
-        <v>142</v>
+        <v>187</v>
       </c>
       <c r="F95" t="s">
         <v>6</v>

--- a/DhalisMenu_cat.xlsx
+++ b/DhalisMenu_cat.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Documents\Custom Office Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DD2F75C-3FF0-4C4B-84EE-A8D553B829EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F259F666-5E35-4362-A9ED-0C11C9490B9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="398" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="194">
   <si>
     <t>Item</t>
   </si>
@@ -602,6 +602,9 @@
   </si>
   <si>
     <t>Maggi.jpg</t>
+  </si>
+  <si>
+    <t>Glass Single</t>
   </si>
 </sst>
 </file>
@@ -974,7 +977,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F99"/>
+  <dimension ref="A1:F100"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="8.81640625" bestFit="1" customWidth="1"/>
@@ -2964,6 +2967,26 @@
         <v>6</v>
       </c>
     </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A100" t="s">
+        <v>98</v>
+      </c>
+      <c r="B100" t="s">
+        <v>193</v>
+      </c>
+      <c r="C100">
+        <v>0</v>
+      </c>
+      <c r="D100">
+        <v>1</v>
+      </c>
+      <c r="E100" t="s">
+        <v>181</v>
+      </c>
+      <c r="F100" t="s">
+        <v>6</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/DhalisMenu_cat.xlsx
+++ b/DhalisMenu_cat.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dell\Documents\Custom Office Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F259F666-5E35-4362-A9ED-0C11C9490B9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB2BB163-33AF-4676-B469-0D38CC495160}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="406" uniqueCount="195">
   <si>
     <t>Item</t>
   </si>
@@ -605,6 +605,9 @@
   </si>
   <si>
     <t>Glass Single</t>
+  </si>
+  <si>
+    <t>Big Glass Single</t>
   </si>
 </sst>
 </file>
@@ -977,7 +980,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F100"/>
+  <dimension ref="A1:F101"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="8.81640625" bestFit="1" customWidth="1"/>
@@ -2987,6 +2990,26 @@
         <v>6</v>
       </c>
     </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A101" t="s">
+        <v>98</v>
+      </c>
+      <c r="B101" t="s">
+        <v>194</v>
+      </c>
+      <c r="C101">
+        <v>3</v>
+      </c>
+      <c r="D101">
+        <v>5</v>
+      </c>
+      <c r="E101" t="s">
+        <v>181</v>
+      </c>
+      <c r="F101" t="s">
+        <v>6</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
